--- a/research/traditional_assets/database/data/belgium/belgium_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_office_equipment_services.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.08460000000000001</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.03181818181818181</v>
+        <v>-0.05043103448275862</v>
       </c>
       <c r="H2">
-        <v>-0.03181818181818181</v>
+        <v>-0.05043103448275862</v>
       </c>
       <c r="I2">
-        <v>-0.07272727272727272</v>
+        <v>-0.06681034482758622</v>
       </c>
       <c r="J2">
-        <v>-0.07272727272727272</v>
+        <v>-0.06681034482758622</v>
       </c>
       <c r="K2">
-        <v>-2.17</v>
+        <v>-2.1</v>
       </c>
       <c r="L2">
-        <v>-0.09393939393939393</v>
+        <v>-0.09051724137931035</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="V2">
-        <v>0.6897163120567377</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="W2">
-        <v>-0.7457044673539518</v>
+        <v>-0.8860759493670886</v>
       </c>
       <c r="X2">
-        <v>0.1348747666478803</v>
+        <v>0.1790273616288177</v>
       </c>
       <c r="Y2">
-        <v>-0.8805792340018321</v>
+        <v>-1.065103310995906</v>
       </c>
       <c r="Z2">
-        <v>3.818181818181818</v>
+        <v>3.504531722054379</v>
       </c>
       <c r="AA2">
-        <v>-0.2776859504132231</v>
+        <v>-0.2341389728096676</v>
       </c>
       <c r="AB2">
-        <v>0.06190615391566941</v>
+        <v>0.09455475065883834</v>
       </c>
       <c r="AC2">
-        <v>-0.3395921043288925</v>
+        <v>-0.3286937234685059</v>
       </c>
       <c r="AD2">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>7.209999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.6630824372759857</v>
+        <v>0.6526674233825198</v>
       </c>
       <c r="AI2">
-        <v>0.8809523809523809</v>
+        <v>0.9913793103448276</v>
       </c>
       <c r="AJ2">
-        <v>0.5610894941634241</v>
+        <v>0.5938951559389515</v>
       </c>
       <c r="AK2">
-        <v>0.8277841561423651</v>
+        <v>0.988950276243094</v>
       </c>
       <c r="AL2">
-        <v>0.237</v>
+        <v>0.246</v>
       </c>
       <c r="AM2">
-        <v>0.237</v>
+        <v>0.246</v>
       </c>
       <c r="AN2">
-        <v>-8.879999999999999</v>
+        <v>-9.82905982905983</v>
       </c>
       <c r="AO2">
-        <v>-7.088607594936709</v>
+        <v>-6.300813008130081</v>
       </c>
       <c r="AP2">
-        <v>-5.767999999999999</v>
+        <v>-7.649572649572649</v>
       </c>
       <c r="AQ2">
-        <v>-7.088607594936709</v>
+        <v>-6.300813008130081</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.08460000000000001</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.03181818181818181</v>
+        <v>-0.05043103448275862</v>
       </c>
       <c r="H3">
-        <v>-0.03181818181818181</v>
+        <v>-0.05043103448275862</v>
       </c>
       <c r="I3">
-        <v>-0.07272727272727272</v>
+        <v>-0.06681034482758622</v>
       </c>
       <c r="J3">
-        <v>-0.07272727272727272</v>
+        <v>-0.06681034482758622</v>
       </c>
       <c r="K3">
-        <v>-2.17</v>
+        <v>-2.1</v>
       </c>
       <c r="L3">
-        <v>-0.09393939393939393</v>
+        <v>-0.09051724137931035</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="V3">
-        <v>0.6897163120567377</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="W3">
-        <v>-0.7457044673539518</v>
+        <v>-0.8860759493670886</v>
       </c>
       <c r="X3">
-        <v>0.1348747666478803</v>
+        <v>0.1790273616288177</v>
       </c>
       <c r="Y3">
-        <v>-0.8805792340018321</v>
+        <v>-1.065103310995906</v>
       </c>
       <c r="Z3">
-        <v>3.818181818181818</v>
+        <v>3.504531722054379</v>
       </c>
       <c r="AA3">
-        <v>-0.2776859504132231</v>
+        <v>-0.2341389728096676</v>
       </c>
       <c r="AB3">
-        <v>0.06190615391566941</v>
+        <v>0.09455475065883834</v>
       </c>
       <c r="AC3">
-        <v>-0.3395921043288925</v>
+        <v>-0.3286937234685059</v>
       </c>
       <c r="AD3">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="AG3">
-        <v>7.209999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.6630824372759857</v>
+        <v>0.6526674233825198</v>
       </c>
       <c r="AI3">
-        <v>0.8809523809523809</v>
+        <v>0.9913793103448276</v>
       </c>
       <c r="AJ3">
-        <v>0.5610894941634241</v>
+        <v>0.5938951559389515</v>
       </c>
       <c r="AK3">
-        <v>0.8277841561423651</v>
+        <v>0.988950276243094</v>
       </c>
       <c r="AL3">
-        <v>0.237</v>
+        <v>0.246</v>
       </c>
       <c r="AM3">
-        <v>0.237</v>
+        <v>0.246</v>
       </c>
       <c r="AN3">
-        <v>-8.879999999999999</v>
+        <v>-9.82905982905983</v>
       </c>
       <c r="AO3">
-        <v>-7.088607594936709</v>
+        <v>-6.300813008130081</v>
       </c>
       <c r="AP3">
-        <v>-5.767999999999999</v>
+        <v>-7.649572649572649</v>
       </c>
       <c r="AQ3">
-        <v>-7.088607594936709</v>
+        <v>-6.300813008130081</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_office_equipment_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtbr_fou" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.06909999999999999</v>
+        <v>0.00942</v>
       </c>
       <c r="G2">
-        <v>-0.05043103448275862</v>
+        <v>0.02473684210526316</v>
       </c>
       <c r="H2">
-        <v>-0.05043103448275862</v>
+        <v>0.02463815789473684</v>
       </c>
       <c r="I2">
-        <v>-0.06681034482758622</v>
+        <v>0.02299342105263158</v>
       </c>
       <c r="J2">
-        <v>-0.06681034482758622</v>
+        <v>0.01149671052631579</v>
       </c>
       <c r="K2">
-        <v>-2.1</v>
+        <v>-0.652</v>
       </c>
       <c r="L2">
-        <v>-0.09051724137931035</v>
+        <v>-0.02144736842105263</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.55</v>
+        <v>0.717</v>
       </c>
       <c r="V2">
-        <v>0.4166666666666666</v>
+        <v>0.09663072776280324</v>
       </c>
       <c r="W2">
-        <v>-0.8860759493670886</v>
+        <v>-6.52</v>
       </c>
       <c r="X2">
-        <v>0.1790273616288177</v>
+        <v>0.120412238872818</v>
       </c>
       <c r="Y2">
-        <v>-1.065103310995906</v>
+        <v>-6.640412238872818</v>
       </c>
       <c r="Z2">
-        <v>3.504531722054379</v>
+        <v>4.342857142857143</v>
       </c>
       <c r="AA2">
-        <v>-0.2341389728096676</v>
+        <v>0.04992857142857142</v>
       </c>
       <c r="AB2">
-        <v>0.09455475065883834</v>
+        <v>0.0785090961515342</v>
       </c>
       <c r="AC2">
-        <v>-0.3286937234685059</v>
+        <v>-0.02858052472296278</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AG2">
-        <v>8.949999999999999</v>
+        <v>8.572999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.6526674233825198</v>
+        <v>0.5559545182525433</v>
       </c>
       <c r="AI2">
-        <v>0.9913793103448276</v>
+        <v>0.90926886561613</v>
       </c>
       <c r="AJ2">
-        <v>0.5938951559389515</v>
+        <v>0.5360470205715</v>
       </c>
       <c r="AK2">
-        <v>0.988950276243094</v>
+        <v>0.902421052631579</v>
       </c>
       <c r="AL2">
-        <v>0.246</v>
+        <v>0.282</v>
       </c>
       <c r="AM2">
-        <v>0.246</v>
+        <v>0.282</v>
       </c>
       <c r="AN2">
-        <v>-9.82905982905983</v>
+        <v>6.932835820895521</v>
       </c>
       <c r="AO2">
-        <v>-6.300813008130081</v>
+        <v>2.478723404255319</v>
       </c>
       <c r="AP2">
-        <v>-7.649572649572649</v>
+        <v>6.397761194029849</v>
       </c>
       <c r="AQ2">
-        <v>-6.300813008130081</v>
+        <v>2.478723404255319</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.06909999999999999</v>
+        <v>0.00942</v>
       </c>
       <c r="G3">
-        <v>-0.05043103448275862</v>
+        <v>0.02473684210526316</v>
       </c>
       <c r="H3">
-        <v>-0.05043103448275862</v>
+        <v>0.02463815789473684</v>
       </c>
       <c r="I3">
-        <v>-0.06681034482758622</v>
+        <v>0.02299342105263158</v>
       </c>
       <c r="J3">
-        <v>-0.06681034482758622</v>
+        <v>0.01149671052631579</v>
       </c>
       <c r="K3">
-        <v>-2.1</v>
+        <v>-0.652</v>
       </c>
       <c r="L3">
-        <v>-0.09051724137931035</v>
+        <v>-0.02144736842105263</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8834 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.55</v>
+        <v>0.717</v>
       </c>
       <c r="V3">
-        <v>0.4166666666666666</v>
+        <v>0.09663072776280324</v>
       </c>
       <c r="W3">
-        <v>-0.8860759493670886</v>
+        <v>-6.52</v>
       </c>
       <c r="X3">
-        <v>0.1790273616288177</v>
+        <v>0.120412238872818</v>
       </c>
       <c r="Y3">
-        <v>-1.065103310995906</v>
+        <v>-6.640412238872818</v>
       </c>
       <c r="Z3">
-        <v>3.504531722054379</v>
+        <v>4.342857142857143</v>
       </c>
       <c r="AA3">
-        <v>-0.2341389728096676</v>
+        <v>0.04992857142857142</v>
       </c>
       <c r="AB3">
-        <v>0.09455475065883834</v>
+        <v>0.0785090961515342</v>
       </c>
       <c r="AC3">
-        <v>-0.3286937234685059</v>
+        <v>-0.02858052472296278</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.5</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AG3">
-        <v>8.949999999999999</v>
+        <v>8.572999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.6526674233825198</v>
+        <v>0.5559545182525433</v>
       </c>
       <c r="AI3">
-        <v>0.9913793103448276</v>
+        <v>0.90926886561613</v>
       </c>
       <c r="AJ3">
-        <v>0.5938951559389515</v>
+        <v>0.5360470205715</v>
       </c>
       <c r="AK3">
-        <v>0.988950276243094</v>
+        <v>0.902421052631579</v>
       </c>
       <c r="AL3">
-        <v>0.246</v>
+        <v>0.282</v>
       </c>
       <c r="AM3">
-        <v>0.246</v>
+        <v>0.282</v>
       </c>
       <c r="AN3">
-        <v>-9.82905982905983</v>
+        <v>6.932835820895521</v>
       </c>
       <c r="AO3">
-        <v>-6.300813008130081</v>
+        <v>2.478723404255319</v>
       </c>
       <c r="AP3">
-        <v>-7.649572649572649</v>
+        <v>6.397761194029849</v>
       </c>
       <c r="AQ3">
-        <v>-6.300813008130081</v>
+        <v>2.478723404255319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fountain S.A. (ENXTBR:FOU)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTBR:FOU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Office Equipment &amp; Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-2.4113475177305</v>
+      </c>
+      <c r="F2">
+        <v>-8.645862466130771</v>
+      </c>
+      <c r="G2">
+        <v>6.93283582089552</v>
+      </c>
+      <c r="H2">
+        <v>0.124701492537313</v>
+      </c>
+      <c r="I2">
+        <v>0.5559545182525431</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>7.42</v>
+      </c>
+      <c r="L2">
+        <v>13.2105249793876</v>
+      </c>
+      <c r="M2">
+        <v>15.993</v>
+      </c>
+      <c r="N2">
+        <v>12.6606249793876</v>
+      </c>
+      <c r="O2">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="P2">
+        <v>0.1671</v>
+      </c>
+      <c r="Q2">
+        <v>0.0785090961515342</v>
+      </c>
+      <c r="R2">
+        <v>0.08896083927810999</v>
+      </c>
+      <c r="S2">
+        <v>0.0450407087465906</v>
+      </c>
+      <c r="T2">
+        <v>0.7549579892280071</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.120412238872818</v>
+      </c>
+      <c r="X2">
+        <v>0.0822335953392222</v>
+      </c>
+      <c r="Y2">
+        <v>1.490185290285</v>
+      </c>
+      <c r="Z2">
+        <v>0.793068610451479</v>
+      </c>
+      <c r="AA2">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.06005427832878751</v>
+      </c>
+      <c r="AC2">
+        <v>-2.411347517730496</v>
+      </c>
+      <c r="AD2">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0.282</v>
+      </c>
+      <c r="AF2">
+        <v>2.02</v>
+      </c>
+      <c r="AG2">
+        <v>1.34</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>7.42</v>
+      </c>
+      <c r="AK2">
+        <v>0.05476650414205181</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>2.38</v>
+      </c>
+      <c r="AR2">
+        <v>0.282</v>
+      </c>
+      <c r="AS2">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AT2">
+        <v>0.717</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.717</v>
+      </c>
+      <c r="H2">
+        <v>7.42</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.675</v>
+      </c>
+      <c r="K2">
+        <v>2.02</v>
+      </c>
+      <c r="L2">
+        <v>-0.345</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-0.345</v>
+      </c>
+      <c r="O2">
+        <v>-0.08624999999999999</v>
+      </c>
+      <c r="P2">
+        <v>-0.25875</v>
+      </c>
+      <c r="Q2">
+        <v>1.76125</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08896083927811002</v>
+      </c>
+      <c r="C3">
+        <v>13.2105249793876</v>
+      </c>
+      <c r="D3">
+        <v>12.6606249793876</v>
+      </c>
+      <c r="E3">
+        <v>-9.1229</v>
+      </c>
+      <c r="F3">
+        <v>0.1671</v>
+      </c>
+      <c r="G3">
+        <v>0.717</v>
+      </c>
+      <c r="H3">
+        <v>7.42</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.675</v>
+      </c>
+      <c r="K3">
+        <v>2.02</v>
+      </c>
+      <c r="L3">
+        <v>-0.345</v>
+      </c>
+      <c r="M3">
+        <v>0.03990348000000001</v>
+      </c>
+      <c r="N3">
+        <v>-0.38490348</v>
+      </c>
+      <c r="O3">
+        <v>-0.09622586999999999</v>
+      </c>
+      <c r="P3">
+        <v>-0.28867761</v>
+      </c>
+      <c r="Q3">
+        <v>1.73132239</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08223359533922217</v>
+      </c>
+      <c r="T3">
+        <v>0.7930686104514787</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-2.161465616532693</v>
+      </c>
+      <c r="W3">
+        <v>0.7549579892280072</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-8.645862466130771</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09096083927811002</v>
+      </c>
+      <c r="C4">
+        <v>12.55797937864165</v>
+      </c>
+      <c r="D4">
+        <v>12.17517937864165</v>
+      </c>
+      <c r="E4">
+        <v>-8.9558</v>
+      </c>
+      <c r="F4">
+        <v>0.3342</v>
+      </c>
+      <c r="G4">
+        <v>0.717</v>
+      </c>
+      <c r="H4">
+        <v>7.42</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.675</v>
+      </c>
+      <c r="K4">
+        <v>2.02</v>
+      </c>
+      <c r="L4">
+        <v>-0.345</v>
+      </c>
+      <c r="M4">
+        <v>0.07980696000000001</v>
+      </c>
+      <c r="N4">
+        <v>-0.42480696</v>
+      </c>
+      <c r="O4">
+        <v>-0.10620174</v>
+      </c>
+      <c r="P4">
+        <v>-0.31860522</v>
+      </c>
+      <c r="Q4">
+        <v>1.70139478</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08267679529166322</v>
+      </c>
+      <c r="T4">
+        <v>0.8011611472928204</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-1.080732808266347</v>
+      </c>
+      <c r="W4">
+        <v>0.4968789946140036</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-4.322931233065385</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09296083927811004</v>
+      </c>
+      <c r="C5">
+        <v>11.94128592547806</v>
+      </c>
+      <c r="D5">
+        <v>11.72558592547806</v>
+      </c>
+      <c r="E5">
+        <v>-8.788699999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.5013</v>
+      </c>
+      <c r="G5">
+        <v>0.717</v>
+      </c>
+      <c r="H5">
+        <v>7.42</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.675</v>
+      </c>
+      <c r="K5">
+        <v>2.02</v>
+      </c>
+      <c r="L5">
+        <v>-0.345</v>
+      </c>
+      <c r="M5">
+        <v>0.11971044</v>
+      </c>
+      <c r="N5">
+        <v>-0.4647104399999999</v>
+      </c>
+      <c r="O5">
+        <v>-0.11617761</v>
+      </c>
+      <c r="P5">
+        <v>-0.34853283</v>
+      </c>
+      <c r="Q5">
+        <v>1.67146717</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08312913338745358</v>
+      </c>
+      <c r="T5">
+        <v>0.8094205405638805</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-0.720488538844231</v>
+      </c>
+      <c r="W5">
+        <v>0.4108526630760024</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-2.881954155376924</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09496083927811004</v>
+      </c>
+      <c r="C6">
+        <v>11.35661431949074</v>
+      </c>
+      <c r="D6">
+        <v>11.30801431949074</v>
+      </c>
+      <c r="E6">
+        <v>-8.621599999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.6684</v>
+      </c>
+      <c r="G6">
+        <v>0.717</v>
+      </c>
+      <c r="H6">
+        <v>7.42</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.675</v>
+      </c>
+      <c r="K6">
+        <v>2.02</v>
+      </c>
+      <c r="L6">
+        <v>-0.345</v>
+      </c>
+      <c r="M6">
+        <v>0.15961392</v>
+      </c>
+      <c r="N6">
+        <v>-0.5046139199999999</v>
+      </c>
+      <c r="O6">
+        <v>-0.12615348</v>
+      </c>
+      <c r="P6">
+        <v>-0.37846044</v>
+      </c>
+      <c r="Q6">
+        <v>1.64153956</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08359089519357288</v>
+      </c>
+      <c r="T6">
+        <v>0.8178520045280875</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-0.5403664041331733</v>
+      </c>
+      <c r="W6">
+        <v>0.3678394973070018</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-2.161465616532693</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09696083927811004</v>
+      </c>
+      <c r="C7">
+        <v>10.80066111655057</v>
+      </c>
+      <c r="D7">
+        <v>10.91916111655057</v>
+      </c>
+      <c r="E7">
+        <v>-8.454499999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.8355000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0.717</v>
+      </c>
+      <c r="H7">
+        <v>7.42</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.675</v>
+      </c>
+      <c r="K7">
+        <v>2.02</v>
+      </c>
+      <c r="L7">
+        <v>-0.345</v>
+      </c>
+      <c r="M7">
+        <v>0.1995174</v>
+      </c>
+      <c r="N7">
+        <v>-0.5445174</v>
+      </c>
+      <c r="O7">
+        <v>-0.13612935</v>
+      </c>
+      <c r="P7">
+        <v>-0.40838805</v>
+      </c>
+      <c r="Q7">
+        <v>1.61161195</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08406237830087365</v>
+      </c>
+      <c r="T7">
+        <v>0.8264609729968042</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.4322931233065386</v>
+      </c>
+      <c r="W7">
+        <v>0.3420315978456014</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-1.729172493226154</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09896083927811003</v>
+      </c>
+      <c r="C8">
+        <v>10.27056215418325</v>
+      </c>
+      <c r="D8">
+        <v>10.55616215418325</v>
+      </c>
+      <c r="E8">
+        <v>-8.2874</v>
+      </c>
+      <c r="F8">
+        <v>1.0026</v>
+      </c>
+      <c r="G8">
+        <v>0.717</v>
+      </c>
+      <c r="H8">
+        <v>7.42</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.675</v>
+      </c>
+      <c r="K8">
+        <v>2.02</v>
+      </c>
+      <c r="L8">
+        <v>-0.345</v>
+      </c>
+      <c r="M8">
+        <v>0.23942088</v>
+      </c>
+      <c r="N8">
+        <v>-0.5844208799999999</v>
+      </c>
+      <c r="O8">
+        <v>-0.14610522</v>
+      </c>
+      <c r="P8">
+        <v>-0.4383156599999999</v>
+      </c>
+      <c r="Q8">
+        <v>1.58168434</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08454389296364889</v>
+      </c>
+      <c r="T8">
+        <v>0.8352531110074084</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.3602442694221155</v>
+      </c>
+      <c r="W8">
+        <v>0.3248263315380012</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-1.440977077688462</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.10096083927811</v>
+      </c>
+      <c r="C9">
+        <v>9.763821883016561</v>
+      </c>
+      <c r="D9">
+        <v>10.21652188301656</v>
+      </c>
+      <c r="E9">
+        <v>-8.120299999999999</v>
+      </c>
+      <c r="F9">
+        <v>1.1697</v>
+      </c>
+      <c r="G9">
+        <v>0.717</v>
+      </c>
+      <c r="H9">
+        <v>7.42</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.675</v>
+      </c>
+      <c r="K9">
+        <v>2.02</v>
+      </c>
+      <c r="L9">
+        <v>-0.345</v>
+      </c>
+      <c r="M9">
+        <v>0.27932436</v>
+      </c>
+      <c r="N9">
+        <v>-0.62432436</v>
+      </c>
+      <c r="O9">
+        <v>-0.15608109</v>
+      </c>
+      <c r="P9">
+        <v>-0.46824327</v>
+      </c>
+      <c r="Q9">
+        <v>1.55175673</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08503576278046232</v>
+      </c>
+      <c r="T9">
+        <v>0.8442343272548</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.3087808023618133</v>
+      </c>
+      <c r="W9">
+        <v>0.312536855604001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-1.235123209447253</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.10296083927811</v>
+      </c>
+      <c r="C10">
+        <v>9.278255915365099</v>
+      </c>
+      <c r="D10">
+        <v>9.898055915365099</v>
+      </c>
+      <c r="E10">
+        <v>-7.953199999999999</v>
+      </c>
+      <c r="F10">
+        <v>1.3368</v>
+      </c>
+      <c r="G10">
+        <v>0.717</v>
+      </c>
+      <c r="H10">
+        <v>7.42</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.675</v>
+      </c>
+      <c r="K10">
+        <v>2.02</v>
+      </c>
+      <c r="L10">
+        <v>-0.345</v>
+      </c>
+      <c r="M10">
+        <v>0.31922784</v>
+      </c>
+      <c r="N10">
+        <v>-0.66422784</v>
+      </c>
+      <c r="O10">
+        <v>-0.16605696</v>
+      </c>
+      <c r="P10">
+        <v>-0.49817088</v>
+      </c>
+      <c r="Q10">
+        <v>1.52182912</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08553832541938039</v>
+      </c>
+      <c r="T10">
+        <v>0.8534107873336564</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.2701832020665866</v>
+      </c>
+      <c r="W10">
+        <v>0.3033197486535009</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-1.080732808266347</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.10496083927811</v>
+      </c>
+      <c r="C11">
+        <v>8.811943994133021</v>
+      </c>
+      <c r="D11">
+        <v>9.59884399413302</v>
+      </c>
+      <c r="E11">
+        <v>-7.786099999999999</v>
+      </c>
+      <c r="F11">
+        <v>1.5039</v>
+      </c>
+      <c r="G11">
+        <v>0.717</v>
+      </c>
+      <c r="H11">
+        <v>7.42</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.675</v>
+      </c>
+      <c r="K11">
+        <v>2.02</v>
+      </c>
+      <c r="L11">
+        <v>-0.345</v>
+      </c>
+      <c r="M11">
+        <v>0.35913132</v>
+      </c>
+      <c r="N11">
+        <v>-0.70413132</v>
+      </c>
+      <c r="O11">
+        <v>-0.17603283</v>
+      </c>
+      <c r="P11">
+        <v>-0.52809849</v>
+      </c>
+      <c r="Q11">
+        <v>1.49190151</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08605193339102193</v>
+      </c>
+      <c r="T11">
+        <v>0.8627889278538066</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.2401628462814103</v>
+      </c>
+      <c r="W11">
+        <v>0.2961508876920008</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-0.9606513851256413</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.10696083927811</v>
+      </c>
+      <c r="C12">
+        <v>8.363191241737535</v>
+      </c>
+      <c r="D12">
+        <v>9.317191241737534</v>
+      </c>
+      <c r="E12">
+        <v>-7.618999999999999</v>
+      </c>
+      <c r="F12">
+        <v>1.671</v>
+      </c>
+      <c r="G12">
+        <v>0.717</v>
+      </c>
+      <c r="H12">
+        <v>7.42</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.675</v>
+      </c>
+      <c r="K12">
+        <v>2.02</v>
+      </c>
+      <c r="L12">
+        <v>-0.345</v>
+      </c>
+      <c r="M12">
+        <v>0.3990348000000001</v>
+      </c>
+      <c r="N12">
+        <v>-0.7440348000000001</v>
+      </c>
+      <c r="O12">
+        <v>-0.1860087</v>
+      </c>
+      <c r="P12">
+        <v>-0.5580261000000001</v>
+      </c>
+      <c r="Q12">
+        <v>1.4619739</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.0865769548731444</v>
+      </c>
+      <c r="T12">
+        <v>0.8723754714966266</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.2161465616532693</v>
+      </c>
+      <c r="W12">
+        <v>0.2904157989228007</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-0.8645862466130771</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.10896083927811</v>
+      </c>
+      <c r="C13">
+        <v>7.930496036845381</v>
+      </c>
+      <c r="D13">
+        <v>9.05159603684538</v>
+      </c>
+      <c r="E13">
+        <v>-7.451899999999999</v>
+      </c>
+      <c r="F13">
+        <v>1.8381</v>
+      </c>
+      <c r="G13">
+        <v>0.717</v>
+      </c>
+      <c r="H13">
+        <v>7.42</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.675</v>
+      </c>
+      <c r="K13">
+        <v>2.02</v>
+      </c>
+      <c r="L13">
+        <v>-0.345</v>
+      </c>
+      <c r="M13">
+        <v>0.43893828</v>
+      </c>
+      <c r="N13">
+        <v>-0.78393828</v>
+      </c>
+      <c r="O13">
+        <v>-0.19598457</v>
+      </c>
+      <c r="P13">
+        <v>-0.58795371</v>
+      </c>
+      <c r="Q13">
+        <v>1.43204629</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08711377459082018</v>
+      </c>
+      <c r="T13">
+        <v>0.8821774430864764</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.1964968742302448</v>
+      </c>
+      <c r="W13">
+        <v>0.2857234535661825</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-0.7859874969209792</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.11096083927811</v>
+      </c>
+      <c r="C14">
+        <v>7.512523233053278</v>
+      </c>
+      <c r="D14">
+        <v>8.800723233053278</v>
+      </c>
+      <c r="E14">
+        <v>-7.284799999999999</v>
+      </c>
+      <c r="F14">
+        <v>2.0052</v>
+      </c>
+      <c r="G14">
+        <v>0.717</v>
+      </c>
+      <c r="H14">
+        <v>7.42</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.675</v>
+      </c>
+      <c r="K14">
+        <v>2.02</v>
+      </c>
+      <c r="L14">
+        <v>-0.345</v>
+      </c>
+      <c r="M14">
+        <v>0.47884176</v>
+      </c>
+      <c r="N14">
+        <v>-0.82384176</v>
+      </c>
+      <c r="O14">
+        <v>-0.20596044</v>
+      </c>
+      <c r="P14">
+        <v>-0.61788132</v>
+      </c>
+      <c r="Q14">
+        <v>1.40211868</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08766279475662495</v>
+      </c>
+      <c r="T14">
+        <v>0.8922021867579135</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.1801221347110578</v>
+      </c>
+      <c r="W14">
+        <v>0.2818131657690006</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-0.720488538844231</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.11296083927811</v>
+      </c>
+      <c r="C15">
+        <v>7.108081711066188</v>
+      </c>
+      <c r="D15">
+        <v>8.563381711066187</v>
+      </c>
+      <c r="E15">
+        <v>-7.117699999999999</v>
+      </c>
+      <c r="F15">
+        <v>2.1723</v>
+      </c>
+      <c r="G15">
+        <v>0.717</v>
+      </c>
+      <c r="H15">
+        <v>7.42</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.675</v>
+      </c>
+      <c r="K15">
+        <v>2.02</v>
+      </c>
+      <c r="L15">
+        <v>-0.345</v>
+      </c>
+      <c r="M15">
+        <v>0.5187452400000001</v>
+      </c>
+      <c r="N15">
+        <v>-0.8637452400000001</v>
+      </c>
+      <c r="O15">
+        <v>-0.21593631</v>
+      </c>
+      <c r="P15">
+        <v>-0.6478089300000001</v>
+      </c>
+      <c r="Q15">
+        <v>1.37219107</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08822443607566663</v>
+      </c>
+      <c r="T15">
+        <v>0.9024573843068552</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.1662665858871302</v>
+      </c>
+      <c r="W15">
+        <v>0.2785044607098467</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.6650663435485209</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.11496083927811</v>
+      </c>
+      <c r="C16">
+        <v>6.716105467783312</v>
+      </c>
+      <c r="D16">
+        <v>8.338505467783312</v>
+      </c>
+      <c r="E16">
+        <v>-6.950599999999999</v>
+      </c>
+      <c r="F16">
+        <v>2.3394</v>
+      </c>
+      <c r="G16">
+        <v>0.717</v>
+      </c>
+      <c r="H16">
+        <v>7.42</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.675</v>
+      </c>
+      <c r="K16">
+        <v>2.02</v>
+      </c>
+      <c r="L16">
+        <v>-0.345</v>
+      </c>
+      <c r="M16">
+        <v>0.5586487200000001</v>
+      </c>
+      <c r="N16">
+        <v>-0.9036487200000001</v>
+      </c>
+      <c r="O16">
+        <v>-0.22591218</v>
+      </c>
+      <c r="P16">
+        <v>-0.6777365400000001</v>
+      </c>
+      <c r="Q16">
+        <v>1.34226346</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08879913882073251</v>
+      </c>
+      <c r="T16">
+        <v>0.9129510748220511</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.1543904011809066</v>
+      </c>
+      <c r="W16">
+        <v>0.2756684278020005</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.6175616047236265</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.11696083927811</v>
+      </c>
+      <c r="C17">
+        <v>6.335637608768558</v>
+      </c>
+      <c r="D17">
+        <v>8.125137608768558</v>
+      </c>
+      <c r="E17">
+        <v>-6.783499999999999</v>
+      </c>
+      <c r="F17">
+        <v>2.5065</v>
+      </c>
+      <c r="G17">
+        <v>0.717</v>
+      </c>
+      <c r="H17">
+        <v>7.42</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.675</v>
+      </c>
+      <c r="K17">
+        <v>2.02</v>
+      </c>
+      <c r="L17">
+        <v>-0.345</v>
+      </c>
+      <c r="M17">
+        <v>0.5985522</v>
+      </c>
+      <c r="N17">
+        <v>-0.9435522</v>
+      </c>
+      <c r="O17">
+        <v>-0.23588805</v>
+      </c>
+      <c r="P17">
+        <v>-0.7076641499999999</v>
+      </c>
+      <c r="Q17">
+        <v>1.31233585</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08938736398332936</v>
+      </c>
+      <c r="T17">
+        <v>0.9236916757023105</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.1440977077688462</v>
+      </c>
+      <c r="W17">
+        <v>0.2732105326152005</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.5763908310753849</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.11896083927811</v>
+      </c>
+      <c r="C18">
+        <v>5.965816737032689</v>
+      </c>
+      <c r="D18">
+        <v>7.922416737032689</v>
+      </c>
+      <c r="E18">
+        <v>-6.616399999999999</v>
+      </c>
+      <c r="F18">
+        <v>2.6736</v>
+      </c>
+      <c r="G18">
+        <v>0.717</v>
+      </c>
+      <c r="H18">
+        <v>7.42</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.675</v>
+      </c>
+      <c r="K18">
+        <v>2.02</v>
+      </c>
+      <c r="L18">
+        <v>-0.345</v>
+      </c>
+      <c r="M18">
+        <v>0.6384556800000001</v>
+      </c>
+      <c r="N18">
+        <v>-0.9834556800000001</v>
+      </c>
+      <c r="O18">
+        <v>-0.24586392</v>
+      </c>
+      <c r="P18">
+        <v>-0.73759176</v>
+      </c>
+      <c r="Q18">
+        <v>1.28240824</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08998959450694044</v>
+      </c>
+      <c r="T18">
+        <v>0.9346880051749572</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.1350916010332933</v>
+      </c>
+      <c r="W18">
+        <v>0.2710598743267505</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.5403664041331733</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.12096083927811</v>
+      </c>
+      <c r="C19">
+        <v>5.605865329801668</v>
+      </c>
+      <c r="D19">
+        <v>7.729565329801668</v>
+      </c>
+      <c r="E19">
+        <v>-6.449299999999999</v>
+      </c>
+      <c r="F19">
+        <v>2.8407</v>
+      </c>
+      <c r="G19">
+        <v>0.717</v>
+      </c>
+      <c r="H19">
+        <v>7.42</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.675</v>
+      </c>
+      <c r="K19">
+        <v>2.02</v>
+      </c>
+      <c r="L19">
+        <v>-0.345</v>
+      </c>
+      <c r="M19">
+        <v>0.6783591600000002</v>
+      </c>
+      <c r="N19">
+        <v>-1.02335916</v>
+      </c>
+      <c r="O19">
+        <v>-0.25583979</v>
+      </c>
+      <c r="P19">
+        <v>-0.76751937</v>
+      </c>
+      <c r="Q19">
+        <v>1.25248063</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09060633660943369</v>
+      </c>
+      <c r="T19">
+        <v>0.9459493064421253</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.127145036266629</v>
+      </c>
+      <c r="W19">
+        <v>0.269162234660471</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.5085801450665157</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.12296083927811</v>
+      </c>
+      <c r="C20">
+        <v>5.255079772573344</v>
+      </c>
+      <c r="D20">
+        <v>7.545879772573343</v>
+      </c>
+      <c r="E20">
+        <v>-6.2822</v>
+      </c>
+      <c r="F20">
+        <v>3.0078</v>
+      </c>
+      <c r="G20">
+        <v>0.717</v>
+      </c>
+      <c r="H20">
+        <v>7.42</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.675</v>
+      </c>
+      <c r="K20">
+        <v>2.02</v>
+      </c>
+      <c r="L20">
+        <v>-0.345</v>
+      </c>
+      <c r="M20">
+        <v>0.7182626400000001</v>
+      </c>
+      <c r="N20">
+        <v>-1.06326264</v>
+      </c>
+      <c r="O20">
+        <v>-0.26581566</v>
+      </c>
+      <c r="P20">
+        <v>-0.79744698</v>
+      </c>
+      <c r="Q20">
+        <v>1.22255302</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09123812120223165</v>
+      </c>
+      <c r="T20">
+        <v>0.9574852735938585</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.1200814231407052</v>
+      </c>
+      <c r="W20">
+        <v>0.2674754438460004</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.4803256925628208</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.12496083927811</v>
+      </c>
+      <c r="C21">
+        <v>4.912821781175027</v>
+      </c>
+      <c r="D21">
+        <v>7.370721781175027</v>
+      </c>
+      <c r="E21">
+        <v>-6.115099999999999</v>
+      </c>
+      <c r="F21">
+        <v>3.1749</v>
+      </c>
+      <c r="G21">
+        <v>0.717</v>
+      </c>
+      <c r="H21">
+        <v>7.42</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.675</v>
+      </c>
+      <c r="K21">
+        <v>2.02</v>
+      </c>
+      <c r="L21">
+        <v>-0.345</v>
+      </c>
+      <c r="M21">
+        <v>0.7581661200000001</v>
+      </c>
+      <c r="N21">
+        <v>-1.10316612</v>
+      </c>
+      <c r="O21">
+        <v>-0.27579153</v>
+      </c>
+      <c r="P21">
+        <v>-0.82737459</v>
+      </c>
+      <c r="Q21">
+        <v>1.19262541</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09188550541460488</v>
+      </c>
+      <c r="T21">
+        <v>0.9693060794406962</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.1137613482385628</v>
+      </c>
+      <c r="W21">
+        <v>0.2659662099593688</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.4550453929542513</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.12696083927811</v>
+      </c>
+      <c r="C22">
+        <v>4.578510991406488</v>
+      </c>
+      <c r="D22">
+        <v>7.203510991406489</v>
+      </c>
+      <c r="E22">
+        <v>-5.947999999999999</v>
+      </c>
+      <c r="F22">
+        <v>3.342000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.717</v>
+      </c>
+      <c r="H22">
+        <v>7.42</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.675</v>
+      </c>
+      <c r="K22">
+        <v>2.02</v>
+      </c>
+      <c r="L22">
+        <v>-0.345</v>
+      </c>
+      <c r="M22">
+        <v>0.7980696000000002</v>
+      </c>
+      <c r="N22">
+        <v>-1.1430696</v>
+      </c>
+      <c r="O22">
+        <v>-0.2857674</v>
+      </c>
+      <c r="P22">
+        <v>-0.8573022</v>
+      </c>
+      <c r="Q22">
+        <v>1.1626978</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09254907423228745</v>
+      </c>
+      <c r="T22">
+        <v>0.981422405433705</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.1080732808266346</v>
+      </c>
+      <c r="W22">
+        <v>0.2646078994614004</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.4322931233065384</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.12896083927811</v>
+      </c>
+      <c r="C23">
+        <v>4.251618534967911</v>
+      </c>
+      <c r="D23">
+        <v>7.043718534967911</v>
+      </c>
+      <c r="E23">
+        <v>-5.780899999999999</v>
+      </c>
+      <c r="F23">
+        <v>3.5091</v>
+      </c>
+      <c r="G23">
+        <v>0.717</v>
+      </c>
+      <c r="H23">
+        <v>7.42</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.675</v>
+      </c>
+      <c r="K23">
+        <v>2.02</v>
+      </c>
+      <c r="L23">
+        <v>-0.345</v>
+      </c>
+      <c r="M23">
+        <v>0.83797308</v>
+      </c>
+      <c r="N23">
+        <v>-1.18297308</v>
+      </c>
+      <c r="O23">
+        <v>-0.29574327</v>
+      </c>
+      <c r="P23">
+        <v>-0.88722981</v>
+      </c>
+      <c r="Q23">
+        <v>1.13277019</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09322944226054425</v>
+      </c>
+      <c r="T23">
+        <v>0.9938454738569164</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.1029269341206044</v>
+      </c>
+      <c r="W23">
+        <v>0.2633789518680004</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.4117077364824178</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.13096083927811</v>
+      </c>
+      <c r="C24">
+        <v>3.93166145184799</v>
+      </c>
+      <c r="D24">
+        <v>6.89086145184799</v>
+      </c>
+      <c r="E24">
+        <v>-5.613799999999999</v>
+      </c>
+      <c r="F24">
+        <v>3.6762</v>
+      </c>
+      <c r="G24">
+        <v>0.717</v>
+      </c>
+      <c r="H24">
+        <v>7.42</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.675</v>
+      </c>
+      <c r="K24">
+        <v>2.02</v>
+      </c>
+      <c r="L24">
+        <v>-0.345</v>
+      </c>
+      <c r="M24">
+        <v>0.87787656</v>
+      </c>
+      <c r="N24">
+        <v>-1.22287656</v>
+      </c>
+      <c r="O24">
+        <v>-0.30571914</v>
+      </c>
+      <c r="P24">
+        <v>-0.91715742</v>
+      </c>
+      <c r="Q24">
+        <v>1.10284258</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09392725562285892</v>
+      </c>
+      <c r="T24">
+        <v>1.006587082496108</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.09824843711512242</v>
+      </c>
+      <c r="W24">
+        <v>0.2622617267830912</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.3929937484604897</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.13296083927811</v>
+      </c>
+      <c r="C25">
+        <v>3.618197814805727</v>
+      </c>
+      <c r="D25">
+        <v>6.744497814805728</v>
+      </c>
+      <c r="E25">
+        <v>-5.446699999999999</v>
+      </c>
+      <c r="F25">
+        <v>3.8433</v>
+      </c>
+      <c r="G25">
+        <v>0.717</v>
+      </c>
+      <c r="H25">
+        <v>7.42</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.675</v>
+      </c>
+      <c r="K25">
+        <v>2.02</v>
+      </c>
+      <c r="L25">
+        <v>-0.345</v>
+      </c>
+      <c r="M25">
+        <v>0.9177800400000001</v>
+      </c>
+      <c r="N25">
+        <v>-1.26278004</v>
+      </c>
+      <c r="O25">
+        <v>-0.31569501</v>
+      </c>
+      <c r="P25">
+        <v>-0.94708503</v>
+      </c>
+      <c r="Q25">
+        <v>1.07291497</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09464319400757137</v>
+      </c>
+      <c r="T25">
+        <v>1.019659642009044</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.09397676593620403</v>
+      </c>
+      <c r="W25">
+        <v>0.2612416517055656</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.3759070637448161</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.13496083927811</v>
+      </c>
+      <c r="C26">
+        <v>3.310822462272672</v>
+      </c>
+      <c r="D26">
+        <v>6.604222462272672</v>
+      </c>
+      <c r="E26">
+        <v>-5.279599999999999</v>
+      </c>
+      <c r="F26">
+        <v>4.0104</v>
+      </c>
+      <c r="G26">
+        <v>0.717</v>
+      </c>
+      <c r="H26">
+        <v>7.42</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.675</v>
+      </c>
+      <c r="K26">
+        <v>2.02</v>
+      </c>
+      <c r="L26">
+        <v>-0.345</v>
+      </c>
+      <c r="M26">
+        <v>0.95768352</v>
+      </c>
+      <c r="N26">
+        <v>-1.30268352</v>
+      </c>
+      <c r="O26">
+        <v>-0.32567088</v>
+      </c>
+      <c r="P26">
+        <v>-0.97701264</v>
+      </c>
+      <c r="Q26">
+        <v>1.04298736</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09537797287609207</v>
+      </c>
+      <c r="T26">
+        <v>1.033076216246005</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.09006106735552888</v>
+      </c>
+      <c r="W26">
+        <v>0.2603065828845003</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.3602442694221155</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.13696083927811</v>
+      </c>
+      <c r="C27">
+        <v>3.009163252900764</v>
+      </c>
+      <c r="D27">
+        <v>6.469663252900765</v>
+      </c>
+      <c r="E27">
+        <v>-5.112499999999999</v>
+      </c>
+      <c r="F27">
+        <v>4.1775</v>
+      </c>
+      <c r="G27">
+        <v>0.717</v>
+      </c>
+      <c r="H27">
+        <v>7.42</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.675</v>
+      </c>
+      <c r="K27">
+        <v>2.02</v>
+      </c>
+      <c r="L27">
+        <v>-0.345</v>
+      </c>
+      <c r="M27">
+        <v>0.9975870000000001</v>
+      </c>
+      <c r="N27">
+        <v>-1.342587</v>
+      </c>
+      <c r="O27">
+        <v>-0.33564675</v>
+      </c>
+      <c r="P27">
+        <v>-1.00694025</v>
+      </c>
+      <c r="Q27">
+        <v>1.01305975</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09613234584777328</v>
+      </c>
+      <c r="T27">
+        <v>1.046850565795952</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.08645862466130771</v>
+      </c>
+      <c r="W27">
+        <v>0.2594463195691203</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.3458344986452309</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.13896083927811</v>
+      </c>
+      <c r="C28">
+        <v>2.71287776884273</v>
+      </c>
+      <c r="D28">
+        <v>6.340477768842731</v>
+      </c>
+      <c r="E28">
+        <v>-4.945399999999998</v>
+      </c>
+      <c r="F28">
+        <v>4.344600000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.717</v>
+      </c>
+      <c r="H28">
+        <v>7.42</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.675</v>
+      </c>
+      <c r="K28">
+        <v>2.02</v>
+      </c>
+      <c r="L28">
+        <v>-0.345</v>
+      </c>
+      <c r="M28">
+        <v>1.03749048</v>
+      </c>
+      <c r="N28">
+        <v>-1.38249048</v>
+      </c>
+      <c r="O28">
+        <v>-0.34562262</v>
+      </c>
+      <c r="P28">
+        <v>-1.03686786</v>
+      </c>
+      <c r="Q28">
+        <v>0.9831321399999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09690710727814861</v>
+      </c>
+      <c r="T28">
+        <v>1.060997195063465</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.08313329294356511</v>
+      </c>
+      <c r="W28">
+        <v>0.2586522303549234</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.3325331717742603</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.14096083927811</v>
+      </c>
+      <c r="C29">
+        <v>2.421650406271204</v>
+      </c>
+      <c r="D29">
+        <v>6.216350406271204</v>
+      </c>
+      <c r="E29">
+        <v>-4.778299999999999</v>
+      </c>
+      <c r="F29">
+        <v>4.5117</v>
+      </c>
+      <c r="G29">
+        <v>0.717</v>
+      </c>
+      <c r="H29">
+        <v>7.42</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.675</v>
+      </c>
+      <c r="K29">
+        <v>2.02</v>
+      </c>
+      <c r="L29">
+        <v>-0.345</v>
+      </c>
+      <c r="M29">
+        <v>1.07739396</v>
+      </c>
+      <c r="N29">
+        <v>-1.42239396</v>
+      </c>
+      <c r="O29">
+        <v>-0.35559849</v>
+      </c>
+      <c r="P29">
+        <v>-1.06679547</v>
+      </c>
+      <c r="Q29">
+        <v>0.9532045299999998</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09770309504908214</v>
+      </c>
+      <c r="T29">
+        <v>1.075531403215019</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.08005428209380344</v>
+      </c>
+      <c r="W29">
+        <v>0.2579169625640003</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.3202171283752138</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.14296083927811</v>
+      </c>
+      <c r="C30">
+        <v>2.135189801088798</v>
+      </c>
+      <c r="D30">
+        <v>6.096989801088799</v>
+      </c>
+      <c r="E30">
+        <v>-4.611199999999998</v>
+      </c>
+      <c r="F30">
+        <v>4.678800000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.717</v>
+      </c>
+      <c r="H30">
+        <v>7.42</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.675</v>
+      </c>
+      <c r="K30">
+        <v>2.02</v>
+      </c>
+      <c r="L30">
+        <v>-0.345</v>
+      </c>
+      <c r="M30">
+        <v>1.11729744</v>
+      </c>
+      <c r="N30">
+        <v>-1.46229744</v>
+      </c>
+      <c r="O30">
+        <v>-0.36557436</v>
+      </c>
+      <c r="P30">
+        <v>-1.09672308</v>
+      </c>
+      <c r="Q30">
+        <v>0.9232769199999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09852119359143049</v>
+      </c>
+      <c r="T30">
+        <v>1.090469339370783</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.07719520059045332</v>
+      </c>
+      <c r="W30">
+        <v>0.2572342139010003</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.3087808023618133</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.14496083927811</v>
+      </c>
+      <c r="C31">
+        <v>1.853226545625709</v>
+      </c>
+      <c r="D31">
+        <v>5.98212654562571</v>
+      </c>
+      <c r="E31">
+        <v>-4.444099999999999</v>
+      </c>
+      <c r="F31">
+        <v>4.8459</v>
+      </c>
+      <c r="G31">
+        <v>0.717</v>
+      </c>
+      <c r="H31">
+        <v>7.42</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.675</v>
+      </c>
+      <c r="K31">
+        <v>2.02</v>
+      </c>
+      <c r="L31">
+        <v>-0.345</v>
+      </c>
+      <c r="M31">
+        <v>1.15720092</v>
+      </c>
+      <c r="N31">
+        <v>-1.50220092</v>
+      </c>
+      <c r="O31">
+        <v>-0.37555023</v>
+      </c>
+      <c r="P31">
+        <v>-1.12665069</v>
+      </c>
+      <c r="Q31">
+        <v>0.8933493099999998</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09936233716314079</v>
+      </c>
+      <c r="T31">
+        <v>1.105828062460513</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.074533297121817</v>
+      </c>
+      <c r="W31">
+        <v>0.2565985513526899</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.298133188487268</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.14696083927811</v>
+      </c>
+      <c r="C32">
+        <v>1.575511158660301</v>
+      </c>
+      <c r="D32">
+        <v>5.871511158660301</v>
+      </c>
+      <c r="E32">
+        <v>-4.276999999999999</v>
+      </c>
+      <c r="F32">
+        <v>5.013</v>
+      </c>
+      <c r="G32">
+        <v>0.717</v>
+      </c>
+      <c r="H32">
+        <v>7.42</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.675</v>
+      </c>
+      <c r="K32">
+        <v>2.02</v>
+      </c>
+      <c r="L32">
+        <v>-0.345</v>
+      </c>
+      <c r="M32">
+        <v>1.1971044</v>
+      </c>
+      <c r="N32">
+        <v>-1.5421044</v>
+      </c>
+      <c r="O32">
+        <v>-0.3855261</v>
+      </c>
+      <c r="P32">
+        <v>-1.1565783</v>
+      </c>
+      <c r="Q32">
+        <v>0.8634217</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1002275134083285</v>
+      </c>
+      <c r="T32">
+        <v>1.121625606209949</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.07204885388442311</v>
+      </c>
+      <c r="W32">
+        <v>0.2560052663076002</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.2881954155376925</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.14896083927811</v>
+      </c>
+      <c r="C33">
+        <v>1.301812276568685</v>
+      </c>
+      <c r="D33">
+        <v>5.764912276568686</v>
+      </c>
+      <c r="E33">
+        <v>-4.109899999999999</v>
+      </c>
+      <c r="F33">
+        <v>5.1801</v>
+      </c>
+      <c r="G33">
+        <v>0.717</v>
+      </c>
+      <c r="H33">
+        <v>7.42</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.675</v>
+      </c>
+      <c r="K33">
+        <v>2.02</v>
+      </c>
+      <c r="L33">
+        <v>-0.345</v>
+      </c>
+      <c r="M33">
+        <v>1.23700788</v>
+      </c>
+      <c r="N33">
+        <v>-1.58200788</v>
+      </c>
+      <c r="O33">
+        <v>-0.39550197</v>
+      </c>
+      <c r="P33">
+        <v>-1.18650591</v>
+      </c>
+      <c r="Q33">
+        <v>0.8334940899999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1011177672258405</v>
+      </c>
+      <c r="T33">
+        <v>1.137881049778209</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.06972469730750622</v>
+      </c>
+      <c r="W33">
+        <v>0.2554502577170325</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.278898789230025</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.15096083927811</v>
+      </c>
+      <c r="C34">
+        <v>1.03191503800177</v>
+      </c>
+      <c r="D34">
+        <v>5.662115038001771</v>
+      </c>
+      <c r="E34">
+        <v>-3.942799999999999</v>
+      </c>
+      <c r="F34">
+        <v>5.3472</v>
+      </c>
+      <c r="G34">
+        <v>0.717</v>
+      </c>
+      <c r="H34">
+        <v>7.42</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.675</v>
+      </c>
+      <c r="K34">
+        <v>2.02</v>
+      </c>
+      <c r="L34">
+        <v>-0.345</v>
+      </c>
+      <c r="M34">
+        <v>1.27691136</v>
+      </c>
+      <c r="N34">
+        <v>-1.62191136</v>
+      </c>
+      <c r="O34">
+        <v>-0.40547784</v>
+      </c>
+      <c r="P34">
+        <v>-1.21643352</v>
+      </c>
+      <c r="Q34">
+        <v>0.80356648</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1020342049791617</v>
+      </c>
+      <c r="T34">
+        <v>1.154614594627888</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.06754580051664666</v>
+      </c>
+      <c r="W34">
+        <v>0.2549299371633753</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.2701832020665866</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1529608392781101</v>
+      </c>
+      <c r="C35">
+        <v>0.7656196383567453</v>
+      </c>
+      <c r="D35">
+        <v>5.562919638356746</v>
+      </c>
+      <c r="E35">
+        <v>-3.775699999999999</v>
+      </c>
+      <c r="F35">
+        <v>5.5143</v>
+      </c>
+      <c r="G35">
+        <v>0.717</v>
+      </c>
+      <c r="H35">
+        <v>7.42</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.675</v>
+      </c>
+      <c r="K35">
+        <v>2.02</v>
+      </c>
+      <c r="L35">
+        <v>-0.345</v>
+      </c>
+      <c r="M35">
+        <v>1.31681484</v>
+      </c>
+      <c r="N35">
+        <v>-1.66181484</v>
+      </c>
+      <c r="O35">
+        <v>-0.41545371</v>
+      </c>
+      <c r="P35">
+        <v>-1.24636113</v>
+      </c>
+      <c r="Q35">
+        <v>0.7736388699999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1029779990833283</v>
+      </c>
+      <c r="T35">
+        <v>1.171847648279051</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.06549895807674827</v>
+      </c>
+      <c r="W35">
+        <v>0.2544411511887275</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.2619958323069931</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.15496083927811</v>
+      </c>
+      <c r="C36">
+        <v>0.5027400335789567</v>
+      </c>
+      <c r="D36">
+        <v>5.467140033578958</v>
+      </c>
+      <c r="E36">
+        <v>-3.608599999999998</v>
+      </c>
+      <c r="F36">
+        <v>5.681400000000001</v>
+      </c>
+      <c r="G36">
+        <v>0.717</v>
+      </c>
+      <c r="H36">
+        <v>7.42</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.675</v>
+      </c>
+      <c r="K36">
+        <v>2.02</v>
+      </c>
+      <c r="L36">
+        <v>-0.345</v>
+      </c>
+      <c r="M36">
+        <v>1.35671832</v>
+      </c>
+      <c r="N36">
+        <v>-1.70171832</v>
+      </c>
+      <c r="O36">
+        <v>-0.4254295800000001</v>
+      </c>
+      <c r="P36">
+        <v>-1.27628874</v>
+      </c>
+      <c r="Q36">
+        <v>0.7437112599999998</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1039503930088333</v>
+      </c>
+      <c r="T36">
+        <v>1.189602915677218</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.06357251813331449</v>
+      </c>
+      <c r="W36">
+        <v>0.2539811173302355</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.254290072533258</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1569608392781101</v>
+      </c>
+      <c r="C37">
+        <v>0.2431027756011055</v>
+      </c>
+      <c r="D37">
+        <v>5.374602775601106</v>
+      </c>
+      <c r="E37">
+        <v>-3.441499999999999</v>
+      </c>
+      <c r="F37">
+        <v>5.8485</v>
+      </c>
+      <c r="G37">
+        <v>0.717</v>
+      </c>
+      <c r="H37">
+        <v>7.42</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.675</v>
+      </c>
+      <c r="K37">
+        <v>2.02</v>
+      </c>
+      <c r="L37">
+        <v>-0.345</v>
+      </c>
+      <c r="M37">
+        <v>1.3966218</v>
+      </c>
+      <c r="N37">
+        <v>-1.7416218</v>
+      </c>
+      <c r="O37">
+        <v>-0.43540545</v>
+      </c>
+      <c r="P37">
+        <v>-1.30621635</v>
+      </c>
+      <c r="Q37">
+        <v>0.7137836499999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1049527067474307</v>
+      </c>
+      <c r="T37">
+        <v>1.207904498995329</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.06175616047236266</v>
+      </c>
+      <c r="W37">
+        <v>0.2535473711208002</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.2470246418894506</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1589608392781101</v>
+      </c>
+      <c r="C38">
+        <v>-0.01345403591735739</v>
+      </c>
+      <c r="D38">
+        <v>5.285145964082643</v>
+      </c>
+      <c r="E38">
+        <v>-3.274399999999999</v>
+      </c>
+      <c r="F38">
+        <v>6.0156</v>
+      </c>
+      <c r="G38">
+        <v>0.717</v>
+      </c>
+      <c r="H38">
+        <v>7.42</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.675</v>
+      </c>
+      <c r="K38">
+        <v>2.02</v>
+      </c>
+      <c r="L38">
+        <v>-0.345</v>
+      </c>
+      <c r="M38">
+        <v>1.43652528</v>
+      </c>
+      <c r="N38">
+        <v>-1.78152528</v>
+      </c>
+      <c r="O38">
+        <v>-0.44538132</v>
+      </c>
+      <c r="P38">
+        <v>-1.33614396</v>
+      </c>
+      <c r="Q38">
+        <v>0.68385604</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1059863427903593</v>
+      </c>
+      <c r="T38">
+        <v>1.226778006792131</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.06004071157035258</v>
+      </c>
+      <c r="W38">
+        <v>0.2531377219230002</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.2401628462814103</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.16096083927811</v>
+      </c>
+      <c r="C39">
+        <v>-0.2670816988789797</v>
+      </c>
+      <c r="D39">
+        <v>5.198618301121021</v>
+      </c>
+      <c r="E39">
+        <v>-3.107299999999999</v>
+      </c>
+      <c r="F39">
+        <v>6.182700000000001</v>
+      </c>
+      <c r="G39">
+        <v>0.717</v>
+      </c>
+      <c r="H39">
+        <v>7.42</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.675</v>
+      </c>
+      <c r="K39">
+        <v>2.02</v>
+      </c>
+      <c r="L39">
+        <v>-0.345</v>
+      </c>
+      <c r="M39">
+        <v>1.47642876</v>
+      </c>
+      <c r="N39">
+        <v>-1.82142876</v>
+      </c>
+      <c r="O39">
+        <v>-0.45535719</v>
+      </c>
+      <c r="P39">
+        <v>-1.36607157</v>
+      </c>
+      <c r="Q39">
+        <v>0.6539284299999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1070527926759206</v>
+      </c>
+      <c r="T39">
+        <v>1.246250673566609</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.05841798963601873</v>
+      </c>
+      <c r="W39">
+        <v>0.2527502159250812</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.233671958544075</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.16296083927811</v>
+      </c>
+      <c r="C40">
+        <v>-0.5179217626760115</v>
+      </c>
+      <c r="D40">
+        <v>5.114878237323989</v>
+      </c>
+      <c r="E40">
+        <v>-2.940199999999999</v>
+      </c>
+      <c r="F40">
+        <v>6.3498</v>
+      </c>
+      <c r="G40">
+        <v>0.717</v>
+      </c>
+      <c r="H40">
+        <v>7.42</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.675</v>
+      </c>
+      <c r="K40">
+        <v>2.02</v>
+      </c>
+      <c r="L40">
+        <v>-0.345</v>
+      </c>
+      <c r="M40">
+        <v>1.51633224</v>
+      </c>
+      <c r="N40">
+        <v>-1.86133224</v>
+      </c>
+      <c r="O40">
+        <v>-0.46533306</v>
+      </c>
+      <c r="P40">
+        <v>-1.39599918</v>
+      </c>
+      <c r="Q40">
+        <v>0.62400082</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1081536441706935</v>
+      </c>
+      <c r="T40">
+        <v>1.2663514908822</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.0568806741192814</v>
+      </c>
+      <c r="W40">
+        <v>0.2523831049796844</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.2275226964771255</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1649608392781101</v>
+      </c>
+      <c r="C41">
+        <v>-0.7661068008953409</v>
+      </c>
+      <c r="D41">
+        <v>5.03379319910466</v>
+      </c>
+      <c r="E41">
+        <v>-2.773099999999999</v>
+      </c>
+      <c r="F41">
+        <v>6.516900000000001</v>
+      </c>
+      <c r="G41">
+        <v>0.717</v>
+      </c>
+      <c r="H41">
+        <v>7.42</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.675</v>
+      </c>
+      <c r="K41">
+        <v>2.02</v>
+      </c>
+      <c r="L41">
+        <v>-0.345</v>
+      </c>
+      <c r="M41">
+        <v>1.55623572</v>
+      </c>
+      <c r="N41">
+        <v>-1.90123572</v>
+      </c>
+      <c r="O41">
+        <v>-0.4753089300000001</v>
+      </c>
+      <c r="P41">
+        <v>-1.42592679</v>
+      </c>
+      <c r="Q41">
+        <v>0.5940732099999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1092905891570983</v>
+      </c>
+      <c r="T41">
+        <v>1.287111351388466</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.05542219529571007</v>
+      </c>
+      <c r="W41">
+        <v>0.2520348202366156</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.2216887811828403</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.16696083927811</v>
+      </c>
+      <c r="C42">
+        <v>-1.011761111673241</v>
+      </c>
+      <c r="D42">
+        <v>4.95523888832676</v>
+      </c>
+      <c r="E42">
+        <v>-2.605999999999998</v>
+      </c>
+      <c r="F42">
+        <v>6.684000000000001</v>
+      </c>
+      <c r="G42">
+        <v>0.717</v>
+      </c>
+      <c r="H42">
+        <v>7.42</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.675</v>
+      </c>
+      <c r="K42">
+        <v>2.02</v>
+      </c>
+      <c r="L42">
+        <v>-0.345</v>
+      </c>
+      <c r="M42">
+        <v>1.5961392</v>
+      </c>
+      <c r="N42">
+        <v>-1.9411392</v>
+      </c>
+      <c r="O42">
+        <v>-0.4852848000000001</v>
+      </c>
+      <c r="P42">
+        <v>-1.4558544</v>
+      </c>
+      <c r="Q42">
+        <v>0.5641455999999998</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1104654323097166</v>
+      </c>
+      <c r="T42">
+        <v>1.30856320724494</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.05403664041331732</v>
+      </c>
+      <c r="W42">
+        <v>0.2517039497307001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.2161465616532692</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1689608392781101</v>
+      </c>
+      <c r="C43">
+        <v>-1.255001353481903</v>
+      </c>
+      <c r="D43">
+        <v>4.879098646518098</v>
+      </c>
+      <c r="E43">
+        <v>-2.438899999999999</v>
+      </c>
+      <c r="F43">
+        <v>6.851100000000001</v>
+      </c>
+      <c r="G43">
+        <v>0.717</v>
+      </c>
+      <c r="H43">
+        <v>7.42</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.675</v>
+      </c>
+      <c r="K43">
+        <v>2.02</v>
+      </c>
+      <c r="L43">
+        <v>-0.345</v>
+      </c>
+      <c r="M43">
+        <v>1.63604268</v>
+      </c>
+      <c r="N43">
+        <v>-1.98104268</v>
+      </c>
+      <c r="O43">
+        <v>-0.4952606700000001</v>
+      </c>
+      <c r="P43">
+        <v>-1.48578201</v>
+      </c>
+      <c r="Q43">
+        <v>0.5342179899999997</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1116801006539491</v>
+      </c>
+      <c r="T43">
+        <v>1.330742244655871</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.05271867357396812</v>
+      </c>
+      <c r="W43">
+        <v>0.2513892192494636</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.2108746942958726</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1709608392781101</v>
+      </c>
+      <c r="C44">
+        <v>-1.495937123187494</v>
+      </c>
+      <c r="D44">
+        <v>4.805262876812507</v>
+      </c>
+      <c r="E44">
+        <v>-2.271799999999999</v>
+      </c>
+      <c r="F44">
+        <v>7.0182</v>
+      </c>
+      <c r="G44">
+        <v>0.717</v>
+      </c>
+      <c r="H44">
+        <v>7.42</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.675</v>
+      </c>
+      <c r="K44">
+        <v>2.02</v>
+      </c>
+      <c r="L44">
+        <v>-0.345</v>
+      </c>
+      <c r="M44">
+        <v>1.67594616</v>
+      </c>
+      <c r="N44">
+        <v>-2.02094616</v>
+      </c>
+      <c r="O44">
+        <v>-0.5052365400000001</v>
+      </c>
+      <c r="P44">
+        <v>-1.51570962</v>
+      </c>
+      <c r="Q44">
+        <v>0.5042903799999998</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1129366541134999</v>
+      </c>
+      <c r="T44">
+        <v>1.353686076460283</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.05146346706030222</v>
+      </c>
+      <c r="W44">
+        <v>0.2510894759340002</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.205853868241209</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.17296083927811</v>
+      </c>
+      <c r="C45">
+        <v>-1.734671482403916</v>
+      </c>
+      <c r="D45">
+        <v>4.733628517596085</v>
+      </c>
+      <c r="E45">
+        <v>-2.104699999999998</v>
+      </c>
+      <c r="F45">
+        <v>7.185300000000001</v>
+      </c>
+      <c r="G45">
+        <v>0.717</v>
+      </c>
+      <c r="H45">
+        <v>7.42</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.675</v>
+      </c>
+      <c r="K45">
+        <v>2.02</v>
+      </c>
+      <c r="L45">
+        <v>-0.345</v>
+      </c>
+      <c r="M45">
+        <v>1.71584964</v>
+      </c>
+      <c r="N45">
+        <v>-2.06084964</v>
+      </c>
+      <c r="O45">
+        <v>-0.5152124100000001</v>
+      </c>
+      <c r="P45">
+        <v>-1.54563723</v>
+      </c>
+      <c r="Q45">
+        <v>0.4743627699999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1142372971681227</v>
+      </c>
+      <c r="T45">
+        <v>1.377434954994673</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.05026664224494635</v>
+      </c>
+      <c r="W45">
+        <v>0.2508036741680932</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.2010665689797855</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.17496083927811</v>
+      </c>
+      <c r="C46">
+        <v>-1.971301437458433</v>
+      </c>
+      <c r="D46">
+        <v>4.664098562541567</v>
+      </c>
+      <c r="E46">
+        <v>-1.937599999999999</v>
+      </c>
+      <c r="F46">
+        <v>7.3524</v>
+      </c>
+      <c r="G46">
+        <v>0.717</v>
+      </c>
+      <c r="H46">
+        <v>7.42</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.675</v>
+      </c>
+      <c r="K46">
+        <v>2.02</v>
+      </c>
+      <c r="L46">
+        <v>-0.345</v>
+      </c>
+      <c r="M46">
+        <v>1.75575312</v>
+      </c>
+      <c r="N46">
+        <v>-2.10075312</v>
+      </c>
+      <c r="O46">
+        <v>-0.5251882800000001</v>
+      </c>
+      <c r="P46">
+        <v>-1.57556484</v>
+      </c>
+      <c r="Q46">
+        <v>0.4444351599999998</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1155843917604106</v>
+      </c>
+      <c r="T46">
+        <v>1.402032007762436</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.04912421855756121</v>
+      </c>
+      <c r="W46">
+        <v>0.2505308633915456</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.1964968742302449</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.17696083927811</v>
+      </c>
+      <c r="C47">
+        <v>-2.205918377669732</v>
+      </c>
+      <c r="D47">
+        <v>4.596581622330269</v>
+      </c>
+      <c r="E47">
+        <v>-1.770499999999998</v>
+      </c>
+      <c r="F47">
+        <v>7.519500000000001</v>
+      </c>
+      <c r="G47">
+        <v>0.717</v>
+      </c>
+      <c r="H47">
+        <v>7.42</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.675</v>
+      </c>
+      <c r="K47">
+        <v>2.02</v>
+      </c>
+      <c r="L47">
+        <v>-0.345</v>
+      </c>
+      <c r="M47">
+        <v>1.7956566</v>
+      </c>
+      <c r="N47">
+        <v>-2.1406566</v>
+      </c>
+      <c r="O47">
+        <v>-0.5351641500000001</v>
+      </c>
+      <c r="P47">
+        <v>-1.60549245</v>
+      </c>
+      <c r="Q47">
+        <v>0.4145075499999997</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1169804716105999</v>
+      </c>
+      <c r="T47">
+        <v>1.427523498812661</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.04803256925628206</v>
+      </c>
+      <c r="W47">
+        <v>0.2502701775384001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.1921302770251283</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.17896083927811</v>
+      </c>
+      <c r="C48">
+        <v>-2.438608476102427</v>
+      </c>
+      <c r="D48">
+        <v>4.530991523897574</v>
+      </c>
+      <c r="E48">
+        <v>-1.603399999999999</v>
+      </c>
+      <c r="F48">
+        <v>7.6866</v>
+      </c>
+      <c r="G48">
+        <v>0.717</v>
+      </c>
+      <c r="H48">
+        <v>7.42</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.675</v>
+      </c>
+      <c r="K48">
+        <v>2.02</v>
+      </c>
+      <c r="L48">
+        <v>-0.345</v>
+      </c>
+      <c r="M48">
+        <v>1.83556008</v>
+      </c>
+      <c r="N48">
+        <v>-2.18056008</v>
+      </c>
+      <c r="O48">
+        <v>-0.5451400200000001</v>
+      </c>
+      <c r="P48">
+        <v>-1.63542006</v>
+      </c>
+      <c r="Q48">
+        <v>0.3845799399999998</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1184282581219073</v>
+      </c>
+      <c r="T48">
+        <v>1.453959119161044</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.04698838296810202</v>
+      </c>
+      <c r="W48">
+        <v>0.2500208258527827</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.1879535318724082</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1809608392781101</v>
+      </c>
+      <c r="C49">
+        <v>-2.669453056493286</v>
+      </c>
+      <c r="D49">
+        <v>4.467246943506715</v>
+      </c>
+      <c r="E49">
+        <v>-1.436299999999998</v>
+      </c>
+      <c r="F49">
+        <v>7.853700000000001</v>
+      </c>
+      <c r="G49">
+        <v>0.717</v>
+      </c>
+      <c r="H49">
+        <v>7.42</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.675</v>
+      </c>
+      <c r="K49">
+        <v>2.02</v>
+      </c>
+      <c r="L49">
+        <v>-0.345</v>
+      </c>
+      <c r="M49">
+        <v>1.87546356</v>
+      </c>
+      <c r="N49">
+        <v>-2.22046356</v>
+      </c>
+      <c r="O49">
+        <v>-0.5551158900000001</v>
+      </c>
+      <c r="P49">
+        <v>-1.66534767</v>
+      </c>
+      <c r="Q49">
+        <v>0.35465233</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1199306780864716</v>
+      </c>
+      <c r="T49">
+        <v>1.481392310088611</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.04598863013899347</v>
+      </c>
+      <c r="W49">
+        <v>0.2497820848771917</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.1839545205559738</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.18296083927811</v>
+      </c>
+      <c r="C50">
+        <v>-2.898528929634375</v>
+      </c>
+      <c r="D50">
+        <v>4.405271070365624</v>
+      </c>
+      <c r="E50">
+        <v>-1.2692</v>
+      </c>
+      <c r="F50">
+        <v>8.020799999999999</v>
+      </c>
+      <c r="G50">
+        <v>0.717</v>
+      </c>
+      <c r="H50">
+        <v>7.42</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.675</v>
+      </c>
+      <c r="K50">
+        <v>2.02</v>
+      </c>
+      <c r="L50">
+        <v>-0.345</v>
+      </c>
+      <c r="M50">
+        <v>1.91536704</v>
+      </c>
+      <c r="N50">
+        <v>-2.26036704</v>
+      </c>
+      <c r="O50">
+        <v>-0.5650917600000001</v>
+      </c>
+      <c r="P50">
+        <v>-1.69527528</v>
+      </c>
+      <c r="Q50">
+        <v>0.3247247199999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1214908834342884</v>
+      </c>
+      <c r="T50">
+        <v>1.509880623744161</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.04503053367776444</v>
+      </c>
+      <c r="W50">
+        <v>0.2495532914422501</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.180122134711058</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.18496083927811</v>
+      </c>
+      <c r="C51">
+        <v>-3.125908702138739</v>
+      </c>
+      <c r="D51">
+        <v>4.344991297861262</v>
+      </c>
+      <c r="E51">
+        <v>-1.102099999999998</v>
+      </c>
+      <c r="F51">
+        <v>8.187900000000001</v>
+      </c>
+      <c r="G51">
+        <v>0.717</v>
+      </c>
+      <c r="H51">
+        <v>7.42</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.675</v>
+      </c>
+      <c r="K51">
+        <v>2.02</v>
+      </c>
+      <c r="L51">
+        <v>-0.345</v>
+      </c>
+      <c r="M51">
+        <v>1.95527052</v>
+      </c>
+      <c r="N51">
+        <v>-2.30027052</v>
+      </c>
+      <c r="O51">
+        <v>-0.5750676300000001</v>
+      </c>
+      <c r="P51">
+        <v>-1.72520289</v>
+      </c>
+      <c r="Q51">
+        <v>0.2947971099999998</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1231122733055489</v>
+      </c>
+      <c r="T51">
+        <v>1.539486126170517</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.04411154319454475</v>
+      </c>
+      <c r="W51">
+        <v>0.2493338365148573</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.176446172778179</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1869608392781101</v>
+      </c>
+      <c r="C52">
+        <v>-3.35166106019815</v>
+      </c>
+      <c r="D52">
+        <v>4.28633893980185</v>
+      </c>
+      <c r="E52">
+        <v>-0.9349999999999987</v>
+      </c>
+      <c r="F52">
+        <v>8.355</v>
+      </c>
+      <c r="G52">
+        <v>0.717</v>
+      </c>
+      <c r="H52">
+        <v>7.42</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.675</v>
+      </c>
+      <c r="K52">
+        <v>2.02</v>
+      </c>
+      <c r="L52">
+        <v>-0.345</v>
+      </c>
+      <c r="M52">
+        <v>1.995174</v>
+      </c>
+      <c r="N52">
+        <v>-2.340174</v>
+      </c>
+      <c r="O52">
+        <v>-0.5850435</v>
+      </c>
+      <c r="P52">
+        <v>-1.7551305</v>
+      </c>
+      <c r="Q52">
+        <v>0.2648694999999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1247985187716599</v>
+      </c>
+      <c r="T52">
+        <v>1.570275848693928</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.04322931233065386</v>
+      </c>
+      <c r="W52">
+        <v>0.2491231597845602</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.1729172493226154</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.18896083927811</v>
+      </c>
+      <c r="C53">
+        <v>-3.575851030664593</v>
+      </c>
+      <c r="D53">
+        <v>4.229248969335408</v>
+      </c>
+      <c r="E53">
+        <v>-0.7678999999999991</v>
+      </c>
+      <c r="F53">
+        <v>8.5221</v>
+      </c>
+      <c r="G53">
+        <v>0.717</v>
+      </c>
+      <c r="H53">
+        <v>7.42</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.675</v>
+      </c>
+      <c r="K53">
+        <v>2.02</v>
+      </c>
+      <c r="L53">
+        <v>-0.345</v>
+      </c>
+      <c r="M53">
+        <v>2.03507748</v>
+      </c>
+      <c r="N53">
+        <v>-2.38007748</v>
+      </c>
+      <c r="O53">
+        <v>-0.5950193699999999</v>
+      </c>
+      <c r="P53">
+        <v>-1.78505811</v>
+      </c>
+      <c r="Q53">
+        <v>0.2349418900000002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1265535905833264</v>
+      </c>
+      <c r="T53">
+        <v>1.602322294585641</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.042381678755543</v>
+      </c>
+      <c r="W53">
+        <v>0.2489207448868237</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.169526715022172</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1909608392781101</v>
+      </c>
+      <c r="C54">
+        <v>-3.798540221541828</v>
+      </c>
+      <c r="D54">
+        <v>4.173659778458173</v>
+      </c>
+      <c r="E54">
+        <v>-0.6007999999999978</v>
+      </c>
+      <c r="F54">
+        <v>8.689200000000001</v>
+      </c>
+      <c r="G54">
+        <v>0.717</v>
+      </c>
+      <c r="H54">
+        <v>7.42</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.675</v>
+      </c>
+      <c r="K54">
+        <v>2.02</v>
+      </c>
+      <c r="L54">
+        <v>-0.345</v>
+      </c>
+      <c r="M54">
+        <v>2.07498096</v>
+      </c>
+      <c r="N54">
+        <v>-2.41998096</v>
+      </c>
+      <c r="O54">
+        <v>-0.60499524</v>
+      </c>
+      <c r="P54">
+        <v>-1.81498572</v>
+      </c>
+      <c r="Q54">
+        <v>0.2050142799999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1283817903871458</v>
+      </c>
+      <c r="T54">
+        <v>1.635704009056175</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.04156664647178256</v>
+      </c>
+      <c r="W54">
+        <v>0.2487261151774617</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.1662665858871302</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.19296083927811</v>
+      </c>
+      <c r="C55">
+        <v>-4.019787043756889</v>
+      </c>
+      <c r="D55">
+        <v>4.119512956243113</v>
+      </c>
+      <c r="E55">
+        <v>-0.4336999999999982</v>
+      </c>
+      <c r="F55">
+        <v>8.856300000000001</v>
+      </c>
+      <c r="G55">
+        <v>0.717</v>
+      </c>
+      <c r="H55">
+        <v>7.42</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.675</v>
+      </c>
+      <c r="K55">
+        <v>2.02</v>
+      </c>
+      <c r="L55">
+        <v>-0.345</v>
+      </c>
+      <c r="M55">
+        <v>2.11488444</v>
+      </c>
+      <c r="N55">
+        <v>-2.459884440000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.6149711100000002</v>
+      </c>
+      <c r="P55">
+        <v>-1.84491333</v>
+      </c>
+      <c r="Q55">
+        <v>0.1750866699999996</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1302877859272978</v>
+      </c>
+      <c r="T55">
+        <v>1.670506222014817</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.04078237012325835</v>
+      </c>
+      <c r="W55">
+        <v>0.2485388299854341</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.1631294804930334</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.19496083927811</v>
+      </c>
+      <c r="C56">
+        <v>-4.239646915889831</v>
+      </c>
+      <c r="D56">
+        <v>4.06675308411017</v>
+      </c>
+      <c r="E56">
+        <v>-0.2665999999999986</v>
+      </c>
+      <c r="F56">
+        <v>9.023400000000001</v>
+      </c>
+      <c r="G56">
+        <v>0.717</v>
+      </c>
+      <c r="H56">
+        <v>7.42</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.675</v>
+      </c>
+      <c r="K56">
+        <v>2.02</v>
+      </c>
+      <c r="L56">
+        <v>-0.345</v>
+      </c>
+      <c r="M56">
+        <v>2.15478792</v>
+      </c>
+      <c r="N56">
+        <v>-2.49978792</v>
+      </c>
+      <c r="O56">
+        <v>-0.62494698</v>
+      </c>
+      <c r="P56">
+        <v>-1.87484094</v>
+      </c>
+      <c r="Q56">
+        <v>0.1451590599999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1322766508387608</v>
+      </c>
+      <c r="T56">
+        <v>1.706821574667313</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.04002714104690172</v>
+      </c>
+      <c r="W56">
+        <v>0.2483584812820001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.1601085641876068</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.19696083927811</v>
+      </c>
+      <c r="C57">
+        <v>-4.458172453370184</v>
+      </c>
+      <c r="D57">
+        <v>4.015327546629818</v>
+      </c>
+      <c r="E57">
+        <v>-0.09949999999999726</v>
+      </c>
+      <c r="F57">
+        <v>9.190500000000002</v>
+      </c>
+      <c r="G57">
+        <v>0.717</v>
+      </c>
+      <c r="H57">
+        <v>7.42</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.675</v>
+      </c>
+      <c r="K57">
+        <v>2.02</v>
+      </c>
+      <c r="L57">
+        <v>-0.345</v>
+      </c>
+      <c r="M57">
+        <v>2.1946914</v>
+      </c>
+      <c r="N57">
+        <v>-2.539691400000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.6349228500000001</v>
+      </c>
+      <c r="P57">
+        <v>-1.90476855</v>
+      </c>
+      <c r="Q57">
+        <v>0.1152314499999996</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1343539097462888</v>
+      </c>
+      <c r="T57">
+        <v>1.744750942993253</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.03929937484604896</v>
+      </c>
+      <c r="W57">
+        <v>0.2481846907132365</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.157197499384196</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.19896083927811</v>
+      </c>
+      <c r="C58">
+        <v>-4.675413643497908</v>
+      </c>
+      <c r="D58">
+        <v>3.965186356502094</v>
+      </c>
+      <c r="E58">
+        <v>0.06760000000000232</v>
+      </c>
+      <c r="F58">
+        <v>9.357600000000001</v>
+      </c>
+      <c r="G58">
+        <v>0.717</v>
+      </c>
+      <c r="H58">
+        <v>7.42</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.675</v>
+      </c>
+      <c r="K58">
+        <v>2.02</v>
+      </c>
+      <c r="L58">
+        <v>-0.345</v>
+      </c>
+      <c r="M58">
+        <v>2.23459488</v>
+      </c>
+      <c r="N58">
+        <v>-2.57959488</v>
+      </c>
+      <c r="O58">
+        <v>-0.64489872</v>
+      </c>
+      <c r="P58">
+        <v>-1.93469616</v>
+      </c>
+      <c r="Q58">
+        <v>0.08530383999999991</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1365255895132499</v>
+      </c>
+      <c r="T58">
+        <v>1.784404373515827</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.03859760029522666</v>
+      </c>
+      <c r="W58">
+        <v>0.2480171069505001</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.1543904011809065</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.20096083927811</v>
+      </c>
+      <c r="C59">
+        <v>-4.89141800751272</v>
+      </c>
+      <c r="D59">
+        <v>3.916281992487281</v>
+      </c>
+      <c r="E59">
+        <v>0.2347000000000019</v>
+      </c>
+      <c r="F59">
+        <v>9.524700000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.717</v>
+      </c>
+      <c r="H59">
+        <v>7.42</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.675</v>
+      </c>
+      <c r="K59">
+        <v>2.02</v>
+      </c>
+      <c r="L59">
+        <v>-0.345</v>
+      </c>
+      <c r="M59">
+        <v>2.27449836</v>
+      </c>
+      <c r="N59">
+        <v>-2.619498360000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.6548745900000001</v>
+      </c>
+      <c r="P59">
+        <v>-1.96462377</v>
+      </c>
+      <c r="Q59">
+        <v>0.05537622999999958</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.138798277641465</v>
+      </c>
+      <c r="T59">
+        <v>1.825902149644102</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.03792044941285426</v>
+      </c>
+      <c r="W59">
+        <v>0.2478554033197896</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.1516817976514171</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.20296083927811</v>
+      </c>
+      <c r="C60">
+        <v>-5.106230750816287</v>
+      </c>
+      <c r="D60">
+        <v>3.868569249183714</v>
+      </c>
+      <c r="E60">
+        <v>0.4018000000000015</v>
+      </c>
+      <c r="F60">
+        <v>9.691800000000001</v>
+      </c>
+      <c r="G60">
+        <v>0.717</v>
+      </c>
+      <c r="H60">
+        <v>7.42</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.675</v>
+      </c>
+      <c r="K60">
+        <v>2.02</v>
+      </c>
+      <c r="L60">
+        <v>-0.345</v>
+      </c>
+      <c r="M60">
+        <v>2.31440184</v>
+      </c>
+      <c r="N60">
+        <v>-2.65940184</v>
+      </c>
+      <c r="O60">
+        <v>-0.66485046</v>
+      </c>
+      <c r="P60">
+        <v>-1.99455138</v>
+      </c>
+      <c r="Q60">
+        <v>0.02544861999999992</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1411791890138809</v>
+      </c>
+      <c r="T60">
+        <v>1.869376010349914</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.0372666485609085</v>
+      </c>
+      <c r="W60">
+        <v>0.247699275676345</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.149066594243634</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.20496083927811</v>
+      </c>
+      <c r="C61">
+        <v>-5.319894902345501</v>
+      </c>
+      <c r="D61">
+        <v>3.822005097654499</v>
+      </c>
+      <c r="E61">
+        <v>0.5689000000000011</v>
+      </c>
+      <c r="F61">
+        <v>9.8589</v>
+      </c>
+      <c r="G61">
+        <v>0.717</v>
+      </c>
+      <c r="H61">
+        <v>7.42</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.675</v>
+      </c>
+      <c r="K61">
+        <v>2.02</v>
+      </c>
+      <c r="L61">
+        <v>-0.345</v>
+      </c>
+      <c r="M61">
+        <v>2.35430532</v>
+      </c>
+      <c r="N61">
+        <v>-2.699305320000001</v>
+      </c>
+      <c r="O61">
+        <v>-0.6748263300000001</v>
+      </c>
+      <c r="P61">
+        <v>-2.02447899</v>
+      </c>
+      <c r="Q61">
+        <v>-0.004478990000000405</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1436762424044633</v>
+      </c>
+      <c r="T61">
+        <v>1.914970547187717</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.03663501044970666</v>
+      </c>
+      <c r="W61">
+        <v>0.24754844049539</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.1465400417988267</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.20696083927811</v>
+      </c>
+      <c r="C62">
+        <v>-5.532451444000048</v>
+      </c>
+      <c r="D62">
+        <v>3.776548555999952</v>
+      </c>
+      <c r="E62">
+        <v>0.7360000000000007</v>
+      </c>
+      <c r="F62">
+        <v>10.026</v>
+      </c>
+      <c r="G62">
+        <v>0.717</v>
+      </c>
+      <c r="H62">
+        <v>7.42</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.675</v>
+      </c>
+      <c r="K62">
+        <v>2.02</v>
+      </c>
+      <c r="L62">
+        <v>-0.345</v>
+      </c>
+      <c r="M62">
+        <v>2.3942088</v>
+      </c>
+      <c r="N62">
+        <v>-2.7392088</v>
+      </c>
+      <c r="O62">
+        <v>-0.6848022</v>
+      </c>
+      <c r="P62">
+        <v>-2.0544066</v>
+      </c>
+      <c r="Q62">
+        <v>-0.03440660000000006</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1462981484645749</v>
+      </c>
+      <c r="T62">
+        <v>1.96284481086741</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.03602442694221156</v>
+      </c>
+      <c r="W62">
+        <v>0.2474026331538001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.1440977077688463</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.20896083927811</v>
+      </c>
+      <c r="C63">
+        <v>-5.743939430942539</v>
+      </c>
+      <c r="D63">
+        <v>3.732160569057463</v>
+      </c>
+      <c r="E63">
+        <v>0.903100000000002</v>
+      </c>
+      <c r="F63">
+        <v>10.1931</v>
+      </c>
+      <c r="G63">
+        <v>0.717</v>
+      </c>
+      <c r="H63">
+        <v>7.42</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.675</v>
+      </c>
+      <c r="K63">
+        <v>2.02</v>
+      </c>
+      <c r="L63">
+        <v>-0.345</v>
+      </c>
+      <c r="M63">
+        <v>2.43411228</v>
+      </c>
+      <c r="N63">
+        <v>-2.779112280000001</v>
+      </c>
+      <c r="O63">
+        <v>-0.6947780700000001</v>
+      </c>
+      <c r="P63">
+        <v>-2.084334210000001</v>
+      </c>
+      <c r="Q63">
+        <v>-0.06433421000000061</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1490545112457178</v>
+      </c>
+      <c r="T63">
+        <v>2.013174164992215</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.03543386256610972</v>
+      </c>
+      <c r="W63">
+        <v>0.247261606380787</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.141735450264439</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.21096083927811</v>
+      </c>
+      <c r="C64">
+        <v>-5.954396103513454</v>
+      </c>
+      <c r="D64">
+        <v>3.688803896486547</v>
+      </c>
+      <c r="E64">
+        <v>1.070200000000002</v>
+      </c>
+      <c r="F64">
+        <v>10.3602</v>
+      </c>
+      <c r="G64">
+        <v>0.717</v>
+      </c>
+      <c r="H64">
+        <v>7.42</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.675</v>
+      </c>
+      <c r="K64">
+        <v>2.02</v>
+      </c>
+      <c r="L64">
+        <v>-0.345</v>
+      </c>
+      <c r="M64">
+        <v>2.47401576</v>
+      </c>
+      <c r="N64">
+        <v>-2.81901576</v>
+      </c>
+      <c r="O64">
+        <v>-0.70475394</v>
+      </c>
+      <c r="P64">
+        <v>-2.11426182</v>
+      </c>
+      <c r="Q64">
+        <v>-0.09426182000000027</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1519559457521841</v>
+      </c>
+      <c r="T64">
+        <v>2.06615243249201</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.03486234865375311</v>
+      </c>
+      <c r="W64">
+        <v>0.2471251288585163</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.1394493946150124</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.21296083927811</v>
+      </c>
+      <c r="C65">
+        <v>-6.163856991434946</v>
+      </c>
+      <c r="D65">
+        <v>3.646443008565055</v>
+      </c>
+      <c r="E65">
+        <v>1.237300000000001</v>
+      </c>
+      <c r="F65">
+        <v>10.5273</v>
+      </c>
+      <c r="G65">
+        <v>0.717</v>
+      </c>
+      <c r="H65">
+        <v>7.42</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.675</v>
+      </c>
+      <c r="K65">
+        <v>2.02</v>
+      </c>
+      <c r="L65">
+        <v>-0.345</v>
+      </c>
+      <c r="M65">
+        <v>2.51391924</v>
+      </c>
+      <c r="N65">
+        <v>-2.858919240000001</v>
+      </c>
+      <c r="O65">
+        <v>-0.7147298100000001</v>
+      </c>
+      <c r="P65">
+        <v>-2.14418943</v>
+      </c>
+      <c r="Q65">
+        <v>-0.1241894300000004</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1550142145562972</v>
+      </c>
+      <c r="T65">
+        <v>2.12199439012693</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.03430897804020148</v>
+      </c>
+      <c r="W65">
+        <v>0.2469929839560001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.137235912160806</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.21496083927811</v>
+      </c>
+      <c r="C66">
+        <v>-6.372356010916321</v>
+      </c>
+      <c r="D66">
+        <v>3.605043989083679</v>
+      </c>
+      <c r="E66">
+        <v>1.404400000000001</v>
+      </c>
+      <c r="F66">
+        <v>10.6944</v>
+      </c>
+      <c r="G66">
+        <v>0.717</v>
+      </c>
+      <c r="H66">
+        <v>7.42</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.675</v>
+      </c>
+      <c r="K66">
+        <v>2.02</v>
+      </c>
+      <c r="L66">
+        <v>-0.345</v>
+      </c>
+      <c r="M66">
+        <v>2.55382272</v>
+      </c>
+      <c r="N66">
+        <v>-2.89882272</v>
+      </c>
+      <c r="O66">
+        <v>-0.72470568</v>
+      </c>
+      <c r="P66">
+        <v>-2.17411704</v>
+      </c>
+      <c r="Q66">
+        <v>-0.15411704</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.158242387182861</v>
+      </c>
+      <c r="T66">
+        <v>2.180938678741566</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.03377290025832333</v>
+      </c>
+      <c r="W66">
+        <v>0.2468649685816876</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.1350916010332932</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2169608392781101</v>
+      </c>
+      <c r="C67">
+        <v>-6.579925555218999</v>
+      </c>
+      <c r="D67">
+        <v>3.564574444781002</v>
+      </c>
+      <c r="E67">
+        <v>1.571500000000002</v>
+      </c>
+      <c r="F67">
+        <v>10.8615</v>
+      </c>
+      <c r="G67">
+        <v>0.717</v>
+      </c>
+      <c r="H67">
+        <v>7.42</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.675</v>
+      </c>
+      <c r="K67">
+        <v>2.02</v>
+      </c>
+      <c r="L67">
+        <v>-0.345</v>
+      </c>
+      <c r="M67">
+        <v>2.5937262</v>
+      </c>
+      <c r="N67">
+        <v>-2.938726200000001</v>
+      </c>
+      <c r="O67">
+        <v>-0.7346815500000001</v>
+      </c>
+      <c r="P67">
+        <v>-2.20404465</v>
+      </c>
+      <c r="Q67">
+        <v>-0.1840446500000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1616550268166571</v>
+      </c>
+      <c r="T67">
+        <v>2.243251212419897</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.03325331717742604</v>
+      </c>
+      <c r="W67">
+        <v>0.2467408921419694</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.1330132687097043</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2189608392781101</v>
+      </c>
+      <c r="C68">
+        <v>-6.78659657918918</v>
+      </c>
+      <c r="D68">
+        <v>3.525003420810821</v>
+      </c>
+      <c r="E68">
+        <v>1.738600000000002</v>
+      </c>
+      <c r="F68">
+        <v>11.0286</v>
+      </c>
+      <c r="G68">
+        <v>0.717</v>
+      </c>
+      <c r="H68">
+        <v>7.42</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.675</v>
+      </c>
+      <c r="K68">
+        <v>2.02</v>
+      </c>
+      <c r="L68">
+        <v>-0.345</v>
+      </c>
+      <c r="M68">
+        <v>2.63362968</v>
+      </c>
+      <c r="N68">
+        <v>-2.97862968</v>
+      </c>
+      <c r="O68">
+        <v>-0.74465742</v>
+      </c>
+      <c r="P68">
+        <v>-2.23397226</v>
+      </c>
+      <c r="Q68">
+        <v>-0.2139722599999998</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1652684099583234</v>
+      </c>
+      <c r="T68">
+        <v>2.309229189255777</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.03274947903837414</v>
+      </c>
+      <c r="W68">
+        <v>0.2466205755943638</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.1309979161534964</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2209608392781101</v>
+      </c>
+      <c r="C69">
+        <v>-6.992398678221882</v>
+      </c>
+      <c r="D69">
+        <v>3.486301321778119</v>
+      </c>
+      <c r="E69">
+        <v>1.905700000000001</v>
+      </c>
+      <c r="F69">
+        <v>11.1957</v>
+      </c>
+      <c r="G69">
+        <v>0.717</v>
+      </c>
+      <c r="H69">
+        <v>7.42</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.675</v>
+      </c>
+      <c r="K69">
+        <v>2.02</v>
+      </c>
+      <c r="L69">
+        <v>-0.345</v>
+      </c>
+      <c r="M69">
+        <v>2.67353316</v>
+      </c>
+      <c r="N69">
+        <v>-3.01853316</v>
+      </c>
+      <c r="O69">
+        <v>-0.7546332900000001</v>
+      </c>
+      <c r="P69">
+        <v>-2.26389987</v>
+      </c>
+      <c r="Q69">
+        <v>-0.2438998700000004</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1691007860176666</v>
+      </c>
+      <c r="T69">
+        <v>2.379205831354437</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.03226068084377154</v>
+      </c>
+      <c r="W69">
+        <v>0.2465038505854927</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.1290427233750862</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2229608392781101</v>
+      </c>
+      <c r="C70">
+        <v>-7.197360162079625</v>
+      </c>
+      <c r="D70">
+        <v>3.448439837920377</v>
+      </c>
+      <c r="E70">
+        <v>2.072800000000003</v>
+      </c>
+      <c r="F70">
+        <v>11.3628</v>
+      </c>
+      <c r="G70">
+        <v>0.717</v>
+      </c>
+      <c r="H70">
+        <v>7.42</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.675</v>
+      </c>
+      <c r="K70">
+        <v>2.02</v>
+      </c>
+      <c r="L70">
+        <v>-0.345</v>
+      </c>
+      <c r="M70">
+        <v>2.713436640000001</v>
+      </c>
+      <c r="N70">
+        <v>-3.058436640000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.7646091600000002</v>
+      </c>
+      <c r="P70">
+        <v>-2.293827480000001</v>
+      </c>
+      <c r="Q70">
+        <v>-0.2738274800000009</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1731726855807187</v>
+      </c>
+      <c r="T70">
+        <v>2.453556013584263</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.03178625906665725</v>
+      </c>
+      <c r="W70">
+        <v>0.2463905586651178</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.1271450362666291</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2249608392781101</v>
+      </c>
+      <c r="C71">
+        <v>-7.401508123952731</v>
+      </c>
+      <c r="D71">
+        <v>3.411391876047271</v>
+      </c>
+      <c r="E71">
+        <v>2.239900000000002</v>
+      </c>
+      <c r="F71">
+        <v>11.5299</v>
+      </c>
+      <c r="G71">
+        <v>0.717</v>
+      </c>
+      <c r="H71">
+        <v>7.42</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.675</v>
+      </c>
+      <c r="K71">
+        <v>2.02</v>
+      </c>
+      <c r="L71">
+        <v>-0.345</v>
+      </c>
+      <c r="M71">
+        <v>2.75334012</v>
+      </c>
+      <c r="N71">
+        <v>-3.09834012</v>
+      </c>
+      <c r="O71">
+        <v>-0.7745850300000001</v>
+      </c>
+      <c r="P71">
+        <v>-2.323755090000001</v>
+      </c>
+      <c r="Q71">
+        <v>-0.3037550900000006</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.177507288341387</v>
+      </c>
+      <c r="T71">
+        <v>2.5327029817644</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.03132558864540134</v>
+      </c>
+      <c r="W71">
+        <v>0.2462805505685219</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.1253023545816054</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2269608392781101</v>
+      </c>
+      <c r="C72">
+        <v>-7.604868505115306</v>
+      </c>
+      <c r="D72">
+        <v>3.375131494884696</v>
+      </c>
+      <c r="E72">
+        <v>2.407000000000002</v>
+      </c>
+      <c r="F72">
+        <v>11.697</v>
+      </c>
+      <c r="G72">
+        <v>0.717</v>
+      </c>
+      <c r="H72">
+        <v>7.42</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.675</v>
+      </c>
+      <c r="K72">
+        <v>2.02</v>
+      </c>
+      <c r="L72">
+        <v>-0.345</v>
+      </c>
+      <c r="M72">
+        <v>2.7932436</v>
+      </c>
+      <c r="N72">
+        <v>-3.1382436</v>
+      </c>
+      <c r="O72">
+        <v>-0.7845609</v>
+      </c>
+      <c r="P72">
+        <v>-2.3536827</v>
+      </c>
+      <c r="Q72">
+        <v>-0.3336827000000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1821308646194332</v>
+      </c>
+      <c r="T72">
+        <v>2.61712641448988</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.03087808023618133</v>
+      </c>
+      <c r="W72">
+        <v>0.2461736855604001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.1235123209447253</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.22896083927811</v>
+      </c>
+      <c r="C73">
+        <v>-7.80746615550113</v>
+      </c>
+      <c r="D73">
+        <v>3.339633844498871</v>
+      </c>
+      <c r="E73">
+        <v>2.574100000000001</v>
+      </c>
+      <c r="F73">
+        <v>11.8641</v>
+      </c>
+      <c r="G73">
+        <v>0.717</v>
+      </c>
+      <c r="H73">
+        <v>7.42</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.675</v>
+      </c>
+      <c r="K73">
+        <v>2.02</v>
+      </c>
+      <c r="L73">
+        <v>-0.345</v>
+      </c>
+      <c r="M73">
+        <v>2.83314708</v>
+      </c>
+      <c r="N73">
+        <v>-3.17814708</v>
+      </c>
+      <c r="O73">
+        <v>-0.7945367700000001</v>
+      </c>
+      <c r="P73">
+        <v>-2.38361031</v>
+      </c>
+      <c r="Q73">
+        <v>-0.3636103100000003</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1870733082269999</v>
+      </c>
+      <c r="T73">
+        <v>2.707372152920565</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.03044317769764356</v>
+      </c>
+      <c r="W73">
+        <v>0.2460698308341973</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.1217727107905744</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2309608392781101</v>
+      </c>
+      <c r="C74">
+        <v>-8.009324890496718</v>
+      </c>
+      <c r="D74">
+        <v>3.304875109503282</v>
+      </c>
+      <c r="E74">
+        <v>2.741200000000001</v>
+      </c>
+      <c r="F74">
+        <v>12.0312</v>
+      </c>
+      <c r="G74">
+        <v>0.717</v>
+      </c>
+      <c r="H74">
+        <v>7.42</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.675</v>
+      </c>
+      <c r="K74">
+        <v>2.02</v>
+      </c>
+      <c r="L74">
+        <v>-0.345</v>
+      </c>
+      <c r="M74">
+        <v>2.87305056</v>
+      </c>
+      <c r="N74">
+        <v>-3.21805056</v>
+      </c>
+      <c r="O74">
+        <v>-0.80451264</v>
+      </c>
+      <c r="P74">
+        <v>-2.41353792</v>
+      </c>
+      <c r="Q74">
+        <v>-0.39353792</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1923687835208213</v>
+      </c>
+      <c r="T74">
+        <v>2.804064015524872</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.03002035578517629</v>
+      </c>
+      <c r="W74">
+        <v>0.2459688609615001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.120081423140705</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.23296083927811</v>
+      </c>
+      <c r="C75">
+        <v>-8.210467544224326</v>
+      </c>
+      <c r="D75">
+        <v>3.270832455775674</v>
+      </c>
+      <c r="E75">
+        <v>2.908300000000001</v>
+      </c>
+      <c r="F75">
+        <v>12.1983</v>
+      </c>
+      <c r="G75">
+        <v>0.717</v>
+      </c>
+      <c r="H75">
+        <v>7.42</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.675</v>
+      </c>
+      <c r="K75">
+        <v>2.02</v>
+      </c>
+      <c r="L75">
+        <v>-0.345</v>
+      </c>
+      <c r="M75">
+        <v>2.91295404</v>
+      </c>
+      <c r="N75">
+        <v>-3.25795404</v>
+      </c>
+      <c r="O75">
+        <v>-0.8144885100000001</v>
+      </c>
+      <c r="P75">
+        <v>-2.44346553</v>
+      </c>
+      <c r="Q75">
+        <v>-0.4234655300000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1980565162438147</v>
+      </c>
+      <c r="T75">
+        <v>2.907918238322088</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.02960911803469442</v>
+      </c>
+      <c r="W75">
+        <v>0.245870657386685</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.1184364721387778</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.23496083927811</v>
+      </c>
+      <c r="C76">
+        <v>-8.410916019565406</v>
+      </c>
+      <c r="D76">
+        <v>3.237483980434595</v>
+      </c>
+      <c r="E76">
+        <v>3.075400000000002</v>
+      </c>
+      <c r="F76">
+        <v>12.3654</v>
+      </c>
+      <c r="G76">
+        <v>0.717</v>
+      </c>
+      <c r="H76">
+        <v>7.42</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.675</v>
+      </c>
+      <c r="K76">
+        <v>2.02</v>
+      </c>
+      <c r="L76">
+        <v>-0.345</v>
+      </c>
+      <c r="M76">
+        <v>2.95285752</v>
+      </c>
+      <c r="N76">
+        <v>-3.29785752</v>
+      </c>
+      <c r="O76">
+        <v>-0.82446438</v>
+      </c>
+      <c r="P76">
+        <v>-2.47339314</v>
+      </c>
+      <c r="Q76">
+        <v>-0.4533931399999998</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2041817668685768</v>
+      </c>
+      <c r="T76">
+        <v>3.019761247488323</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.02920899481800937</v>
+      </c>
+      <c r="W76">
+        <v>0.2457751079625407</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.1168359792720375</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2369608392781101</v>
+      </c>
+      <c r="C77">
+        <v>-8.61069133515479</v>
+      </c>
+      <c r="D77">
+        <v>3.204808664845211</v>
+      </c>
+      <c r="E77">
+        <v>3.242500000000001</v>
+      </c>
+      <c r="F77">
+        <v>12.5325</v>
+      </c>
+      <c r="G77">
+        <v>0.717</v>
+      </c>
+      <c r="H77">
+        <v>7.42</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.675</v>
+      </c>
+      <c r="K77">
+        <v>2.02</v>
+      </c>
+      <c r="L77">
+        <v>-0.345</v>
+      </c>
+      <c r="M77">
+        <v>2.992761</v>
+      </c>
+      <c r="N77">
+        <v>-3.337761</v>
+      </c>
+      <c r="O77">
+        <v>-0.8344402500000001</v>
+      </c>
+      <c r="P77">
+        <v>-2.50332075</v>
+      </c>
+      <c r="Q77">
+        <v>-0.4833207500000003</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2107970375433199</v>
+      </c>
+      <c r="T77">
+        <v>3.140551697387856</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.02881954155376924</v>
+      </c>
+      <c r="W77">
+        <v>0.2456821065230401</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.115278166215077</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.23896083927811</v>
+      </c>
+      <c r="C78">
+        <v>-8.809813669557498</v>
+      </c>
+      <c r="D78">
+        <v>3.172786330442503</v>
+      </c>
+      <c r="E78">
+        <v>3.409600000000001</v>
+      </c>
+      <c r="F78">
+        <v>12.6996</v>
+      </c>
+      <c r="G78">
+        <v>0.717</v>
+      </c>
+      <c r="H78">
+        <v>7.42</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.675</v>
+      </c>
+      <c r="K78">
+        <v>2.02</v>
+      </c>
+      <c r="L78">
+        <v>-0.345</v>
+      </c>
+      <c r="M78">
+        <v>3.03266448</v>
+      </c>
+      <c r="N78">
+        <v>-3.37766448</v>
+      </c>
+      <c r="O78">
+        <v>-0.84441612</v>
+      </c>
+      <c r="P78">
+        <v>-2.53324836</v>
+      </c>
+      <c r="Q78">
+        <v>-0.51324836</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2179635807742915</v>
+      </c>
+      <c r="T78">
+        <v>3.27140801811235</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.0284403370596407</v>
+      </c>
+      <c r="W78">
+        <v>0.2455915524898422</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.1137613482385627</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.24096083927811</v>
+      </c>
+      <c r="C79">
+        <v>-9.008302402823269</v>
+      </c>
+      <c r="D79">
+        <v>3.141397597176733</v>
+      </c>
+      <c r="E79">
+        <v>3.576700000000002</v>
+      </c>
+      <c r="F79">
+        <v>12.8667</v>
+      </c>
+      <c r="G79">
+        <v>0.717</v>
+      </c>
+      <c r="H79">
+        <v>7.42</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.675</v>
+      </c>
+      <c r="K79">
+        <v>2.02</v>
+      </c>
+      <c r="L79">
+        <v>-0.345</v>
+      </c>
+      <c r="M79">
+        <v>3.072567960000001</v>
+      </c>
+      <c r="N79">
+        <v>-3.41756796</v>
+      </c>
+      <c r="O79">
+        <v>-0.8543919900000001</v>
+      </c>
+      <c r="P79">
+        <v>-2.563175970000001</v>
+      </c>
+      <c r="Q79">
+        <v>-0.5431759700000005</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2257533016775216</v>
+      </c>
+      <c r="T79">
+        <v>3.413643149334626</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.02807098203289211</v>
+      </c>
+      <c r="W79">
+        <v>0.2455033505094547</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.1122839281315684</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.24296083927811</v>
+      </c>
+      <c r="C80">
+        <v>-9.206176155598623</v>
+      </c>
+      <c r="D80">
+        <v>3.110623844401378</v>
+      </c>
+      <c r="E80">
+        <v>3.743800000000002</v>
+      </c>
+      <c r="F80">
+        <v>13.0338</v>
+      </c>
+      <c r="G80">
+        <v>0.717</v>
+      </c>
+      <c r="H80">
+        <v>7.42</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.675</v>
+      </c>
+      <c r="K80">
+        <v>2.02</v>
+      </c>
+      <c r="L80">
+        <v>-0.345</v>
+      </c>
+      <c r="M80">
+        <v>3.112471440000001</v>
+      </c>
+      <c r="N80">
+        <v>-3.457471440000001</v>
+      </c>
+      <c r="O80">
+        <v>-0.8643678600000002</v>
+      </c>
+      <c r="P80">
+        <v>-2.593103580000001</v>
+      </c>
+      <c r="Q80">
+        <v>-0.5731035800000006</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2342511790264998</v>
+      </c>
+      <c r="T80">
+        <v>3.568808747031654</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.02771109764785503</v>
+      </c>
+      <c r="W80">
+        <v>0.2454174101183078</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.1108443905914203</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.24496083927811</v>
+      </c>
+      <c r="C81">
+        <v>-9.40345282596234</v>
+      </c>
+      <c r="D81">
+        <v>3.080447174037661</v>
+      </c>
+      <c r="E81">
+        <v>3.910900000000002</v>
+      </c>
+      <c r="F81">
+        <v>13.2009</v>
+      </c>
+      <c r="G81">
+        <v>0.717</v>
+      </c>
+      <c r="H81">
+        <v>7.42</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.675</v>
+      </c>
+      <c r="K81">
+        <v>2.02</v>
+      </c>
+      <c r="L81">
+        <v>-0.345</v>
+      </c>
+      <c r="M81">
+        <v>3.15237492</v>
+      </c>
+      <c r="N81">
+        <v>-3.49737492</v>
+      </c>
+      <c r="O81">
+        <v>-0.8743437300000001</v>
+      </c>
+      <c r="P81">
+        <v>-2.62303119</v>
+      </c>
+      <c r="Q81">
+        <v>-0.6030311900000003</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2435583780277618</v>
+      </c>
+      <c r="T81">
+        <v>3.738752020699829</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.02736032425990751</v>
+      </c>
+      <c r="W81">
+        <v>0.2453336454332659</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.1094412970396301</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2469608392781101</v>
+      </c>
+      <c r="C82">
+        <v>-9.600149624137449</v>
+      </c>
+      <c r="D82">
+        <v>3.050850375862552</v>
+      </c>
+      <c r="E82">
+        <v>4.078000000000003</v>
+      </c>
+      <c r="F82">
+        <v>13.368</v>
+      </c>
+      <c r="G82">
+        <v>0.717</v>
+      </c>
+      <c r="H82">
+        <v>7.42</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.675</v>
+      </c>
+      <c r="K82">
+        <v>2.02</v>
+      </c>
+      <c r="L82">
+        <v>-0.345</v>
+      </c>
+      <c r="M82">
+        <v>3.192278400000001</v>
+      </c>
+      <c r="N82">
+        <v>-3.537278400000001</v>
+      </c>
+      <c r="O82">
+        <v>-0.8843196000000002</v>
+      </c>
+      <c r="P82">
+        <v>-2.6529588</v>
+      </c>
+      <c r="Q82">
+        <v>-0.6329588000000004</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2537962969291498</v>
+      </c>
+      <c r="T82">
+        <v>3.925689621734821</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.02701832020665866</v>
+      </c>
+      <c r="W82">
+        <v>0.2452519748653501</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.1080732808266347</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2489608392781101</v>
+      </c>
+      <c r="C83">
+        <v>-9.796283105221194</v>
+      </c>
+      <c r="D83">
+        <v>3.021816894778807</v>
+      </c>
+      <c r="E83">
+        <v>4.245100000000003</v>
+      </c>
+      <c r="F83">
+        <v>13.5351</v>
+      </c>
+      <c r="G83">
+        <v>0.717</v>
+      </c>
+      <c r="H83">
+        <v>7.42</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.675</v>
+      </c>
+      <c r="K83">
+        <v>2.02</v>
+      </c>
+      <c r="L83">
+        <v>-0.345</v>
+      </c>
+      <c r="M83">
+        <v>3.232181880000001</v>
+      </c>
+      <c r="N83">
+        <v>-3.57718188</v>
+      </c>
+      <c r="O83">
+        <v>-0.8942954700000001</v>
+      </c>
+      <c r="P83">
+        <v>-2.68288641</v>
+      </c>
+      <c r="Q83">
+        <v>-0.66288641</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2651118915043683</v>
+      </c>
+      <c r="T83">
+        <v>4.132304864984023</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.02668476069793448</v>
+      </c>
+      <c r="W83">
+        <v>0.2451723208546668</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.1067390427917378</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2509608392781101</v>
+      </c>
+      <c r="C84">
+        <v>-9.991869200063775</v>
+      </c>
+      <c r="D84">
+        <v>2.993330799936227</v>
+      </c>
+      <c r="E84">
+        <v>4.412200000000002</v>
+      </c>
+      <c r="F84">
+        <v>13.7022</v>
+      </c>
+      <c r="G84">
+        <v>0.717</v>
+      </c>
+      <c r="H84">
+        <v>7.42</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.675</v>
+      </c>
+      <c r="K84">
+        <v>2.02</v>
+      </c>
+      <c r="L84">
+        <v>-0.345</v>
+      </c>
+      <c r="M84">
+        <v>3.272085360000001</v>
+      </c>
+      <c r="N84">
+        <v>-3.617085360000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.9042713400000002</v>
+      </c>
+      <c r="P84">
+        <v>-2.712814020000001</v>
+      </c>
+      <c r="Q84">
+        <v>-0.6928140200000006</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2776847743657221</v>
+      </c>
+      <c r="T84">
+        <v>4.361877357483134</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.02635933678698406</v>
+      </c>
+      <c r="W84">
+        <v>0.2450946096247318</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.1054373471479364</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.25296083927811</v>
+      </c>
+      <c r="C85">
+        <v>-10.18692324441685</v>
+      </c>
+      <c r="D85">
+        <v>2.965376755583152</v>
+      </c>
+      <c r="E85">
+        <v>4.579300000000003</v>
+      </c>
+      <c r="F85">
+        <v>13.8693</v>
+      </c>
+      <c r="G85">
+        <v>0.717</v>
+      </c>
+      <c r="H85">
+        <v>7.42</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.675</v>
+      </c>
+      <c r="K85">
+        <v>2.02</v>
+      </c>
+      <c r="L85">
+        <v>-0.345</v>
+      </c>
+      <c r="M85">
+        <v>3.311988840000001</v>
+      </c>
+      <c r="N85">
+        <v>-3.65698884</v>
+      </c>
+      <c r="O85">
+        <v>-0.9142472100000001</v>
+      </c>
+      <c r="P85">
+        <v>-2.74274163</v>
+      </c>
+      <c r="Q85">
+        <v>-0.7227416300000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2917368199166469</v>
+      </c>
+      <c r="T85">
+        <v>4.618458378511554</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.02604175441605654</v>
+      </c>
+      <c r="W85">
+        <v>0.2450187709545543</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.1041670176642262</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.25496083927811</v>
+      </c>
+      <c r="C86">
+        <v>-10.38146000646391</v>
+      </c>
+      <c r="D86">
+        <v>2.93793999353609</v>
+      </c>
+      <c r="E86">
+        <v>4.746400000000001</v>
+      </c>
+      <c r="F86">
+        <v>14.0364</v>
+      </c>
+      <c r="G86">
+        <v>0.717</v>
+      </c>
+      <c r="H86">
+        <v>7.42</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.675</v>
+      </c>
+      <c r="K86">
+        <v>2.02</v>
+      </c>
+      <c r="L86">
+        <v>-0.345</v>
+      </c>
+      <c r="M86">
+        <v>3.35189232</v>
+      </c>
+      <c r="N86">
+        <v>-3.69689232</v>
+      </c>
+      <c r="O86">
+        <v>-0.92422308</v>
+      </c>
+      <c r="P86">
+        <v>-2.77266924</v>
+      </c>
+      <c r="Q86">
+        <v>-0.7526692399999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3075453711614372</v>
+      </c>
+      <c r="T86">
+        <v>4.907112027168523</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.02573173353015111</v>
+      </c>
+      <c r="W86">
+        <v>0.2449447379670001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.1029269341206043</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.25696083927811</v>
+      </c>
+      <c r="C87">
+        <v>-10.57549371283631</v>
+      </c>
+      <c r="D87">
+        <v>2.911006287163693</v>
+      </c>
+      <c r="E87">
+        <v>4.913500000000001</v>
+      </c>
+      <c r="F87">
+        <v>14.2035</v>
+      </c>
+      <c r="G87">
+        <v>0.717</v>
+      </c>
+      <c r="H87">
+        <v>7.42</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.675</v>
+      </c>
+      <c r="K87">
+        <v>2.02</v>
+      </c>
+      <c r="L87">
+        <v>-0.345</v>
+      </c>
+      <c r="M87">
+        <v>3.3917958</v>
+      </c>
+      <c r="N87">
+        <v>-3.7367958</v>
+      </c>
+      <c r="O87">
+        <v>-0.9341989500000001</v>
+      </c>
+      <c r="P87">
+        <v>-2.80259685</v>
+      </c>
+      <c r="Q87">
+        <v>-0.7825968500000005</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3254617292388664</v>
+      </c>
+      <c r="T87">
+        <v>5.234252828979759</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.0254290072533258</v>
+      </c>
+      <c r="W87">
+        <v>0.2448724469320942</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.1017160290133032</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.25896083927811</v>
+      </c>
+      <c r="C88">
+        <v>-10.76903807321128</v>
+      </c>
+      <c r="D88">
+        <v>2.884561926788718</v>
+      </c>
+      <c r="E88">
+        <v>5.080600000000002</v>
+      </c>
+      <c r="F88">
+        <v>14.3706</v>
+      </c>
+      <c r="G88">
+        <v>0.717</v>
+      </c>
+      <c r="H88">
+        <v>7.42</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.675</v>
+      </c>
+      <c r="K88">
+        <v>2.02</v>
+      </c>
+      <c r="L88">
+        <v>-0.345</v>
+      </c>
+      <c r="M88">
+        <v>3.431699280000001</v>
+      </c>
+      <c r="N88">
+        <v>-3.776699280000001</v>
+      </c>
+      <c r="O88">
+        <v>-0.9441748200000002</v>
+      </c>
+      <c r="P88">
+        <v>-2.832524460000001</v>
+      </c>
+      <c r="Q88">
+        <v>-0.8125244600000006</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3459375670416426</v>
+      </c>
+      <c r="T88">
+        <v>5.608128031049742</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.02513332112247317</v>
+      </c>
+      <c r="W88">
+        <v>0.2448018370840466</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.1005332844898927</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.26096083927811</v>
+      </c>
+      <c r="C89">
+        <v>-10.96210630358133</v>
+      </c>
+      <c r="D89">
+        <v>2.85859369641867</v>
+      </c>
+      <c r="E89">
+        <v>5.247700000000002</v>
+      </c>
+      <c r="F89">
+        <v>14.5377</v>
+      </c>
+      <c r="G89">
+        <v>0.717</v>
+      </c>
+      <c r="H89">
+        <v>7.42</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.675</v>
+      </c>
+      <c r="K89">
+        <v>2.02</v>
+      </c>
+      <c r="L89">
+        <v>-0.345</v>
+      </c>
+      <c r="M89">
+        <v>3.471602760000001</v>
+      </c>
+      <c r="N89">
+        <v>-3.81660276</v>
+      </c>
+      <c r="O89">
+        <v>-0.9541506900000001</v>
+      </c>
+      <c r="P89">
+        <v>-2.86245207</v>
+      </c>
+      <c r="Q89">
+        <v>-0.8424520700000002</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3695635337371535</v>
+      </c>
+      <c r="T89">
+        <v>6.039522494976645</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.024844432373939</v>
+      </c>
+      <c r="W89">
+        <v>0.2447328504508966</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.09937772949575585</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2629608392781101</v>
+      </c>
+      <c r="C90">
+        <v>-11.15471114827788</v>
+      </c>
+      <c r="D90">
+        <v>2.833088851722116</v>
+      </c>
+      <c r="E90">
+        <v>5.414800000000001</v>
+      </c>
+      <c r="F90">
+        <v>14.7048</v>
+      </c>
+      <c r="G90">
+        <v>0.717</v>
+      </c>
+      <c r="H90">
+        <v>7.42</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.675</v>
+      </c>
+      <c r="K90">
+        <v>2.02</v>
+      </c>
+      <c r="L90">
+        <v>-0.345</v>
+      </c>
+      <c r="M90">
+        <v>3.51150624</v>
+      </c>
+      <c r="N90">
+        <v>-3.85650624</v>
+      </c>
+      <c r="O90">
+        <v>-0.96412656</v>
+      </c>
+      <c r="P90">
+        <v>-2.89237968</v>
+      </c>
+      <c r="Q90">
+        <v>-0.8723796799999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.397127161548583</v>
+      </c>
+      <c r="T90">
+        <v>6.5428160362247</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.0245621092787806</v>
+      </c>
+      <c r="W90">
+        <v>0.2446654316957728</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.09824843711512243</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.26496083927811</v>
+      </c>
+      <c r="C91">
+        <v>-11.34686490082643</v>
+      </c>
+      <c r="D91">
+        <v>2.808035099173574</v>
+      </c>
+      <c r="E91">
+        <v>5.581900000000001</v>
+      </c>
+      <c r="F91">
+        <v>14.8719</v>
+      </c>
+      <c r="G91">
+        <v>0.717</v>
+      </c>
+      <c r="H91">
+        <v>7.42</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.675</v>
+      </c>
+      <c r="K91">
+        <v>2.02</v>
+      </c>
+      <c r="L91">
+        <v>-0.345</v>
+      </c>
+      <c r="M91">
+        <v>3.55140972</v>
+      </c>
+      <c r="N91">
+        <v>-3.89640972</v>
+      </c>
+      <c r="O91">
+        <v>-0.9741024300000001</v>
+      </c>
+      <c r="P91">
+        <v>-2.92230729</v>
+      </c>
+      <c r="Q91">
+        <v>-0.90230729</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4297023580529997</v>
+      </c>
+      <c r="T91">
+        <v>7.13761749406331</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.02428613052283925</v>
+      </c>
+      <c r="W91">
+        <v>0.244599527968854</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.09714452209135715</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2669608392781101</v>
+      </c>
+      <c r="C92">
+        <v>-11.53857942370474</v>
+      </c>
+      <c r="D92">
+        <v>2.783420576295256</v>
+      </c>
+      <c r="E92">
+        <v>5.749000000000002</v>
+      </c>
+      <c r="F92">
+        <v>15.039</v>
+      </c>
+      <c r="G92">
+        <v>0.717</v>
+      </c>
+      <c r="H92">
+        <v>7.42</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.675</v>
+      </c>
+      <c r="K92">
+        <v>2.02</v>
+      </c>
+      <c r="L92">
+        <v>-0.345</v>
+      </c>
+      <c r="M92">
+        <v>3.591313200000001</v>
+      </c>
+      <c r="N92">
+        <v>-3.936313200000001</v>
+      </c>
+      <c r="O92">
+        <v>-0.9840783000000002</v>
+      </c>
+      <c r="P92">
+        <v>-2.952234900000001</v>
+      </c>
+      <c r="Q92">
+        <v>-0.9322349000000005</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4687925938582997</v>
+      </c>
+      <c r="T92">
+        <v>7.851379243469641</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.02401628462814103</v>
+      </c>
+      <c r="W92">
+        <v>0.2445350887692001</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.09606513851256415</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.26896083927811</v>
+      </c>
+      <c r="C93">
+        <v>-11.72986616707104</v>
+      </c>
+      <c r="D93">
+        <v>2.759233832928964</v>
+      </c>
+      <c r="E93">
+        <v>5.916100000000002</v>
+      </c>
+      <c r="F93">
+        <v>15.2061</v>
+      </c>
+      <c r="G93">
+        <v>0.717</v>
+      </c>
+      <c r="H93">
+        <v>7.42</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.675</v>
+      </c>
+      <c r="K93">
+        <v>2.02</v>
+      </c>
+      <c r="L93">
+        <v>-0.345</v>
+      </c>
+      <c r="M93">
+        <v>3.631216680000001</v>
+      </c>
+      <c r="N93">
+        <v>-3.97621668</v>
+      </c>
+      <c r="O93">
+        <v>-0.9940541700000001</v>
+      </c>
+      <c r="P93">
+        <v>-2.98216251</v>
+      </c>
+      <c r="Q93">
+        <v>-0.9621625100000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5165695487314441</v>
+      </c>
+      <c r="T93">
+        <v>8.723754714966267</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.02375236941244718</v>
+      </c>
+      <c r="W93">
+        <v>0.2444720658156924</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.09500947764978873</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.27096083927811</v>
+      </c>
+      <c r="C94">
+        <v>-11.920736186524</v>
+      </c>
+      <c r="D94">
+        <v>2.735463813475995</v>
+      </c>
+      <c r="E94">
+        <v>6.083200000000001</v>
+      </c>
+      <c r="F94">
+        <v>15.3732</v>
+      </c>
+      <c r="G94">
+        <v>0.717</v>
+      </c>
+      <c r="H94">
+        <v>7.42</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.675</v>
+      </c>
+      <c r="K94">
+        <v>2.02</v>
+      </c>
+      <c r="L94">
+        <v>-0.345</v>
+      </c>
+      <c r="M94">
+        <v>3.671120160000001</v>
+      </c>
+      <c r="N94">
+        <v>-4.016120160000001</v>
+      </c>
+      <c r="O94">
+        <v>-1.00403004</v>
+      </c>
+      <c r="P94">
+        <v>-3.012090120000001</v>
+      </c>
+      <c r="Q94">
+        <v>-0.9920901200000007</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5762907423228749</v>
+      </c>
+      <c r="T94">
+        <v>9.814224054337055</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.02349419148405101</v>
+      </c>
+      <c r="W94">
+        <v>0.2444104129263914</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.09397676593620408</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.27296083927811</v>
+      </c>
+      <c r="C95">
+        <v>-12.11120015995277</v>
+      </c>
+      <c r="D95">
+        <v>2.712099840047227</v>
+      </c>
+      <c r="E95">
+        <v>6.250300000000003</v>
+      </c>
+      <c r="F95">
+        <v>15.5403</v>
+      </c>
+      <c r="G95">
+        <v>0.717</v>
+      </c>
+      <c r="H95">
+        <v>7.42</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.675</v>
+      </c>
+      <c r="K95">
+        <v>2.02</v>
+      </c>
+      <c r="L95">
+        <v>-0.345</v>
+      </c>
+      <c r="M95">
+        <v>3.711023640000001</v>
+      </c>
+      <c r="N95">
+        <v>-4.05602364</v>
+      </c>
+      <c r="O95">
+        <v>-1.01400591</v>
+      </c>
+      <c r="P95">
+        <v>-3.04201773</v>
+      </c>
+      <c r="Q95">
+        <v>-1.02201773</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6530751340832854</v>
+      </c>
+      <c r="T95">
+        <v>11.21625606209949</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.02324156576916874</v>
+      </c>
+      <c r="W95">
+        <v>0.2443500859056775</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.09296626307667499</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.27496083927811</v>
+      </c>
+      <c r="C96">
+        <v>-12.30126840353065</v>
+      </c>
+      <c r="D96">
+        <v>2.689131596469353</v>
+      </c>
+      <c r="E96">
+        <v>6.417400000000002</v>
+      </c>
+      <c r="F96">
+        <v>15.7074</v>
+      </c>
+      <c r="G96">
+        <v>0.717</v>
+      </c>
+      <c r="H96">
+        <v>7.42</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.675</v>
+      </c>
+      <c r="K96">
+        <v>2.02</v>
+      </c>
+      <c r="L96">
+        <v>-0.345</v>
+      </c>
+      <c r="M96">
+        <v>3.750927120000001</v>
+      </c>
+      <c r="N96">
+        <v>-4.095927120000001</v>
+      </c>
+      <c r="O96">
+        <v>-1.02398178</v>
+      </c>
+      <c r="P96">
+        <v>-3.071945340000001</v>
+      </c>
+      <c r="Q96">
+        <v>-1.051945340000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7554543230971666</v>
+      </c>
+      <c r="T96">
+        <v>13.08563207244941</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.02299431506949673</v>
+      </c>
+      <c r="W96">
+        <v>0.2442910424385958</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.09197726027798692</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.27696083927811</v>
+      </c>
+      <c r="C97">
+        <v>-12.49095088690298</v>
+      </c>
+      <c r="D97">
+        <v>2.666549113097022</v>
+      </c>
+      <c r="E97">
+        <v>6.584500000000002</v>
+      </c>
+      <c r="F97">
+        <v>15.8745</v>
+      </c>
+      <c r="G97">
+        <v>0.717</v>
+      </c>
+      <c r="H97">
+        <v>7.42</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.675</v>
+      </c>
+      <c r="K97">
+        <v>2.02</v>
+      </c>
+      <c r="L97">
+        <v>-0.345</v>
+      </c>
+      <c r="M97">
+        <v>3.7908306</v>
+      </c>
+      <c r="N97">
+        <v>-4.1358306</v>
+      </c>
+      <c r="O97">
+        <v>-1.03395765</v>
+      </c>
+      <c r="P97">
+        <v>-3.10187295</v>
+      </c>
+      <c r="Q97">
+        <v>-1.08187295</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8987851877166002</v>
+      </c>
+      <c r="T97">
+        <v>15.7027584869393</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.02275226964771256</v>
+      </c>
+      <c r="W97">
+        <v>0.2442332419918738</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.09100907859085017</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.27896083927811</v>
+      </c>
+      <c r="C98">
+        <v>-12.68025724761618</v>
+      </c>
+      <c r="D98">
+        <v>2.644342752383824</v>
+      </c>
+      <c r="E98">
+        <v>6.7516</v>
+      </c>
+      <c r="F98">
+        <v>16.0416</v>
+      </c>
+      <c r="G98">
+        <v>0.717</v>
+      </c>
+      <c r="H98">
+        <v>7.42</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.675</v>
+      </c>
+      <c r="K98">
+        <v>2.02</v>
+      </c>
+      <c r="L98">
+        <v>-0.345</v>
+      </c>
+      <c r="M98">
+        <v>3.83073408</v>
+      </c>
+      <c r="N98">
+        <v>-4.17573408</v>
+      </c>
+      <c r="O98">
+        <v>-1.04393352</v>
+      </c>
+      <c r="P98">
+        <v>-3.13180056</v>
+      </c>
+      <c r="Q98">
+        <v>-1.11180056</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.113781484645748</v>
+      </c>
+      <c r="T98">
+        <v>19.62844810867408</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.02251526683888222</v>
+      </c>
+      <c r="W98">
+        <v>0.2441766457211251</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.09006106735552888</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2809608392781101</v>
+      </c>
+      <c r="C99">
+        <v>-12.86919680483168</v>
+      </c>
+      <c r="D99">
+        <v>2.622503195168325</v>
+      </c>
+      <c r="E99">
+        <v>6.918700000000001</v>
+      </c>
+      <c r="F99">
+        <v>16.2087</v>
+      </c>
+      <c r="G99">
+        <v>0.717</v>
+      </c>
+      <c r="H99">
+        <v>7.42</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.675</v>
+      </c>
+      <c r="K99">
+        <v>2.02</v>
+      </c>
+      <c r="L99">
+        <v>-0.345</v>
+      </c>
+      <c r="M99">
+        <v>3.87063756</v>
+      </c>
+      <c r="N99">
+        <v>-4.21563756</v>
+      </c>
+      <c r="O99">
+        <v>-1.05390939</v>
+      </c>
+      <c r="P99">
+        <v>-3.16172817</v>
+      </c>
+      <c r="Q99">
+        <v>-1.14172817</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.472108646194331</v>
+      </c>
+      <c r="T99">
+        <v>26.17126414489878</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.02228315068590405</v>
+      </c>
+      <c r="W99">
+        <v>0.2441212163837939</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.08913260274361612</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2829608392781101</v>
+      </c>
+      <c r="C100">
+        <v>-13.05777857236592</v>
+      </c>
+      <c r="D100">
+        <v>2.601021427634086</v>
+      </c>
+      <c r="E100">
+        <v>7.085800000000003</v>
+      </c>
+      <c r="F100">
+        <v>16.3758</v>
+      </c>
+      <c r="G100">
+        <v>0.717</v>
+      </c>
+      <c r="H100">
+        <v>7.42</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.675</v>
+      </c>
+      <c r="K100">
+        <v>2.02</v>
+      </c>
+      <c r="L100">
+        <v>-0.345</v>
+      </c>
+      <c r="M100">
+        <v>3.91054104</v>
+      </c>
+      <c r="N100">
+        <v>-4.255541040000001</v>
+      </c>
+      <c r="O100">
+        <v>-1.06388526</v>
+      </c>
+      <c r="P100">
+        <v>-3.19165578</v>
+      </c>
+      <c r="Q100">
+        <v>-1.17165578</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.188762969291496</v>
+      </c>
+      <c r="T100">
+        <v>39.25689621734816</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.02205577159727238</v>
+      </c>
+      <c r="W100">
+        <v>0.2440669182574287</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.0882230863890896</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2849608392781101</v>
+      </c>
+      <c r="C101">
+        <v>-13.24601127109461</v>
+      </c>
+      <c r="D101">
+        <v>2.579888728905387</v>
+      </c>
+      <c r="E101">
+        <v>7.2529</v>
+      </c>
+      <c r="F101">
+        <v>16.5429</v>
+      </c>
+      <c r="G101">
+        <v>0.717</v>
+      </c>
+      <c r="H101">
+        <v>7.42</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.675</v>
+      </c>
+      <c r="K101">
+        <v>2.02</v>
+      </c>
+      <c r="L101">
+        <v>-0.345</v>
+      </c>
+      <c r="M101">
+        <v>3.95044452</v>
+      </c>
+      <c r="N101">
+        <v>-4.29544452</v>
+      </c>
+      <c r="O101">
+        <v>-1.07386113</v>
+      </c>
+      <c r="P101">
+        <v>-3.22158339</v>
+      </c>
+      <c r="Q101">
+        <v>-1.20158339</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.338725938582993</v>
+      </c>
+      <c r="T101">
+        <v>78.51379243469633</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.02183298602558276</v>
+      </c>
+      <c r="W101">
+        <v>0.2440137170629092</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.08733194410233103</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_office_equipment_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,13 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.09896752353295653</v>
+      </c>
+      <c r="C2">
+        <v>12.51792619317907</v>
+      </c>
+      <c r="D2">
+        <v>12.12882619317907</v>
       </c>
       <c r="E2">
-        <v>-7.91</v>
+        <v>-7.7461</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1639</v>
       </c>
       <c r="G2">
         <v>0.553</v>
@@ -1436,43 +1445,45 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03864762000000001</v>
       </c>
       <c r="N2">
-        <v>-0.6650000000000003</v>
+        <v>-0.7036476200000003</v>
       </c>
       <c r="O2">
-        <v>-0.1662500000000001</v>
+        <v>-0.1759119050000001</v>
       </c>
       <c r="P2">
-        <v>-0.4987500000000002</v>
+        <v>-0.5277357150000002</v>
       </c>
       <c r="Q2">
-        <v>1.74125</v>
+        <v>1.712264285</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.08733953881124593</v>
+      </c>
+      <c r="T2">
+        <v>0.8096829289341135</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-4.301687917651851</v>
+      </c>
+      <c r="W2">
+        <v>1.250138010982306</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-17.2067516706074</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1480,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09896752353295653</v>
+        <v>0.1008675235329565</v>
       </c>
       <c r="C3">
-        <v>12.51792619317907</v>
+        <v>12.06822812369064</v>
       </c>
       <c r="D3">
-        <v>12.12882619317907</v>
+        <v>11.84302812369064</v>
       </c>
       <c r="E3">
-        <v>-7.7461</v>
+        <v>-7.5822</v>
       </c>
       <c r="F3">
-        <v>0.1639</v>
+        <v>0.3278</v>
       </c>
       <c r="G3">
         <v>0.553</v>
@@ -1516,37 +1527,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M3">
-        <v>0.03864762000000001</v>
+        <v>0.07729524000000002</v>
       </c>
       <c r="N3">
-        <v>-0.7036476200000003</v>
+        <v>-0.7422952400000002</v>
       </c>
       <c r="O3">
-        <v>-0.1759119050000001</v>
+        <v>-0.1855738100000001</v>
       </c>
       <c r="P3">
-        <v>-0.5277357150000002</v>
+        <v>-0.5567214300000002</v>
       </c>
       <c r="Q3">
-        <v>1.712264285</v>
+        <v>1.68327857</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08733953881124593</v>
+        <v>0.08776341165625864</v>
       </c>
       <c r="T3">
-        <v>0.8096829289341135</v>
+        <v>0.8179449996375229</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-4.301687917651851</v>
+        <v>-2.150843958825925</v>
       </c>
       <c r="W3">
-        <v>1.250138010982306</v>
+        <v>0.7429690054911532</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1554,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-17.2067516706074</v>
+        <v>-8.603375835303702</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1562,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1008675235329565</v>
+        <v>0.1027675235329565</v>
       </c>
       <c r="C4">
-        <v>12.06822812369064</v>
+        <v>11.63168881515947</v>
       </c>
       <c r="D4">
-        <v>11.84302812369064</v>
+        <v>11.57038881515947</v>
       </c>
       <c r="E4">
-        <v>-7.5822</v>
+        <v>-7.4183</v>
       </c>
       <c r="F4">
-        <v>0.3278</v>
+        <v>0.4917</v>
       </c>
       <c r="G4">
         <v>0.553</v>
@@ -1598,37 +1609,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M4">
-        <v>0.07729524000000002</v>
+        <v>0.11594286</v>
       </c>
       <c r="N4">
-        <v>-0.7422952400000002</v>
+        <v>-0.7809428600000002</v>
       </c>
       <c r="O4">
-        <v>-0.1855738100000001</v>
+        <v>-0.1952357150000001</v>
       </c>
       <c r="P4">
-        <v>-0.5567214300000002</v>
+        <v>-0.5857071450000002</v>
       </c>
       <c r="Q4">
-        <v>1.68327857</v>
+        <v>1.654292855</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08776341165625864</v>
+        <v>0.08819602414756028</v>
       </c>
       <c r="T4">
-        <v>0.8179449996375229</v>
+        <v>0.8263774223141984</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-2.150843958825925</v>
+        <v>-1.433895972550617</v>
       </c>
       <c r="W4">
-        <v>0.7429690054911532</v>
+        <v>0.5739126703274356</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1636,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-8.603375835303702</v>
+        <v>-5.735583890202468</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1644,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1027675235329565</v>
+        <v>0.1046675235329565</v>
       </c>
       <c r="C5">
-        <v>11.63168881515947</v>
+        <v>11.20741993134443</v>
       </c>
       <c r="D5">
-        <v>11.57038881515947</v>
+        <v>11.31001993134442</v>
       </c>
       <c r="E5">
-        <v>-7.4183</v>
+        <v>-7.2544</v>
       </c>
       <c r="F5">
-        <v>0.4917</v>
+        <v>0.6556000000000001</v>
       </c>
       <c r="G5">
         <v>0.553</v>
@@ -1680,37 +1691,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M5">
-        <v>0.11594286</v>
+        <v>0.15459048</v>
       </c>
       <c r="N5">
-        <v>-0.7809428600000002</v>
+        <v>-0.8195904800000002</v>
       </c>
       <c r="O5">
-        <v>-0.1952357150000001</v>
+        <v>-0.2048976200000001</v>
       </c>
       <c r="P5">
-        <v>-0.5857071450000002</v>
+        <v>-0.6146928600000001</v>
       </c>
       <c r="Q5">
-        <v>1.654292855</v>
+        <v>1.62530714</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08819602414756028</v>
+        <v>0.08863764939909737</v>
       </c>
       <c r="T5">
-        <v>0.8263774223141984</v>
+        <v>0.8349855204633047</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-1.433895972550617</v>
+        <v>-1.075421979412963</v>
       </c>
       <c r="W5">
-        <v>0.5739126703274356</v>
+        <v>0.4893845027455766</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1718,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-5.735583890202468</v>
+        <v>-4.301687917651851</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1726,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1046675235329565</v>
+        <v>0.1065675235329565</v>
       </c>
       <c r="C6">
-        <v>11.20741993134443</v>
+        <v>10.79461133729002</v>
       </c>
       <c r="D6">
-        <v>11.31001993134442</v>
+        <v>11.06111133729002</v>
       </c>
       <c r="E6">
-        <v>-7.2544</v>
+        <v>-7.0905</v>
       </c>
       <c r="F6">
-        <v>0.6556000000000001</v>
+        <v>0.8195000000000001</v>
       </c>
       <c r="G6">
         <v>0.553</v>
@@ -1762,37 +1773,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M6">
-        <v>0.15459048</v>
+        <v>0.1932381</v>
       </c>
       <c r="N6">
-        <v>-0.8195904800000002</v>
+        <v>-0.8582381000000003</v>
       </c>
       <c r="O6">
-        <v>-0.2048976200000001</v>
+        <v>-0.2145595250000001</v>
       </c>
       <c r="P6">
-        <v>-0.6146928600000001</v>
+        <v>-0.6436785750000003</v>
       </c>
       <c r="Q6">
-        <v>1.62530714</v>
+        <v>1.596321425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08863764939909737</v>
+        <v>0.08908857202435103</v>
       </c>
       <c r="T6">
-        <v>0.8349855204633047</v>
+        <v>0.8437748417313395</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-1.075421979412963</v>
+        <v>-0.8603375835303703</v>
       </c>
       <c r="W6">
-        <v>0.4893845027455766</v>
+        <v>0.4386676021964613</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1800,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-4.301687917651851</v>
+        <v>-3.441350334121482</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1808,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1065675235329565</v>
+        <v>0.1084675235329565</v>
       </c>
       <c r="C7">
-        <v>10.79461133729002</v>
+        <v>10.39252267944043</v>
       </c>
       <c r="D7">
-        <v>11.06111133729002</v>
+        <v>10.82292267944043</v>
       </c>
       <c r="E7">
-        <v>-7.0905</v>
+        <v>-6.9266</v>
       </c>
       <c r="F7">
-        <v>0.8195000000000001</v>
+        <v>0.9834000000000002</v>
       </c>
       <c r="G7">
         <v>0.553</v>
@@ -1844,37 +1855,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M7">
-        <v>0.1932381</v>
+        <v>0.23188572</v>
       </c>
       <c r="N7">
-        <v>-0.8582381000000003</v>
+        <v>-0.8968857200000003</v>
       </c>
       <c r="O7">
-        <v>-0.2145595250000001</v>
+        <v>-0.2242214300000001</v>
       </c>
       <c r="P7">
-        <v>-0.6436785750000003</v>
+        <v>-0.6726642900000003</v>
       </c>
       <c r="Q7">
-        <v>1.596321425</v>
+        <v>1.56733571</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08908857202435103</v>
+        <v>0.08954908874801433</v>
       </c>
       <c r="T7">
-        <v>0.8437748417313395</v>
+        <v>0.8527511698348643</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-0.8603375835303703</v>
+        <v>-0.7169479862753085</v>
       </c>
       <c r="W7">
-        <v>0.4386676021964613</v>
+        <v>0.4048563351637178</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1882,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-3.441350334121482</v>
+        <v>-2.867791945101234</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1890,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1084675235329565</v>
+        <v>0.1103675235329565</v>
       </c>
       <c r="C8">
-        <v>10.39252267944043</v>
+        <v>10.00047603069806</v>
       </c>
       <c r="D8">
-        <v>10.82292267944043</v>
+        <v>10.59477603069806</v>
       </c>
       <c r="E8">
-        <v>-6.926600000000001</v>
+        <v>-6.762700000000001</v>
       </c>
       <c r="F8">
-        <v>0.9834000000000001</v>
+        <v>1.1473</v>
       </c>
       <c r="G8">
         <v>0.553</v>
@@ -1926,37 +1937,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M8">
-        <v>0.23188572</v>
+        <v>0.27053334</v>
       </c>
       <c r="N8">
-        <v>-0.8968857200000002</v>
+        <v>-0.9355333400000003</v>
       </c>
       <c r="O8">
-        <v>-0.2242214300000001</v>
+        <v>-0.2338833350000001</v>
       </c>
       <c r="P8">
-        <v>-0.6726642900000002</v>
+        <v>-0.7016500050000003</v>
       </c>
       <c r="Q8">
-        <v>1.56733571</v>
+        <v>1.538349995</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08954908874801433</v>
+        <v>0.09001950905713277</v>
       </c>
       <c r="T8">
-        <v>0.8527511698348643</v>
+        <v>0.8619205372524434</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-0.7169479862753086</v>
+        <v>-0.614526845378836</v>
       </c>
       <c r="W8">
-        <v>0.4048563351637178</v>
+        <v>0.3807054301403295</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1964,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-2.867791945101234</v>
+        <v>-2.458107381515344</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1972,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1103675235329565</v>
+        <v>0.1122675235329565</v>
       </c>
       <c r="C9">
-        <v>10.00047603069806</v>
+        <v>9.617849446528012</v>
       </c>
       <c r="D9">
-        <v>10.59477603069806</v>
+        <v>10.37604944652801</v>
       </c>
       <c r="E9">
-        <v>-6.7627</v>
+        <v>-6.5988</v>
       </c>
       <c r="F9">
-        <v>1.1473</v>
+        <v>1.3112</v>
       </c>
       <c r="G9">
         <v>0.553</v>
@@ -2008,37 +2019,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M9">
-        <v>0.2705333400000001</v>
+        <v>0.3091809600000001</v>
       </c>
       <c r="N9">
-        <v>-0.9355333400000003</v>
+        <v>-0.9741809600000003</v>
       </c>
       <c r="O9">
-        <v>-0.2338833350000001</v>
+        <v>-0.2435452400000001</v>
       </c>
       <c r="P9">
-        <v>-0.7016500050000003</v>
+        <v>-0.7306357200000002</v>
       </c>
       <c r="Q9">
-        <v>1.538349995</v>
+        <v>1.50936428</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09001950905713277</v>
+        <v>0.09050015589471029</v>
       </c>
       <c r="T9">
-        <v>0.8619205372524436</v>
+        <v>0.8712892387443179</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.6145268453788358</v>
+        <v>-0.5377109897064813</v>
       </c>
       <c r="W9">
-        <v>0.3807054301403295</v>
+        <v>0.3625922513727883</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2046,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-2.458107381515343</v>
+        <v>-2.150843958825925</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2054,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1122675235329565</v>
+        <v>0.1141675235329565</v>
       </c>
       <c r="C10">
-        <v>9.617849446528012</v>
+        <v>9.244071303113309</v>
       </c>
       <c r="D10">
-        <v>10.37604944652801</v>
+        <v>10.16617130311331</v>
       </c>
       <c r="E10">
-        <v>-6.5988</v>
+        <v>-6.4349</v>
       </c>
       <c r="F10">
-        <v>1.3112</v>
+        <v>1.4751</v>
       </c>
       <c r="G10">
         <v>0.553</v>
@@ -2090,37 +2101,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M10">
-        <v>0.3091809600000001</v>
+        <v>0.3478285800000001</v>
       </c>
       <c r="N10">
-        <v>-0.9741809600000003</v>
+        <v>-1.01282858</v>
       </c>
       <c r="O10">
-        <v>-0.2435452400000001</v>
+        <v>-0.2532071450000001</v>
       </c>
       <c r="P10">
-        <v>-0.7306357200000002</v>
+        <v>-0.7596214350000002</v>
       </c>
       <c r="Q10">
-        <v>1.50936428</v>
+        <v>1.480378565</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09050015589471029</v>
+        <v>0.09099136639904777</v>
       </c>
       <c r="T10">
-        <v>0.8712892387443179</v>
+        <v>0.8808638457634862</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.5377109897064813</v>
+        <v>-0.477965324183539</v>
       </c>
       <c r="W10">
-        <v>0.3625922513727883</v>
+        <v>0.3485042234424786</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2128,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-2.150843958825925</v>
+        <v>-1.911861296734156</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2136,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1141675235329565</v>
+        <v>0.1160675235329565</v>
       </c>
       <c r="C11">
-        <v>9.244071303113309</v>
+        <v>8.878615309025426</v>
       </c>
       <c r="D11">
-        <v>10.16617130311331</v>
+        <v>9.964615309025424</v>
       </c>
       <c r="E11">
-        <v>-6.4349</v>
+        <v>-6.271</v>
       </c>
       <c r="F11">
-        <v>1.4751</v>
+        <v>1.639</v>
       </c>
       <c r="G11">
         <v>0.553</v>
@@ -2172,37 +2183,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M11">
-        <v>0.3478285800000001</v>
+        <v>0.3864762</v>
       </c>
       <c r="N11">
-        <v>-1.01282858</v>
+        <v>-1.0514762</v>
       </c>
       <c r="O11">
-        <v>-0.2532071450000001</v>
+        <v>-0.26286905</v>
       </c>
       <c r="P11">
-        <v>-0.7596214350000002</v>
+        <v>-0.7886071500000001</v>
       </c>
       <c r="Q11">
-        <v>1.480378565</v>
+        <v>1.45139285</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09099136639904777</v>
+        <v>0.09149349269237052</v>
       </c>
       <c r="T11">
-        <v>0.8808638457634862</v>
+        <v>0.8906512218275249</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.477965324183539</v>
+        <v>-0.4301687917651852</v>
       </c>
       <c r="W11">
-        <v>0.3485042234424786</v>
+        <v>0.3372338010982306</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2210,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-1.911861296734156</v>
+        <v>-1.720675167060741</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2218,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1160675235329565</v>
+        <v>0.1179675235329566</v>
       </c>
       <c r="C12">
-        <v>8.878615309025424</v>
+        <v>8.5209960987549</v>
       </c>
       <c r="D12">
-        <v>9.964615309025424</v>
+        <v>9.770896098754898</v>
       </c>
       <c r="E12">
-        <v>-6.271</v>
+        <v>-6.1071</v>
       </c>
       <c r="F12">
-        <v>1.639</v>
+        <v>1.8029</v>
       </c>
       <c r="G12">
         <v>0.553</v>
@@ -2254,37 +2265,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M12">
-        <v>0.3864762</v>
+        <v>0.42512382</v>
       </c>
       <c r="N12">
-        <v>-1.0514762</v>
+        <v>-1.09012382</v>
       </c>
       <c r="O12">
-        <v>-0.26286905</v>
+        <v>-0.2725309550000001</v>
       </c>
       <c r="P12">
-        <v>-0.7886071500000001</v>
+        <v>-0.8175928650000002</v>
       </c>
       <c r="Q12">
-        <v>1.45139285</v>
+        <v>1.422407135</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09149349269237052</v>
+        <v>0.09200690272262188</v>
       </c>
       <c r="T12">
-        <v>0.8906512218275249</v>
+        <v>0.9006585389267107</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.4301687917651851</v>
+        <v>-0.3910625379683501</v>
       </c>
       <c r="W12">
-        <v>0.3372338010982306</v>
+        <v>0.328012546452937</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2292,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-1.72067516706074</v>
+        <v>-1.5642501518734</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2300,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1179675235329566</v>
+        <v>0.1198675235329565</v>
       </c>
       <c r="C13">
-        <v>8.5209960987549</v>
+        <v>8.170765330429571</v>
       </c>
       <c r="D13">
-        <v>9.770896098754898</v>
+        <v>9.584565330429569</v>
       </c>
       <c r="E13">
-        <v>-6.1071</v>
+        <v>-5.9432</v>
       </c>
       <c r="F13">
-        <v>1.8029</v>
+        <v>1.9668</v>
       </c>
       <c r="G13">
         <v>0.553</v>
@@ -2336,37 +2347,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M13">
-        <v>0.42512382</v>
+        <v>0.46377144</v>
       </c>
       <c r="N13">
-        <v>-1.09012382</v>
+        <v>-1.12877144</v>
       </c>
       <c r="O13">
-        <v>-0.2725309550000001</v>
+        <v>-0.2821928600000001</v>
       </c>
       <c r="P13">
-        <v>-0.8175928650000002</v>
+        <v>-0.8465785800000003</v>
       </c>
       <c r="Q13">
-        <v>1.422407135</v>
+        <v>1.39342142</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09200690272262188</v>
+        <v>0.09253198116265168</v>
       </c>
       <c r="T13">
-        <v>0.9006585389267107</v>
+        <v>0.9108932950508778</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.3910625379683501</v>
+        <v>-0.3584739931376543</v>
       </c>
       <c r="W13">
-        <v>0.328012546452937</v>
+        <v>0.3203281675818589</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2374,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-1.5642501518734</v>
+        <v>-1.433895972550618</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2382,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1198675235329565</v>
+        <v>0.1217675235329565</v>
       </c>
       <c r="C14">
-        <v>8.170765330429571</v>
+        <v>7.827508221675964</v>
       </c>
       <c r="D14">
-        <v>9.584565330429569</v>
+        <v>9.405208221675963</v>
       </c>
       <c r="E14">
-        <v>-5.9432</v>
+        <v>-5.7793</v>
       </c>
       <c r="F14">
-        <v>1.9668</v>
+        <v>2.1307</v>
       </c>
       <c r="G14">
         <v>0.553</v>
@@ -2418,37 +2429,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M14">
-        <v>0.46377144</v>
+        <v>0.50241906</v>
       </c>
       <c r="N14">
-        <v>-1.12877144</v>
+        <v>-1.16741906</v>
       </c>
       <c r="O14">
-        <v>-0.2821928600000001</v>
+        <v>-0.2918547650000001</v>
       </c>
       <c r="P14">
-        <v>-0.8465785800000003</v>
+        <v>-0.8755642950000002</v>
       </c>
       <c r="Q14">
-        <v>1.39342142</v>
+        <v>1.364435705</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09253198116265168</v>
+        <v>0.09306913037141779</v>
       </c>
       <c r="T14">
-        <v>0.9108932950508778</v>
+        <v>0.9213633329250257</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.3584739931376543</v>
+        <v>-0.330899070588604</v>
       </c>
       <c r="W14">
-        <v>0.3203281675818589</v>
+        <v>0.3138260008447928</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2456,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-1.433895972550618</v>
+        <v>-1.323596282354416</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2464,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1217675235329565</v>
+        <v>0.1236675235329565</v>
       </c>
       <c r="C15">
-        <v>7.827508221675964</v>
+        <v>7.490840467284974</v>
       </c>
       <c r="D15">
-        <v>9.405208221675963</v>
+        <v>9.232440467284974</v>
       </c>
       <c r="E15">
-        <v>-5.7793</v>
+        <v>-5.615399999999999</v>
       </c>
       <c r="F15">
-        <v>2.1307</v>
+        <v>2.2946</v>
       </c>
       <c r="G15">
         <v>0.553</v>
@@ -2500,37 +2511,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M15">
-        <v>0.50241906</v>
+        <v>0.5410666800000001</v>
       </c>
       <c r="N15">
-        <v>-1.16741906</v>
+        <v>-1.20606668</v>
       </c>
       <c r="O15">
-        <v>-0.2918547650000001</v>
+        <v>-0.3015166700000001</v>
       </c>
       <c r="P15">
-        <v>-0.8755642950000002</v>
+        <v>-0.9045500100000003</v>
       </c>
       <c r="Q15">
-        <v>1.364435705</v>
+        <v>1.33544999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09306913037141779</v>
+        <v>0.09361877142224823</v>
       </c>
       <c r="T15">
-        <v>0.9213633329250257</v>
+        <v>0.932076860052061</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.330899070588604</v>
+        <v>-0.3072634226894179</v>
       </c>
       <c r="W15">
-        <v>0.3138260008447928</v>
+        <v>0.3082527150701648</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2538,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-1.323596282354416</v>
+        <v>-1.229053690757671</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2546,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1236675235329565</v>
+        <v>0.1255675235329566</v>
       </c>
       <c r="C16">
-        <v>7.490840467284974</v>
+        <v>7.160405490472854</v>
       </c>
       <c r="D16">
-        <v>9.232440467284974</v>
+        <v>9.065905490472854</v>
       </c>
       <c r="E16">
-        <v>-5.615399999999999</v>
+        <v>-5.451499999999999</v>
       </c>
       <c r="F16">
-        <v>2.2946</v>
+        <v>2.4585</v>
       </c>
       <c r="G16">
         <v>0.553</v>
@@ -2582,37 +2593,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M16">
-        <v>0.5410666800000001</v>
+        <v>0.5797143000000001</v>
       </c>
       <c r="N16">
-        <v>-1.20606668</v>
+        <v>-1.2447143</v>
       </c>
       <c r="O16">
-        <v>-0.3015166700000001</v>
+        <v>-0.3111785750000001</v>
       </c>
       <c r="P16">
-        <v>-0.9045500100000003</v>
+        <v>-0.9335357250000004</v>
       </c>
       <c r="Q16">
-        <v>1.33544999</v>
+        <v>1.306464275</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09361877142224823</v>
+        <v>0.09418134520368643</v>
       </c>
       <c r="T16">
-        <v>0.932076860052061</v>
+        <v>0.9430424701703205</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.3072634226894179</v>
+        <v>-0.2867791945101234</v>
       </c>
       <c r="W16">
-        <v>0.3082527150701648</v>
+        <v>0.3034225340654871</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2620,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-1.229053690757671</v>
+        <v>-1.147116778040494</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2628,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1255675235329565</v>
+        <v>0.1274675235329565</v>
       </c>
       <c r="C17">
-        <v>7.160405490472859</v>
+        <v>6.835871986362051</v>
       </c>
       <c r="D17">
-        <v>9.065905490472858</v>
+        <v>8.905271986362051</v>
       </c>
       <c r="E17">
-        <v>-5.4515</v>
+        <v>-5.287599999999999</v>
       </c>
       <c r="F17">
-        <v>2.4585</v>
+        <v>2.6224</v>
       </c>
       <c r="G17">
         <v>0.553</v>
@@ -2664,37 +2675,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M17">
-        <v>0.5797143</v>
+        <v>0.6183619200000001</v>
       </c>
       <c r="N17">
-        <v>-1.2447143</v>
+        <v>-1.28336192</v>
       </c>
       <c r="O17">
-        <v>-0.3111785750000001</v>
+        <v>-0.3208404800000001</v>
       </c>
       <c r="P17">
-        <v>-0.9335357250000003</v>
+        <v>-0.9625214400000003</v>
       </c>
       <c r="Q17">
-        <v>1.306464275</v>
+        <v>1.27747856</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09418134520368643</v>
+        <v>0.09475731359896841</v>
       </c>
       <c r="T17">
-        <v>0.9430424701703205</v>
+        <v>0.9542691662437768</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.2867791945101235</v>
+        <v>-0.2688554948532407</v>
       </c>
       <c r="W17">
-        <v>0.3034225340654871</v>
+        <v>0.2991961256863941</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2702,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-1.147116778040494</v>
+        <v>-1.075421979412963</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2710,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1274675235329565</v>
+        <v>0.1293675235329566</v>
       </c>
       <c r="C18">
-        <v>6.835871986362051</v>
+        <v>6.516931722069133</v>
       </c>
       <c r="D18">
-        <v>8.905271986362051</v>
+        <v>8.750231722069133</v>
       </c>
       <c r="E18">
-        <v>-5.287599999999999</v>
+        <v>-5.123699999999999</v>
       </c>
       <c r="F18">
-        <v>2.6224</v>
+        <v>2.7863</v>
       </c>
       <c r="G18">
         <v>0.553</v>
@@ -2746,37 +2757,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M18">
-        <v>0.6183619200000001</v>
+        <v>0.6570095400000001</v>
       </c>
       <c r="N18">
-        <v>-1.28336192</v>
+        <v>-1.32200954</v>
       </c>
       <c r="O18">
-        <v>-0.3208404800000001</v>
+        <v>-0.3305023850000001</v>
       </c>
       <c r="P18">
-        <v>-0.9625214400000003</v>
+        <v>-0.9915071550000002</v>
       </c>
       <c r="Q18">
-        <v>1.27747856</v>
+        <v>1.248492845</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09475731359896841</v>
+        <v>0.09534716075076322</v>
       </c>
       <c r="T18">
-        <v>0.9542691662437768</v>
+        <v>0.9657663851141838</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.2688554948532407</v>
+        <v>-0.2530404657442266</v>
       </c>
       <c r="W18">
-        <v>0.2991961256863941</v>
+        <v>0.2954669418224887</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2784,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-1.075421979412963</v>
+        <v>-1.012161862976906</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2792,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1293675235329566</v>
+        <v>0.1312675235329565</v>
       </c>
       <c r="C19">
-        <v>6.516931722069133</v>
+        <v>6.203297562662458</v>
       </c>
       <c r="D19">
-        <v>8.750231722069133</v>
+        <v>8.600497562662458</v>
       </c>
       <c r="E19">
-        <v>-5.123699999999999</v>
+        <v>-4.9598</v>
       </c>
       <c r="F19">
-        <v>2.7863</v>
+        <v>2.950200000000001</v>
       </c>
       <c r="G19">
         <v>0.553</v>
@@ -2828,37 +2839,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M19">
-        <v>0.6570095400000001</v>
+        <v>0.6956571600000002</v>
       </c>
       <c r="N19">
-        <v>-1.32200954</v>
+        <v>-1.360657160000001</v>
       </c>
       <c r="O19">
-        <v>-0.3305023850000001</v>
+        <v>-0.3401642900000001</v>
       </c>
       <c r="P19">
-        <v>-0.9915071550000002</v>
+        <v>-1.02049287</v>
       </c>
       <c r="Q19">
-        <v>1.248492845</v>
+        <v>1.21950713</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09534716075076322</v>
+        <v>0.09595139441845546</v>
       </c>
       <c r="T19">
-        <v>0.9657663851141838</v>
+        <v>0.9775440239570395</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.2530404657442266</v>
+        <v>-0.2389826620917695</v>
       </c>
       <c r="W19">
-        <v>0.2954669418224887</v>
+        <v>0.2921521117212392</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2866,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-1.012161862976906</v>
+        <v>-0.955930648367078</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2874,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1312675235329565</v>
+        <v>0.1331675235329565</v>
       </c>
       <c r="C20">
-        <v>6.203297562662458</v>
+        <v>5.89470169638899</v>
       </c>
       <c r="D20">
-        <v>8.600497562662458</v>
+        <v>8.45580169638899</v>
       </c>
       <c r="E20">
-        <v>-4.9598</v>
+        <v>-4.7959</v>
       </c>
       <c r="F20">
-        <v>2.9502</v>
+        <v>3.1141</v>
       </c>
       <c r="G20">
         <v>0.553</v>
@@ -2910,37 +2921,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M20">
-        <v>0.6956571600000001</v>
+        <v>0.7343047800000001</v>
       </c>
       <c r="N20">
-        <v>-1.36065716</v>
+        <v>-1.39930478</v>
       </c>
       <c r="O20">
-        <v>-0.3401642900000001</v>
+        <v>-0.3498261950000001</v>
       </c>
       <c r="P20">
-        <v>-1.02049287</v>
+        <v>-1.049478585</v>
       </c>
       <c r="Q20">
-        <v>1.21950713</v>
+        <v>1.190521415</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09595139441845546</v>
+        <v>0.09657054743596724</v>
       </c>
       <c r="T20">
-        <v>0.9775440239570395</v>
+        <v>0.9896124686972499</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.2389826620917695</v>
+        <v>-0.2264046272448343</v>
       </c>
       <c r="W20">
-        <v>0.2921521117212392</v>
+        <v>0.289186211104332</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2948,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.955930648367078</v>
+        <v>-0.9056185089793374</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2956,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1331675235329565</v>
+        <v>0.1350675235329565</v>
       </c>
       <c r="C21">
-        <v>5.89470169638899</v>
+        <v>5.590894036091013</v>
       </c>
       <c r="D21">
-        <v>8.45580169638899</v>
+        <v>8.315894036091013</v>
       </c>
       <c r="E21">
-        <v>-4.7959</v>
+        <v>-4.632</v>
       </c>
       <c r="F21">
-        <v>3.1141</v>
+        <v>3.278</v>
       </c>
       <c r="G21">
         <v>0.553</v>
@@ -2992,37 +3003,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M21">
-        <v>0.7343047800000001</v>
+        <v>0.7729524000000001</v>
       </c>
       <c r="N21">
-        <v>-1.39930478</v>
+        <v>-1.4379524</v>
       </c>
       <c r="O21">
-        <v>-0.3498261950000001</v>
+        <v>-0.3594881000000001</v>
       </c>
       <c r="P21">
-        <v>-1.049478585</v>
+        <v>-1.0784643</v>
       </c>
       <c r="Q21">
-        <v>1.190521415</v>
+        <v>1.1615357</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09657054743596724</v>
+        <v>0.09720517927891684</v>
       </c>
       <c r="T21">
-        <v>0.9896124686972499</v>
+        <v>1.001982624555966</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.2264046272448343</v>
+        <v>-0.2150843958825926</v>
       </c>
       <c r="W21">
-        <v>0.289186211104332</v>
+        <v>0.2865169005491153</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3030,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.9056185089793374</v>
+        <v>-0.8603375835303704</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3038,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1350675235329565</v>
+        <v>0.1369675235329565</v>
       </c>
       <c r="C22">
-        <v>5.590894036091013</v>
+        <v>5.291640776738394</v>
       </c>
       <c r="D22">
-        <v>8.315894036091013</v>
+        <v>8.180540776738393</v>
       </c>
       <c r="E22">
-        <v>-4.632</v>
+        <v>-4.4681</v>
       </c>
       <c r="F22">
-        <v>3.278</v>
+        <v>3.4419</v>
       </c>
       <c r="G22">
         <v>0.553</v>
@@ -3074,37 +3085,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M22">
-        <v>0.7729524000000001</v>
+        <v>0.8116000200000001</v>
       </c>
       <c r="N22">
-        <v>-1.4379524</v>
+        <v>-1.47660002</v>
       </c>
       <c r="O22">
-        <v>-0.3594881000000001</v>
+        <v>-0.3691500050000001</v>
       </c>
       <c r="P22">
-        <v>-1.0784643</v>
+        <v>-1.107450015</v>
       </c>
       <c r="Q22">
-        <v>1.1615357</v>
+        <v>1.132549985</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09720517927891684</v>
+        <v>0.09785587775080186</v>
       </c>
       <c r="T22">
-        <v>1.001982624555966</v>
+        <v>1.014665948917433</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.2150843958825926</v>
+        <v>-0.2048422817929453</v>
       </c>
       <c r="W22">
-        <v>0.2865169005491153</v>
+        <v>0.2841018100467765</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3112,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.8603375835303704</v>
+        <v>-0.8193691271717811</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3120,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1369675235329565</v>
+        <v>0.1388675235329566</v>
       </c>
       <c r="C23">
-        <v>5.291640776738394</v>
+        <v>4.996723091574273</v>
       </c>
       <c r="D23">
-        <v>8.180540776738393</v>
+        <v>8.049523091574272</v>
       </c>
       <c r="E23">
-        <v>-4.4681</v>
+        <v>-4.3042</v>
       </c>
       <c r="F23">
-        <v>3.4419</v>
+        <v>3.6058</v>
       </c>
       <c r="G23">
         <v>0.553</v>
@@ -3156,37 +3167,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M23">
-        <v>0.81160002</v>
+        <v>0.8502476400000001</v>
       </c>
       <c r="N23">
-        <v>-1.47660002</v>
+        <v>-1.51524764</v>
       </c>
       <c r="O23">
-        <v>-0.3691500050000001</v>
+        <v>-0.3788119100000001</v>
       </c>
       <c r="P23">
-        <v>-1.107450015</v>
+        <v>-1.13643573</v>
       </c>
       <c r="Q23">
-        <v>1.132549985</v>
+        <v>1.10356427</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09785587775080186</v>
+        <v>0.09852326079888907</v>
       </c>
       <c r="T23">
-        <v>1.014665948917433</v>
+        <v>1.027674486724067</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.2048422817929453</v>
+        <v>-0.1955312689841751</v>
       </c>
       <c r="W23">
-        <v>0.2841018100467765</v>
+        <v>0.2819062732264685</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3194,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.8193691271717813</v>
+        <v>-0.7821250759367002</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3202,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1388675235329566</v>
+        <v>0.1407675235329566</v>
       </c>
       <c r="C24">
-        <v>4.996723091574273</v>
+        <v>4.705935951579136</v>
       </c>
       <c r="D24">
-        <v>8.049523091574272</v>
+        <v>7.922635951579135</v>
       </c>
       <c r="E24">
-        <v>-4.3042</v>
+        <v>-4.1403</v>
       </c>
       <c r="F24">
-        <v>3.6058</v>
+        <v>3.7697</v>
       </c>
       <c r="G24">
         <v>0.553</v>
@@ -3238,37 +3249,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M24">
-        <v>0.8502476400000001</v>
+        <v>0.8888952600000001</v>
       </c>
       <c r="N24">
-        <v>-1.51524764</v>
+        <v>-1.55389526</v>
       </c>
       <c r="O24">
-        <v>-0.3788119100000001</v>
+        <v>-0.3884738150000001</v>
       </c>
       <c r="P24">
-        <v>-1.13643573</v>
+        <v>-1.165421445</v>
       </c>
       <c r="Q24">
-        <v>1.10356427</v>
+        <v>1.074578555</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09852326079888907</v>
+        <v>0.09920797847160193</v>
       </c>
       <c r="T24">
-        <v>1.027674486724067</v>
+        <v>1.041020908629575</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.1955312689841751</v>
+        <v>-0.187029909463124</v>
       </c>
       <c r="W24">
-        <v>0.2819062732264685</v>
+        <v>0.2799016526514047</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3276,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.7821250759367002</v>
+        <v>-0.7481196378524961</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3284,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1407675235329566</v>
+        <v>0.1426675235329566</v>
       </c>
       <c r="C25">
-        <v>4.705935951579136</v>
+        <v>4.419087054857064</v>
       </c>
       <c r="D25">
-        <v>7.922635951579135</v>
+        <v>7.799687054857064</v>
       </c>
       <c r="E25">
-        <v>-4.1403</v>
+        <v>-3.976399999999999</v>
       </c>
       <c r="F25">
-        <v>3.7697</v>
+        <v>3.933600000000001</v>
       </c>
       <c r="G25">
         <v>0.553</v>
@@ -3320,37 +3331,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M25">
-        <v>0.8888952600000001</v>
+        <v>0.9275428800000002</v>
       </c>
       <c r="N25">
-        <v>-1.55389526</v>
+        <v>-1.59254288</v>
       </c>
       <c r="O25">
-        <v>-0.3884738150000001</v>
+        <v>-0.3981357200000001</v>
       </c>
       <c r="P25">
-        <v>-1.165421445</v>
+        <v>-1.19440716</v>
       </c>
       <c r="Q25">
-        <v>1.074578555</v>
+        <v>1.04559284</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09920797847160193</v>
+        <v>0.09991071503043879</v>
       </c>
       <c r="T25">
-        <v>1.041020908629575</v>
+        <v>1.054718552164174</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.187029909463124</v>
+        <v>-0.1792369965688271</v>
       </c>
       <c r="W25">
-        <v>0.2799016526514047</v>
+        <v>0.2780640837909295</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3358,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.7481196378524961</v>
+        <v>-0.7169479862753083</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3366,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1426675235329565</v>
+        <v>0.1445675235329565</v>
       </c>
       <c r="C26">
-        <v>4.419087054857066</v>
+        <v>4.135995854185733</v>
       </c>
       <c r="D26">
-        <v>7.799687054857066</v>
+        <v>7.680495854185733</v>
       </c>
       <c r="E26">
-        <v>-3.9764</v>
+        <v>-3.8125</v>
       </c>
       <c r="F26">
-        <v>3.9336</v>
+        <v>4.0975</v>
       </c>
       <c r="G26">
         <v>0.553</v>
@@ -3402,37 +3413,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M26">
-        <v>0.9275428800000001</v>
+        <v>0.9661905000000001</v>
       </c>
       <c r="N26">
-        <v>-1.59254288</v>
+        <v>-1.6311905</v>
       </c>
       <c r="O26">
-        <v>-0.3981357200000001</v>
+        <v>-0.4077976250000001</v>
       </c>
       <c r="P26">
-        <v>-1.19440716</v>
+        <v>-1.223392875</v>
       </c>
       <c r="Q26">
-        <v>1.04559284</v>
+        <v>1.016607125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09991071503043879</v>
+        <v>0.1006321912308446</v>
       </c>
       <c r="T26">
-        <v>1.054718552164174</v>
+        <v>1.06878146619303</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.1792369965688272</v>
+        <v>-0.1720675167060741</v>
       </c>
       <c r="W26">
-        <v>0.2780640837909295</v>
+        <v>0.2763735204392923</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3440,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.7169479862753085</v>
+        <v>-0.688270066824296</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3448,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1445675235329565</v>
+        <v>0.1464675235329566</v>
       </c>
       <c r="C27">
-        <v>4.135995854185733</v>
+        <v>3.856492672387539</v>
       </c>
       <c r="D27">
-        <v>7.680495854185733</v>
+        <v>7.564892672387539</v>
       </c>
       <c r="E27">
-        <v>-3.8125</v>
+        <v>-3.6486</v>
       </c>
       <c r="F27">
-        <v>4.0975</v>
+        <v>4.2614</v>
       </c>
       <c r="G27">
         <v>0.553</v>
@@ -3484,37 +3495,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M27">
-        <v>0.9661905000000001</v>
+        <v>1.00483812</v>
       </c>
       <c r="N27">
-        <v>-1.6311905</v>
+        <v>-1.66983812</v>
       </c>
       <c r="O27">
-        <v>-0.4077976250000001</v>
+        <v>-0.4174595300000001</v>
       </c>
       <c r="P27">
-        <v>-1.223392875</v>
+        <v>-1.25237859</v>
       </c>
       <c r="Q27">
-        <v>1.016607125</v>
+        <v>0.98762141</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1006321912308446</v>
+        <v>0.1013731667880182</v>
       </c>
       <c r="T27">
-        <v>1.06878146619303</v>
+        <v>1.083224458979422</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.1720675167060741</v>
+        <v>-0.165449535294302</v>
       </c>
       <c r="W27">
-        <v>0.2763735204392923</v>
+        <v>0.2748130004223964</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3522,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.688270066824296</v>
+        <v>-0.661798141177208</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3530,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1464675235329566</v>
+        <v>0.1483675235329566</v>
       </c>
       <c r="C28">
-        <v>3.856492672387539</v>
+        <v>3.580417896406201</v>
       </c>
       <c r="D28">
-        <v>7.564892672387539</v>
+        <v>7.452717896406202</v>
       </c>
       <c r="E28">
-        <v>-3.6486</v>
+        <v>-3.4847</v>
       </c>
       <c r="F28">
-        <v>4.2614</v>
+        <v>4.4253</v>
       </c>
       <c r="G28">
         <v>0.553</v>
@@ -3566,37 +3577,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M28">
-        <v>1.00483812</v>
+        <v>1.04348574</v>
       </c>
       <c r="N28">
-        <v>-1.66983812</v>
+        <v>-1.70848574</v>
       </c>
       <c r="O28">
-        <v>-0.4174595300000001</v>
+        <v>-0.427121435</v>
       </c>
       <c r="P28">
-        <v>-1.25237859</v>
+        <v>-1.281364305</v>
       </c>
       <c r="Q28">
-        <v>0.98762141</v>
+        <v>0.9586356950000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1013731667880182</v>
+        <v>0.1021344430453883</v>
       </c>
       <c r="T28">
-        <v>1.083224458979422</v>
+        <v>1.098063150198318</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.165449535294302</v>
+        <v>-0.1593217747278464</v>
       </c>
       <c r="W28">
-        <v>0.2748130004223964</v>
+        <v>0.2733680744808262</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3604,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.661798141177208</v>
+        <v>-0.6372870989113855</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3612,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1483675235329566</v>
+        <v>0.1502675235329565</v>
       </c>
       <c r="C29">
-        <v>3.580417896406201</v>
+        <v>3.307621242038643</v>
       </c>
       <c r="D29">
-        <v>7.452717896406202</v>
+        <v>7.343821242038644</v>
       </c>
       <c r="E29">
-        <v>-3.4847</v>
+        <v>-3.320799999999999</v>
       </c>
       <c r="F29">
-        <v>4.4253</v>
+        <v>4.589200000000001</v>
       </c>
       <c r="G29">
         <v>0.553</v>
@@ -3648,37 +3659,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M29">
-        <v>1.04348574</v>
+        <v>1.08213336</v>
       </c>
       <c r="N29">
-        <v>-1.70848574</v>
+        <v>-1.747133360000001</v>
       </c>
       <c r="O29">
-        <v>-0.427121435</v>
+        <v>-0.4367833400000001</v>
       </c>
       <c r="P29">
-        <v>-1.281364305</v>
+        <v>-1.31035002</v>
       </c>
       <c r="Q29">
-        <v>0.9586356950000001</v>
+        <v>0.9296499799999998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1021344430453883</v>
+        <v>0.1029168658654632</v>
       </c>
       <c r="T29">
-        <v>1.098063150198318</v>
+        <v>1.113314027284406</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.1593217747278464</v>
+        <v>-0.153631711344709</v>
       </c>
       <c r="W29">
-        <v>0.2733680744808262</v>
+        <v>0.2720263575350824</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3686,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.6372870989113855</v>
+        <v>-0.6145268453788357</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3694,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1502675235329565</v>
+        <v>0.1521675235329565</v>
       </c>
       <c r="C30">
-        <v>3.307621242038643</v>
+        <v>3.03796108219955</v>
       </c>
       <c r="D30">
-        <v>7.343821242038644</v>
+        <v>7.23806108219955</v>
       </c>
       <c r="E30">
-        <v>-3.320799999999999</v>
+        <v>-3.156899999999999</v>
       </c>
       <c r="F30">
-        <v>4.589200000000001</v>
+        <v>4.753100000000001</v>
       </c>
       <c r="G30">
         <v>0.553</v>
@@ -3730,37 +3741,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M30">
-        <v>1.08213336</v>
+        <v>1.12078098</v>
       </c>
       <c r="N30">
-        <v>-1.747133360000001</v>
+        <v>-1.78578098</v>
       </c>
       <c r="O30">
-        <v>-0.4367833400000001</v>
+        <v>-0.4464452450000001</v>
       </c>
       <c r="P30">
-        <v>-1.31035002</v>
+        <v>-1.339335735</v>
       </c>
       <c r="Q30">
-        <v>0.9296499799999998</v>
+        <v>0.9006642649999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1029168658654632</v>
+        <v>0.1037213287649767</v>
       </c>
       <c r="T30">
-        <v>1.113314027284406</v>
+        <v>1.128994506541933</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.153631711344709</v>
+        <v>-0.1483340661259259</v>
       </c>
       <c r="W30">
-        <v>0.2720263575350824</v>
+        <v>0.2707771727924933</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3768,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.6145268453788357</v>
+        <v>-0.5933362645037037</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3776,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1521675235329565</v>
+        <v>0.1540675235329566</v>
       </c>
       <c r="C31">
-        <v>3.03796108219955</v>
+        <v>2.771303832404874</v>
       </c>
       <c r="D31">
-        <v>7.23806108219955</v>
+        <v>7.135303832404874</v>
       </c>
       <c r="E31">
-        <v>-3.1569</v>
+        <v>-2.993</v>
       </c>
       <c r="F31">
-        <v>4.7531</v>
+        <v>4.917</v>
       </c>
       <c r="G31">
         <v>0.553</v>
@@ -3812,37 +3823,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M31">
-        <v>1.12078098</v>
+        <v>1.1594286</v>
       </c>
       <c r="N31">
-        <v>-1.78578098</v>
+        <v>-1.8244286</v>
       </c>
       <c r="O31">
-        <v>-0.446445245</v>
+        <v>-0.4561071500000001</v>
       </c>
       <c r="P31">
-        <v>-1.339335735</v>
+        <v>-1.36832145</v>
       </c>
       <c r="Q31">
-        <v>0.9006642650000001</v>
+        <v>0.8716785499999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1037213287649767</v>
+        <v>0.1045487763187621</v>
       </c>
       <c r="T31">
-        <v>1.128994506541933</v>
+        <v>1.145122999492532</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.148334066125926</v>
+        <v>-0.1433895972550617</v>
       </c>
       <c r="W31">
-        <v>0.2707771727924934</v>
+        <v>0.2696112670327436</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3850,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.5933362645037037</v>
+        <v>-0.5735583890202469</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3858,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1540675235329566</v>
+        <v>0.1559675235329565</v>
       </c>
       <c r="C32">
-        <v>2.771303832404874</v>
+        <v>2.50752338786755</v>
       </c>
       <c r="D32">
-        <v>7.135303832404874</v>
+        <v>7.035423387867549</v>
       </c>
       <c r="E32">
-        <v>-2.993</v>
+        <v>-2.8291</v>
       </c>
       <c r="F32">
-        <v>4.917</v>
+        <v>5.0809</v>
       </c>
       <c r="G32">
         <v>0.553</v>
@@ -3894,37 +3905,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M32">
-        <v>1.1594286</v>
+        <v>1.19807622</v>
       </c>
       <c r="N32">
-        <v>-1.8244286</v>
+        <v>-1.86307622</v>
       </c>
       <c r="O32">
-        <v>-0.4561071500000001</v>
+        <v>-0.465769055</v>
       </c>
       <c r="P32">
-        <v>-1.36832145</v>
+        <v>-1.397307165</v>
       </c>
       <c r="Q32">
-        <v>0.8716785499999999</v>
+        <v>0.842692835</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1045487763187621</v>
+        <v>0.1054002078596137</v>
       </c>
       <c r="T32">
-        <v>1.145122999492532</v>
+        <v>1.161718984992424</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.1433895972550617</v>
+        <v>-0.1387641263758662</v>
       </c>
       <c r="W32">
-        <v>0.2696112670327436</v>
+        <v>0.2685205809994292</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3932,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.5735583890202469</v>
+        <v>-0.5550565055034649</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3940,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1559675235329565</v>
+        <v>0.1578675235329565</v>
       </c>
       <c r="C33">
-        <v>2.50752338786755</v>
+        <v>2.246500607218</v>
       </c>
       <c r="D33">
-        <v>7.035423387867549</v>
+        <v>6.938300607218</v>
       </c>
       <c r="E33">
-        <v>-2.8291</v>
+        <v>-2.6652</v>
       </c>
       <c r="F33">
-        <v>5.0809</v>
+        <v>5.244800000000001</v>
       </c>
       <c r="G33">
         <v>0.553</v>
@@ -3976,37 +3987,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M33">
-        <v>1.19807622</v>
+        <v>1.23672384</v>
       </c>
       <c r="N33">
-        <v>-1.86307622</v>
+        <v>-1.90172384</v>
       </c>
       <c r="O33">
-        <v>-0.465769055</v>
+        <v>-0.4754309600000001</v>
       </c>
       <c r="P33">
-        <v>-1.397307165</v>
+        <v>-1.42629288</v>
       </c>
       <c r="Q33">
-        <v>0.842692835</v>
+        <v>0.8137071199999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1054002078596137</v>
+        <v>0.106276681504608</v>
       </c>
       <c r="T33">
-        <v>1.161718984992424</v>
+        <v>1.178803087712901</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.1387641263758662</v>
+        <v>-0.1344277474266203</v>
       </c>
       <c r="W33">
-        <v>0.2685205809994292</v>
+        <v>0.267498062843197</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4014,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.5550565055034649</v>
+        <v>-0.5377109897064813</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4022,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1578675235329565</v>
+        <v>0.1597675235329565</v>
       </c>
       <c r="C34">
-        <v>2.246500607218</v>
+        <v>1.988122838405244</v>
       </c>
       <c r="D34">
-        <v>6.938300607218</v>
+        <v>6.843822838405244</v>
       </c>
       <c r="E34">
-        <v>-2.6652</v>
+        <v>-2.5013</v>
       </c>
       <c r="F34">
-        <v>5.244800000000001</v>
+        <v>5.408700000000001</v>
       </c>
       <c r="G34">
         <v>0.553</v>
@@ -4058,37 +4069,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M34">
-        <v>1.23672384</v>
+        <v>1.27537146</v>
       </c>
       <c r="N34">
-        <v>-1.90172384</v>
+        <v>-1.94037146</v>
       </c>
       <c r="O34">
-        <v>-0.4754309600000001</v>
+        <v>-0.4850928650000001</v>
       </c>
       <c r="P34">
-        <v>-1.42629288</v>
+        <v>-1.455278595</v>
       </c>
       <c r="Q34">
-        <v>0.8137071199999999</v>
+        <v>0.784721405</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.106276681504608</v>
+        <v>0.1071793185419903</v>
       </c>
       <c r="T34">
-        <v>1.178803087712901</v>
+        <v>1.196397163648914</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.1344277474266203</v>
+        <v>-0.1303541793227834</v>
       </c>
       <c r="W34">
-        <v>0.267498062843197</v>
+        <v>0.2665375154843123</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4096,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.5377109897064813</v>
+        <v>-0.5214167172911335</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4104,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1597675235329565</v>
+        <v>0.1616675235329565</v>
       </c>
       <c r="C35">
-        <v>1.988122838405244</v>
+        <v>1.732283482812008</v>
       </c>
       <c r="D35">
-        <v>6.843822838405244</v>
+        <v>6.751883482812008</v>
       </c>
       <c r="E35">
-        <v>-2.5013</v>
+        <v>-2.3374</v>
       </c>
       <c r="F35">
-        <v>5.408700000000001</v>
+        <v>5.5726</v>
       </c>
       <c r="G35">
         <v>0.553</v>
@@ -4140,37 +4151,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M35">
-        <v>1.27537146</v>
+        <v>1.31401908</v>
       </c>
       <c r="N35">
-        <v>-1.94037146</v>
+        <v>-1.97901908</v>
       </c>
       <c r="O35">
-        <v>-0.4850928650000001</v>
+        <v>-0.4947547700000001</v>
       </c>
       <c r="P35">
-        <v>-1.455278595</v>
+        <v>-1.48426431</v>
       </c>
       <c r="Q35">
-        <v>0.784721405</v>
+        <v>0.7557356899999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1071793185419903</v>
+        <v>0.1081093082168689</v>
       </c>
       <c r="T35">
-        <v>1.196397163648914</v>
+        <v>1.21452439340117</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.1303541793227834</v>
+        <v>-0.1265202328721133</v>
       </c>
       <c r="W35">
-        <v>0.2665375154843123</v>
+        <v>0.2656334709112443</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4178,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.5214167172911335</v>
+        <v>-0.5060809314884531</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4186,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1616675235329565</v>
+        <v>0.1635675235329565</v>
       </c>
       <c r="C36">
-        <v>1.732283482812008</v>
+        <v>1.478881594037984</v>
       </c>
       <c r="D36">
-        <v>6.751883482812008</v>
+        <v>6.662381594037984</v>
       </c>
       <c r="E36">
-        <v>-2.3374</v>
+        <v>-2.1735</v>
       </c>
       <c r="F36">
-        <v>5.5726</v>
+        <v>5.7365</v>
       </c>
       <c r="G36">
         <v>0.553</v>
@@ -4222,37 +4233,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M36">
-        <v>1.31401908</v>
+        <v>1.3526667</v>
       </c>
       <c r="N36">
-        <v>-1.97901908</v>
+        <v>-2.0176667</v>
       </c>
       <c r="O36">
-        <v>-0.4947547700000001</v>
+        <v>-0.5044166750000001</v>
       </c>
       <c r="P36">
-        <v>-1.48426431</v>
+        <v>-1.513250025</v>
       </c>
       <c r="Q36">
-        <v>0.7557356899999998</v>
+        <v>0.7267499749999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1081093082168689</v>
+        <v>0.1090679129586669</v>
       </c>
       <c r="T36">
-        <v>1.21452439340117</v>
+        <v>1.233209384068881</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.1265202328721133</v>
+        <v>-0.1229053690757672</v>
       </c>
       <c r="W36">
-        <v>0.2656334709112443</v>
+        <v>0.2647810860280659</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4260,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.5060809314884531</v>
+        <v>-0.4916214763030688</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4268,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1635675235329565</v>
+        <v>0.1654675235329565</v>
       </c>
       <c r="C37">
-        <v>1.478881594037984</v>
+        <v>1.227821508176385</v>
       </c>
       <c r="D37">
-        <v>6.662381594037984</v>
+        <v>6.575221508176386</v>
       </c>
       <c r="E37">
-        <v>-2.1735</v>
+        <v>-2.009599999999999</v>
       </c>
       <c r="F37">
-        <v>5.7365</v>
+        <v>5.900400000000001</v>
       </c>
       <c r="G37">
         <v>0.553</v>
@@ -4304,37 +4315,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M37">
-        <v>1.3526667</v>
+        <v>1.39131432</v>
       </c>
       <c r="N37">
-        <v>-2.0176667</v>
+        <v>-2.056314320000001</v>
       </c>
       <c r="O37">
-        <v>-0.5044166750000001</v>
+        <v>-0.5140785800000002</v>
       </c>
       <c r="P37">
-        <v>-1.513250025</v>
+        <v>-1.542235740000001</v>
       </c>
       <c r="Q37">
-        <v>0.7267499749999999</v>
+        <v>0.6977642599999996</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1090679129586669</v>
+        <v>0.1100564740986461</v>
       </c>
       <c r="T37">
-        <v>1.233209384068881</v>
+        <v>1.252478280694957</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.1229053690757672</v>
+        <v>-0.1194913310458847</v>
       </c>
       <c r="W37">
-        <v>0.2647810860280659</v>
+        <v>0.2639760558606196</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4342,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.4916214763030688</v>
+        <v>-0.4779653241835389</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4350,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1654675235329565</v>
+        <v>0.1673675235329566</v>
       </c>
       <c r="C38">
-        <v>1.227821508176386</v>
+        <v>0.9790125027370431</v>
       </c>
       <c r="D38">
-        <v>6.575221508176386</v>
+        <v>6.490312502737043</v>
       </c>
       <c r="E38">
-        <v>-2.0096</v>
+        <v>-1.8457</v>
       </c>
       <c r="F38">
-        <v>5.9004</v>
+        <v>6.0643</v>
       </c>
       <c r="G38">
         <v>0.553</v>
@@ -4386,37 +4397,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M38">
-        <v>1.39131432</v>
+        <v>1.42996194</v>
       </c>
       <c r="N38">
-        <v>-2.05631432</v>
+        <v>-2.09496194</v>
       </c>
       <c r="O38">
-        <v>-0.5140785800000001</v>
+        <v>-0.523740485</v>
       </c>
       <c r="P38">
-        <v>-1.54223574</v>
+        <v>-1.571221455</v>
       </c>
       <c r="Q38">
-        <v>0.69776426</v>
+        <v>0.6687785450000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1100564740986461</v>
+        <v>0.1110764181319579</v>
       </c>
       <c r="T38">
-        <v>1.252478280694957</v>
+        <v>1.272358888325036</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.1194913310458848</v>
+        <v>-0.1162618356122122</v>
       </c>
       <c r="W38">
-        <v>0.2639760558606196</v>
+        <v>0.2632145408373597</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4424,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.4779653241835389</v>
+        <v>-0.4650473424488486</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4432,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1673675235329566</v>
+        <v>0.1692675235329565</v>
       </c>
       <c r="C39">
-        <v>0.9790125027370431</v>
+        <v>0.7323684816594822</v>
       </c>
       <c r="D39">
-        <v>6.490312502737043</v>
+        <v>6.407568481659482</v>
       </c>
       <c r="E39">
-        <v>-1.8457</v>
+        <v>-1.6818</v>
       </c>
       <c r="F39">
-        <v>6.0643</v>
+        <v>6.2282</v>
       </c>
       <c r="G39">
         <v>0.553</v>
@@ -4468,37 +4479,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M39">
-        <v>1.42996194</v>
+        <v>1.46860956</v>
       </c>
       <c r="N39">
-        <v>-2.09496194</v>
+        <v>-2.13360956</v>
       </c>
       <c r="O39">
-        <v>-0.523740485</v>
+        <v>-0.5334023900000001</v>
       </c>
       <c r="P39">
-        <v>-1.571221455</v>
+        <v>-1.60020717</v>
       </c>
       <c r="Q39">
-        <v>0.6687785450000001</v>
+        <v>0.6397928299999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1110764181319579</v>
+        <v>0.1121292635856991</v>
       </c>
       <c r="T39">
-        <v>1.272358888325036</v>
+        <v>1.292880805878665</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.1162618356122122</v>
+        <v>-0.1132023136224171</v>
       </c>
       <c r="W39">
-        <v>0.2632145408373597</v>
+        <v>0.262493105552166</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4506,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.4650473424488486</v>
+        <v>-0.4528092544896685</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4514,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1692675235329565</v>
+        <v>0.1711675235329565</v>
       </c>
       <c r="C40">
-        <v>0.7323684816594822</v>
+        <v>0.4878076841170538</v>
       </c>
       <c r="D40">
-        <v>6.407568481659482</v>
+        <v>6.326907684117054</v>
       </c>
       <c r="E40">
-        <v>-1.6818</v>
+        <v>-1.5179</v>
       </c>
       <c r="F40">
-        <v>6.2282</v>
+        <v>6.3921</v>
       </c>
       <c r="G40">
         <v>0.553</v>
@@ -4550,37 +4561,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M40">
-        <v>1.46860956</v>
+        <v>1.50725718</v>
       </c>
       <c r="N40">
-        <v>-2.13360956</v>
+        <v>-2.17225718</v>
       </c>
       <c r="O40">
-        <v>-0.5334023900000001</v>
+        <v>-0.5430642950000001</v>
       </c>
       <c r="P40">
-        <v>-1.60020717</v>
+        <v>-1.629192885</v>
       </c>
       <c r="Q40">
-        <v>0.6397928299999998</v>
+        <v>0.6108071150000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1121292635856991</v>
+        <v>0.1132166285625139</v>
       </c>
       <c r="T40">
-        <v>1.292880805878665</v>
+        <v>1.314075573188152</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.1132023136224171</v>
+        <v>-0.1102996901962013</v>
       </c>
       <c r="W40">
-        <v>0.262493105552166</v>
+        <v>0.2618086669482643</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4588,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.4528092544896685</v>
+        <v>-0.4411987607848054</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4596,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1711675235329565</v>
+        <v>0.1730675235329566</v>
       </c>
       <c r="C41">
-        <v>0.4878076841170538</v>
+        <v>0.2452524150416995</v>
       </c>
       <c r="D41">
-        <v>6.326907684117054</v>
+        <v>6.2482524150417</v>
       </c>
       <c r="E41">
-        <v>-1.5179</v>
+        <v>-1.353999999999999</v>
       </c>
       <c r="F41">
-        <v>6.3921</v>
+        <v>6.556000000000001</v>
       </c>
       <c r="G41">
         <v>0.553</v>
@@ -4632,37 +4643,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M41">
-        <v>1.50725718</v>
+        <v>1.5459048</v>
       </c>
       <c r="N41">
-        <v>-2.17225718</v>
+        <v>-2.210904800000001</v>
       </c>
       <c r="O41">
-        <v>-0.5430642950000001</v>
+        <v>-0.5527262000000002</v>
       </c>
       <c r="P41">
-        <v>-1.629192885</v>
+        <v>-1.658178600000001</v>
       </c>
       <c r="Q41">
-        <v>0.6108071150000001</v>
+        <v>0.5818213999999997</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1132166285625139</v>
+        <v>0.1143402390385558</v>
       </c>
       <c r="T41">
-        <v>1.314075573188152</v>
+        <v>1.335976832741288</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.1102996901962013</v>
+        <v>-0.1075421979412963</v>
       </c>
       <c r="W41">
-        <v>0.2618086669482643</v>
+        <v>0.2611584502745577</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4670,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.4411987607848054</v>
+        <v>-0.4301687917651853</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4678,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1730675235329566</v>
+        <v>0.1749675235329566</v>
       </c>
       <c r="C42">
-        <v>0.2452524150416995</v>
+        <v>0.004628795502390481</v>
       </c>
       <c r="D42">
-        <v>6.2482524150417</v>
+        <v>6.171528795502391</v>
       </c>
       <c r="E42">
-        <v>-1.353999999999999</v>
+        <v>-1.190099999999999</v>
       </c>
       <c r="F42">
-        <v>6.556000000000001</v>
+        <v>6.719900000000001</v>
       </c>
       <c r="G42">
         <v>0.553</v>
@@ -4714,37 +4725,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M42">
-        <v>1.5459048</v>
+        <v>1.58455242</v>
       </c>
       <c r="N42">
-        <v>-2.210904800000001</v>
+        <v>-2.249552420000001</v>
       </c>
       <c r="O42">
-        <v>-0.5527262000000002</v>
+        <v>-0.5623881050000001</v>
       </c>
       <c r="P42">
-        <v>-1.658178600000001</v>
+        <v>-1.687164315</v>
       </c>
       <c r="Q42">
-        <v>0.5818213999999997</v>
+        <v>0.5528356849999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1143402390385558</v>
+        <v>0.115501938005311</v>
       </c>
       <c r="T42">
-        <v>1.335976832741288</v>
+        <v>1.358620507872496</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.1075421979412963</v>
+        <v>-0.1049192175037037</v>
       </c>
       <c r="W42">
-        <v>0.2611584502745577</v>
+        <v>0.2605399514873734</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4752,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.4301687917651853</v>
+        <v>-0.4196768700148148</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4760,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1749675235329566</v>
+        <v>0.1768675235329565</v>
       </c>
       <c r="C43">
-        <v>0.004628795502390481</v>
+        <v>-0.2341334687486034</v>
       </c>
       <c r="D43">
-        <v>6.171528795502391</v>
+        <v>6.096666531251397</v>
       </c>
       <c r="E43">
-        <v>-1.190099999999999</v>
+        <v>-1.026199999999999</v>
       </c>
       <c r="F43">
-        <v>6.719900000000001</v>
+        <v>6.883800000000001</v>
       </c>
       <c r="G43">
         <v>0.553</v>
@@ -4796,37 +4807,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M43">
-        <v>1.58455242</v>
+        <v>1.62320004</v>
       </c>
       <c r="N43">
-        <v>-2.249552420000001</v>
+        <v>-2.28820004</v>
       </c>
       <c r="O43">
-        <v>-0.5623881050000001</v>
+        <v>-0.5720500100000001</v>
       </c>
       <c r="P43">
-        <v>-1.687164315</v>
+        <v>-1.71615003</v>
       </c>
       <c r="Q43">
-        <v>0.5528356849999998</v>
+        <v>0.5238499699999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.115501938005311</v>
+        <v>0.1167036955571267</v>
       </c>
       <c r="T43">
-        <v>1.358620507872496</v>
+        <v>1.382044999387539</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.1049192175037037</v>
+        <v>-0.1024211408964727</v>
       </c>
       <c r="W43">
-        <v>0.2605399514873734</v>
+        <v>0.2599509050233882</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4834,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.4196768700148148</v>
+        <v>-0.4096845635858906</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4842,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1768675235329565</v>
+        <v>0.1787675235329566</v>
       </c>
       <c r="C44">
-        <v>-0.2341334687486025</v>
+        <v>-0.4711013020857555</v>
       </c>
       <c r="D44">
-        <v>6.096666531251397</v>
+        <v>6.023598697914244</v>
       </c>
       <c r="E44">
-        <v>-1.0262</v>
+        <v>-0.8623000000000003</v>
       </c>
       <c r="F44">
-        <v>6.8838</v>
+        <v>7.0477</v>
       </c>
       <c r="G44">
         <v>0.553</v>
@@ -4878,37 +4889,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M44">
-        <v>1.62320004</v>
+        <v>1.66184766</v>
       </c>
       <c r="N44">
-        <v>-2.28820004</v>
+        <v>-2.32684766</v>
       </c>
       <c r="O44">
-        <v>-0.5720500100000001</v>
+        <v>-0.5817119150000001</v>
       </c>
       <c r="P44">
-        <v>-1.71615003</v>
+        <v>-1.745135745</v>
       </c>
       <c r="Q44">
-        <v>0.5238499699999999</v>
+        <v>0.494864255</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1167036955571267</v>
+        <v>0.117947620040585</v>
       </c>
       <c r="T44">
-        <v>1.382044999387539</v>
+        <v>1.406291402885566</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.1024211408964727</v>
+        <v>-0.1000392538988803</v>
       </c>
       <c r="W44">
-        <v>0.2599509050233882</v>
+        <v>0.259389256069356</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4916,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.4096845635858908</v>
+        <v>-0.4001570155955212</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4924,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1787675235329566</v>
+        <v>0.1806675235329566</v>
       </c>
       <c r="C45">
-        <v>-0.4711013020857555</v>
+        <v>-0.706338458556421</v>
       </c>
       <c r="D45">
-        <v>6.023598697914244</v>
+        <v>5.95226154144358</v>
       </c>
       <c r="E45">
-        <v>-0.8623000000000003</v>
+        <v>-0.6983999999999995</v>
       </c>
       <c r="F45">
-        <v>7.0477</v>
+        <v>7.211600000000001</v>
       </c>
       <c r="G45">
         <v>0.553</v>
@@ -4960,37 +4971,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M45">
-        <v>1.66184766</v>
+        <v>1.70049528</v>
       </c>
       <c r="N45">
-        <v>-2.32684766</v>
+        <v>-2.36549528</v>
       </c>
       <c r="O45">
-        <v>-0.5817119150000001</v>
+        <v>-0.5913738200000001</v>
       </c>
       <c r="P45">
-        <v>-1.745135745</v>
+        <v>-1.77412146</v>
       </c>
       <c r="Q45">
-        <v>0.494864255</v>
+        <v>0.4658785400000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.117947620040585</v>
+        <v>0.1192359703984526</v>
       </c>
       <c r="T45">
-        <v>1.406291402885566</v>
+        <v>1.431403749365665</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.1000392538988803</v>
+        <v>-0.09776563449208753</v>
       </c>
       <c r="W45">
-        <v>0.259389256069356</v>
+        <v>0.2588531366132343</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4998,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.4001570155955212</v>
+        <v>-0.3910625379683501</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5006,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1806675235329566</v>
+        <v>0.1825675235329565</v>
       </c>
       <c r="C46">
-        <v>-0.706338458556421</v>
+        <v>-0.9399057074136481</v>
       </c>
       <c r="D46">
-        <v>5.95226154144358</v>
+        <v>5.882594292586353</v>
       </c>
       <c r="E46">
-        <v>-0.6983999999999995</v>
+        <v>-0.5344999999999995</v>
       </c>
       <c r="F46">
-        <v>7.211600000000001</v>
+        <v>7.375500000000001</v>
       </c>
       <c r="G46">
         <v>0.553</v>
@@ -5042,37 +5053,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M46">
-        <v>1.70049528</v>
+        <v>1.7391429</v>
       </c>
       <c r="N46">
-        <v>-2.36549528</v>
+        <v>-2.404142900000001</v>
       </c>
       <c r="O46">
-        <v>-0.5913738200000001</v>
+        <v>-0.6010357250000001</v>
       </c>
       <c r="P46">
-        <v>-1.77412146</v>
+        <v>-1.803107175000001</v>
       </c>
       <c r="Q46">
-        <v>0.4658785400000001</v>
+        <v>0.4368928249999997</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1192359703984526</v>
+        <v>0.1205711698602427</v>
       </c>
       <c r="T46">
-        <v>1.431403749365665</v>
+        <v>1.457429272081405</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.09776563449208753</v>
+        <v>-0.09559306483670781</v>
       </c>
       <c r="W46">
-        <v>0.2588531366132343</v>
+        <v>0.2583408446884957</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5080,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.3910625379683501</v>
+        <v>-0.3823722593468313</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5088,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1825675235329565</v>
+        <v>0.1844675235329566</v>
       </c>
       <c r="C47">
-        <v>-0.9399057074136481</v>
+        <v>-1.171861005770514</v>
       </c>
       <c r="D47">
-        <v>5.882594292586353</v>
+        <v>5.814538994229487</v>
       </c>
       <c r="E47">
-        <v>-0.5344999999999995</v>
+        <v>-0.3705999999999996</v>
       </c>
       <c r="F47">
-        <v>7.375500000000001</v>
+        <v>7.539400000000001</v>
       </c>
       <c r="G47">
         <v>0.553</v>
@@ -5124,37 +5135,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M47">
-        <v>1.7391429</v>
+        <v>1.77779052</v>
       </c>
       <c r="N47">
-        <v>-2.404142900000001</v>
+        <v>-2.44279052</v>
       </c>
       <c r="O47">
-        <v>-0.6010357250000001</v>
+        <v>-0.6106976300000001</v>
       </c>
       <c r="P47">
-        <v>-1.803107175000001</v>
+        <v>-1.83209289</v>
       </c>
       <c r="Q47">
-        <v>0.4368928249999997</v>
+        <v>0.40790711</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1205711698602427</v>
+        <v>0.1219558211539509</v>
       </c>
       <c r="T47">
-        <v>1.457429272081405</v>
+        <v>1.484418703045875</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.09559306483670781</v>
+        <v>-0.09351495473156199</v>
       </c>
       <c r="W47">
-        <v>0.2583408446884957</v>
+        <v>0.2578508263257023</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5162,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.3823722593468313</v>
+        <v>-0.3740598189262481</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5170,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1844675235329566</v>
+        <v>0.1863675235329565</v>
       </c>
       <c r="C48">
-        <v>-1.171861005770514</v>
+        <v>-1.402259659406948</v>
       </c>
       <c r="D48">
-        <v>5.814538994229487</v>
+        <v>5.748040340593053</v>
       </c>
       <c r="E48">
-        <v>-0.3705999999999996</v>
+        <v>-0.2066999999999997</v>
       </c>
       <c r="F48">
-        <v>7.539400000000001</v>
+        <v>7.7033</v>
       </c>
       <c r="G48">
         <v>0.553</v>
@@ -5206,37 +5217,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M48">
-        <v>1.77779052</v>
+        <v>1.81643814</v>
       </c>
       <c r="N48">
-        <v>-2.44279052</v>
+        <v>-2.481438140000001</v>
       </c>
       <c r="O48">
-        <v>-0.6106976300000001</v>
+        <v>-0.6203595350000002</v>
       </c>
       <c r="P48">
-        <v>-1.83209289</v>
+        <v>-1.861078605000001</v>
       </c>
       <c r="Q48">
-        <v>0.40790711</v>
+        <v>0.3789213949999997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1219558211539509</v>
+        <v>0.1233927234398745</v>
       </c>
       <c r="T48">
-        <v>1.484418703045875</v>
+        <v>1.512426603103344</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.09351495473156199</v>
+        <v>-0.09152527484365641</v>
       </c>
       <c r="W48">
-        <v>0.2578508263257023</v>
+        <v>0.2573816598081342</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5244,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.3740598189262481</v>
+        <v>-0.3661010993746259</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5252,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1863675235329565</v>
+        <v>0.1882675235329566</v>
       </c>
       <c r="C49">
-        <v>-1.402259659406948</v>
+        <v>-1.631154472666826</v>
       </c>
       <c r="D49">
-        <v>5.748040340593053</v>
+        <v>5.683045527333175</v>
       </c>
       <c r="E49">
-        <v>-0.2066999999999997</v>
+        <v>-0.04279999999999884</v>
       </c>
       <c r="F49">
-        <v>7.7033</v>
+        <v>7.867200000000001</v>
       </c>
       <c r="G49">
         <v>0.553</v>
@@ -5288,37 +5299,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M49">
-        <v>1.81643814</v>
+        <v>1.85508576</v>
       </c>
       <c r="N49">
-        <v>-2.481438140000001</v>
+        <v>-2.520085760000001</v>
       </c>
       <c r="O49">
-        <v>-0.6203595350000002</v>
+        <v>-0.6300214400000002</v>
       </c>
       <c r="P49">
-        <v>-1.861078605000001</v>
+        <v>-1.89006432</v>
       </c>
       <c r="Q49">
-        <v>0.3789213949999997</v>
+        <v>0.3499356799999997</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1233927234398745</v>
+        <v>0.1248848911983336</v>
       </c>
       <c r="T49">
-        <v>1.512426603103344</v>
+        <v>1.541511730086101</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.09152527484365641</v>
+        <v>-0.08961849828441357</v>
       </c>
       <c r="W49">
-        <v>0.2573816598081342</v>
+        <v>0.2569320418954647</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5326,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.3661010993746259</v>
+        <v>-0.3584739931376542</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5334,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1882675235329565</v>
+        <v>0.1901675235329566</v>
       </c>
       <c r="C50">
-        <v>-1.631154472666823</v>
+        <v>-1.85859588829917</v>
       </c>
       <c r="D50">
-        <v>5.683045527333177</v>
+        <v>5.619504111700831</v>
       </c>
       <c r="E50">
-        <v>-0.04279999999999973</v>
+        <v>0.1211000000000002</v>
       </c>
       <c r="F50">
-        <v>7.8672</v>
+        <v>8.0311</v>
       </c>
       <c r="G50">
         <v>0.553</v>
@@ -5370,37 +5381,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M50">
-        <v>1.85508576</v>
+        <v>1.89373338</v>
       </c>
       <c r="N50">
-        <v>-2.520085760000001</v>
+        <v>-2.558733380000001</v>
       </c>
       <c r="O50">
-        <v>-0.6300214400000002</v>
+        <v>-0.6396833450000001</v>
       </c>
       <c r="P50">
-        <v>-1.89006432</v>
+        <v>-1.919050035</v>
       </c>
       <c r="Q50">
-        <v>0.3499356799999997</v>
+        <v>0.3209499649999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1248848911983336</v>
+        <v>0.1264355753394774</v>
       </c>
       <c r="T50">
-        <v>1.541511730086101</v>
+        <v>1.571737450283868</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.08961849828441358</v>
+        <v>-0.0877895493398337</v>
       </c>
       <c r="W50">
-        <v>0.2569320418954647</v>
+        <v>0.2565007757343328</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5408,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.3584739931376544</v>
+        <v>-0.3511581973593347</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5416,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1901675235329566</v>
+        <v>0.1920675235329565</v>
       </c>
       <c r="C51">
-        <v>-1.85859588829917</v>
+        <v>-2.08463211802181</v>
       </c>
       <c r="D51">
-        <v>5.619504111700831</v>
+        <v>5.55736788197819</v>
       </c>
       <c r="E51">
-        <v>0.1211000000000002</v>
+        <v>0.2850000000000001</v>
       </c>
       <c r="F51">
-        <v>8.0311</v>
+        <v>8.195</v>
       </c>
       <c r="G51">
         <v>0.553</v>
@@ -5452,37 +5463,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M51">
-        <v>1.89373338</v>
+        <v>1.932381</v>
       </c>
       <c r="N51">
-        <v>-2.558733380000001</v>
+        <v>-2.597381</v>
       </c>
       <c r="O51">
-        <v>-0.6396833450000001</v>
+        <v>-0.6493452500000001</v>
       </c>
       <c r="P51">
-        <v>-1.919050035</v>
+        <v>-1.94803575</v>
       </c>
       <c r="Q51">
-        <v>0.3209499649999998</v>
+        <v>0.2919642499999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1264355753394774</v>
+        <v>0.1280482868462669</v>
       </c>
       <c r="T51">
-        <v>1.571737450283868</v>
+        <v>1.603172199289545</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.0877895493398337</v>
+        <v>-0.08603375835303703</v>
       </c>
       <c r="W51">
-        <v>0.2565007757343328</v>
+        <v>0.2560867602196462</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5490,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.3511581973593347</v>
+        <v>-0.3441350334121482</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5498,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1920675235329565</v>
+        <v>0.1939675235329565</v>
       </c>
       <c r="C52">
-        <v>-2.08463211802181</v>
+        <v>-2.309309264517733</v>
       </c>
       <c r="D52">
-        <v>5.55736788197819</v>
+        <v>5.496590735482267</v>
       </c>
       <c r="E52">
-        <v>0.2850000000000001</v>
+        <v>0.4489000000000001</v>
       </c>
       <c r="F52">
-        <v>8.195</v>
+        <v>8.3589</v>
       </c>
       <c r="G52">
         <v>0.553</v>
@@ -5534,37 +5545,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M52">
-        <v>1.932381</v>
+        <v>1.97102862</v>
       </c>
       <c r="N52">
-        <v>-2.597381</v>
+        <v>-2.63602862</v>
       </c>
       <c r="O52">
-        <v>-0.6493452500000001</v>
+        <v>-0.6590071550000001</v>
       </c>
       <c r="P52">
-        <v>-1.94803575</v>
+        <v>-1.977021465</v>
       </c>
       <c r="Q52">
-        <v>0.2919642499999999</v>
+        <v>0.262978535</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1280482868462669</v>
+        <v>0.1297268233125173</v>
       </c>
       <c r="T52">
-        <v>1.603172199289545</v>
+        <v>1.635889999275046</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.08603375835303703</v>
+        <v>-0.08434682191474219</v>
       </c>
       <c r="W52">
-        <v>0.2560867602196462</v>
+        <v>0.2556889806074962</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5572,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.3441350334121482</v>
+        <v>-0.3373872876589685</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5580,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1939675235329565</v>
+        <v>0.1958675235329566</v>
       </c>
       <c r="C53">
-        <v>-2.309309264517733</v>
+        <v>-2.532671435512857</v>
       </c>
       <c r="D53">
-        <v>5.496590735482267</v>
+        <v>5.437128564487143</v>
       </c>
       <c r="E53">
-        <v>0.4489000000000001</v>
+        <v>0.6128</v>
       </c>
       <c r="F53">
-        <v>8.3589</v>
+        <v>8.5228</v>
       </c>
       <c r="G53">
         <v>0.553</v>
@@ -5616,37 +5627,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M53">
-        <v>1.97102862</v>
+        <v>2.00967624</v>
       </c>
       <c r="N53">
-        <v>-2.63602862</v>
+        <v>-2.67467624</v>
       </c>
       <c r="O53">
-        <v>-0.6590071550000001</v>
+        <v>-0.66866906</v>
       </c>
       <c r="P53">
-        <v>-1.977021465</v>
+        <v>-2.00600718</v>
       </c>
       <c r="Q53">
-        <v>0.262978535</v>
+        <v>0.2339928200000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1297268233125173</v>
+        <v>0.1314752987981947</v>
       </c>
       <c r="T53">
-        <v>1.635889999275046</v>
+        <v>1.669971040926609</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.08434682191474219</v>
+        <v>-0.08272476764715099</v>
       </c>
       <c r="W53">
-        <v>0.2556889806074962</v>
+        <v>0.2553065002111982</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5654,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.3373872876589685</v>
+        <v>-0.3308990705886039</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5662,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1958675235329566</v>
+        <v>0.1977675235329566</v>
       </c>
       <c r="C54">
-        <v>-2.532671435512857</v>
+        <v>-2.754760850528524</v>
       </c>
       <c r="D54">
-        <v>5.437128564487143</v>
+        <v>5.378939149471476</v>
       </c>
       <c r="E54">
-        <v>0.6128</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="F54">
-        <v>8.5228</v>
+        <v>8.6867</v>
       </c>
       <c r="G54">
         <v>0.553</v>
@@ -5698,37 +5709,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M54">
-        <v>2.00967624</v>
+        <v>2.04832386</v>
       </c>
       <c r="N54">
-        <v>-2.67467624</v>
+        <v>-2.71332386</v>
       </c>
       <c r="O54">
-        <v>-0.66866906</v>
+        <v>-0.678330965</v>
       </c>
       <c r="P54">
-        <v>-2.00600718</v>
+        <v>-2.034992895</v>
       </c>
       <c r="Q54">
-        <v>0.2339928200000001</v>
+        <v>0.205007105</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1314752987981947</v>
+        <v>0.1332981774960287</v>
       </c>
       <c r="T54">
-        <v>1.669971040926609</v>
+        <v>1.705502339669729</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.08272476764715099</v>
+        <v>-0.08116392297456325</v>
       </c>
       <c r="W54">
-        <v>0.2553065002111982</v>
+        <v>0.254938453037402</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5736,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.3308990705886039</v>
+        <v>-0.3246556918982528</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5744,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1977675235329566</v>
+        <v>0.1996675235329566</v>
       </c>
       <c r="C55">
-        <v>-2.754760850528524</v>
+        <v>-2.975617940851607</v>
       </c>
       <c r="D55">
-        <v>5.378939149471476</v>
+        <v>5.321982059148393</v>
       </c>
       <c r="E55">
-        <v>0.7766999999999999</v>
+        <v>0.9405999999999999</v>
       </c>
       <c r="F55">
-        <v>8.6867</v>
+        <v>8.8506</v>
       </c>
       <c r="G55">
         <v>0.553</v>
@@ -5780,37 +5791,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M55">
-        <v>2.04832386</v>
+        <v>2.08697148</v>
       </c>
       <c r="N55">
-        <v>-2.71332386</v>
+        <v>-2.75197148</v>
       </c>
       <c r="O55">
-        <v>-0.678330965</v>
+        <v>-0.68799287</v>
       </c>
       <c r="P55">
-        <v>-2.034992895</v>
+        <v>-2.06397861</v>
       </c>
       <c r="Q55">
-        <v>0.205007105</v>
+        <v>0.1760213900000003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1332981774960287</v>
+        <v>0.1352003117894206</v>
       </c>
       <c r="T55">
-        <v>1.705502339669729</v>
+        <v>1.742578477488636</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.08116392297456325</v>
+        <v>-0.07966088736392318</v>
       </c>
       <c r="W55">
-        <v>0.254938453037402</v>
+        <v>0.2545840372404131</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5818,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.3246556918982528</v>
+        <v>-0.3186435494556927</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5826,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1996675235329566</v>
+        <v>0.2015675235329565</v>
       </c>
       <c r="C56">
-        <v>-2.975617940851607</v>
+        <v>-3.195281443219748</v>
       </c>
       <c r="D56">
-        <v>5.321982059148393</v>
+        <v>5.266218556780254</v>
       </c>
       <c r="E56">
-        <v>0.9405999999999999</v>
+        <v>1.104500000000002</v>
       </c>
       <c r="F56">
-        <v>8.8506</v>
+        <v>9.014500000000002</v>
       </c>
       <c r="G56">
         <v>0.553</v>
@@ -5862,37 +5873,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M56">
-        <v>2.08697148</v>
+        <v>2.125619100000001</v>
       </c>
       <c r="N56">
-        <v>-2.75197148</v>
+        <v>-2.790619100000001</v>
       </c>
       <c r="O56">
-        <v>-0.68799287</v>
+        <v>-0.6976547750000002</v>
       </c>
       <c r="P56">
-        <v>-2.06397861</v>
+        <v>-2.092964325000001</v>
       </c>
       <c r="Q56">
-        <v>0.1760213900000003</v>
+        <v>0.1470356749999997</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1352003117894206</v>
+        <v>0.1371869853847411</v>
       </c>
       <c r="T56">
-        <v>1.742578477488636</v>
+        <v>1.78130244365505</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.07966088736392318</v>
+        <v>-0.07821250759367002</v>
       </c>
       <c r="W56">
-        <v>0.2545840372404131</v>
+        <v>0.2542425092905874</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5900,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.3186435494556927</v>
+        <v>-0.31285003037468</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5908,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2015675235329565</v>
+        <v>0.2034675235329566</v>
       </c>
       <c r="C57">
-        <v>-3.195281443219748</v>
+        <v>-3.413788487677863</v>
       </c>
       <c r="D57">
-        <v>5.266218556780254</v>
+        <v>5.211611512322139</v>
       </c>
       <c r="E57">
-        <v>1.104500000000002</v>
+        <v>1.268400000000002</v>
       </c>
       <c r="F57">
-        <v>9.014500000000002</v>
+        <v>9.178400000000002</v>
       </c>
       <c r="G57">
         <v>0.553</v>
@@ -5944,37 +5955,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M57">
-        <v>2.125619100000001</v>
+        <v>2.164266720000001</v>
       </c>
       <c r="N57">
-        <v>-2.790619100000001</v>
+        <v>-2.829266720000001</v>
       </c>
       <c r="O57">
-        <v>-0.6976547750000002</v>
+        <v>-0.7073166800000001</v>
       </c>
       <c r="P57">
-        <v>-2.092964325000001</v>
+        <v>-2.121950040000001</v>
       </c>
       <c r="Q57">
-        <v>0.1470356749999997</v>
+        <v>0.1180499599999996</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1371869853847411</v>
+        <v>0.1392639623253034</v>
       </c>
       <c r="T57">
-        <v>1.78130244365505</v>
+        <v>1.821786590101756</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.07821250759367002</v>
+        <v>-0.07681585567235448</v>
       </c>
       <c r="W57">
-        <v>0.2542425092905874</v>
+        <v>0.2539131787675412</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5982,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.31285003037468</v>
+        <v>-0.3072634226894178</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5990,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2034675235329566</v>
+        <v>0.2053675235329566</v>
       </c>
       <c r="C58">
-        <v>-3.413788487677863</v>
+        <v>-3.631174680024696</v>
       </c>
       <c r="D58">
-        <v>5.211611512322139</v>
+        <v>5.158125319975306</v>
       </c>
       <c r="E58">
-        <v>1.268400000000002</v>
+        <v>1.432300000000001</v>
       </c>
       <c r="F58">
-        <v>9.178400000000002</v>
+        <v>9.342300000000002</v>
       </c>
       <c r="G58">
         <v>0.553</v>
@@ -6026,37 +6037,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M58">
-        <v>2.164266720000001</v>
+        <v>2.20291434</v>
       </c>
       <c r="N58">
-        <v>-2.829266720000001</v>
+        <v>-2.86791434</v>
       </c>
       <c r="O58">
-        <v>-0.7073166800000001</v>
+        <v>-0.7169785850000001</v>
       </c>
       <c r="P58">
-        <v>-2.121950040000001</v>
+        <v>-2.150935755</v>
       </c>
       <c r="Q58">
-        <v>0.1180499599999996</v>
+        <v>0.08906424499999988</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1392639623253034</v>
+        <v>0.1414375428444965</v>
       </c>
       <c r="T58">
-        <v>1.821786590101756</v>
+        <v>1.864153720104123</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.07681585567235448</v>
+        <v>-0.07546820908161142</v>
       </c>
       <c r="W58">
-        <v>0.2539131787675412</v>
+        <v>0.253595403701444</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6064,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.3072634226894178</v>
+        <v>-0.3018728363264456</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6072,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2053675235329566</v>
+        <v>0.2072675235329566</v>
       </c>
       <c r="C59">
-        <v>-3.631174680024696</v>
+        <v>-3.847474179234108</v>
       </c>
       <c r="D59">
-        <v>5.158125319975306</v>
+        <v>5.105725820765894</v>
       </c>
       <c r="E59">
-        <v>1.432300000000001</v>
+        <v>1.596200000000001</v>
       </c>
       <c r="F59">
-        <v>9.342300000000002</v>
+        <v>9.506200000000002</v>
       </c>
       <c r="G59">
         <v>0.553</v>
@@ -6108,37 +6119,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M59">
-        <v>2.20291434</v>
+        <v>2.24156196</v>
       </c>
       <c r="N59">
-        <v>-2.86791434</v>
+        <v>-2.90656196</v>
       </c>
       <c r="O59">
-        <v>-0.7169785850000001</v>
+        <v>-0.7266404900000001</v>
       </c>
       <c r="P59">
-        <v>-2.150935755</v>
+        <v>-2.17992147</v>
       </c>
       <c r="Q59">
-        <v>0.08906424499999988</v>
+        <v>0.06007853000000019</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1414375428444965</v>
+        <v>0.1437146271979369</v>
       </c>
       <c r="T59">
-        <v>1.864153720104123</v>
+        <v>1.908538332487554</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.07546820908161142</v>
+        <v>-0.07416703306296295</v>
       </c>
       <c r="W59">
-        <v>0.253595403701444</v>
+        <v>0.2532885863962467</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6146,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.3018728363264456</v>
+        <v>-0.2966681322518516</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6154,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2072675235329565</v>
+        <v>0.2091675235329565</v>
       </c>
       <c r="C60">
-        <v>-3.847474179234104</v>
+        <v>-4.062719770204835</v>
       </c>
       <c r="D60">
-        <v>5.105725820765896</v>
+        <v>5.054380229795165</v>
       </c>
       <c r="E60">
-        <v>1.5962</v>
+        <v>1.7601</v>
       </c>
       <c r="F60">
-        <v>9.5062</v>
+        <v>9.6701</v>
       </c>
       <c r="G60">
         <v>0.553</v>
@@ -6190,37 +6201,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M60">
-        <v>2.24156196</v>
+        <v>2.28020958</v>
       </c>
       <c r="N60">
-        <v>-2.90656196</v>
+        <v>-2.94520958</v>
       </c>
       <c r="O60">
-        <v>-0.7266404900000001</v>
+        <v>-0.7363023950000001</v>
       </c>
       <c r="P60">
-        <v>-2.17992147</v>
+        <v>-2.208907185</v>
       </c>
       <c r="Q60">
-        <v>0.06007853000000019</v>
+        <v>0.03109281500000005</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1437146271979368</v>
+        <v>0.1461027888369109</v>
       </c>
       <c r="T60">
-        <v>1.908538332487553</v>
+        <v>1.955088047914079</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.07416703306296298</v>
+        <v>-0.07290996470596359</v>
       </c>
       <c r="W60">
-        <v>0.2532885863962467</v>
+        <v>0.2529921696776662</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6228,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.2966681322518521</v>
+        <v>-0.2916398588238542</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6236,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2091675235329565</v>
+        <v>0.2110675235329566</v>
       </c>
       <c r="C61">
-        <v>-4.062719770204835</v>
+        <v>-4.276942932164349</v>
       </c>
       <c r="D61">
-        <v>5.054380229795165</v>
+        <v>5.00405706783565</v>
       </c>
       <c r="E61">
-        <v>1.7601</v>
+        <v>1.923999999999999</v>
       </c>
       <c r="F61">
-        <v>9.6701</v>
+        <v>9.834</v>
       </c>
       <c r="G61">
         <v>0.553</v>
@@ -6272,37 +6283,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M61">
-        <v>2.28020958</v>
+        <v>2.3188572</v>
       </c>
       <c r="N61">
-        <v>-2.94520958</v>
+        <v>-2.9838572</v>
       </c>
       <c r="O61">
-        <v>-0.7363023950000001</v>
+        <v>-0.7459643</v>
       </c>
       <c r="P61">
-        <v>-2.208907185</v>
+        <v>-2.2378929</v>
       </c>
       <c r="Q61">
-        <v>0.03109281500000005</v>
+        <v>0.002107099999999917</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1461027888369109</v>
+        <v>0.1486103585578337</v>
       </c>
       <c r="T61">
-        <v>1.955088047914079</v>
+        <v>2.003965249111931</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.07290996470596359</v>
+        <v>-0.07169479862753086</v>
       </c>
       <c r="W61">
-        <v>0.2529921696776662</v>
+        <v>0.2527056335163718</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6310,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.2916398588238542</v>
+        <v>-0.2867791945101235</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6318,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2110675235329566</v>
+        <v>0.2129675235329566</v>
       </c>
       <c r="C62">
-        <v>-4.276942932164349</v>
+        <v>-4.490173903026649</v>
       </c>
       <c r="D62">
-        <v>5.00405706783565</v>
+        <v>4.95472609697335</v>
       </c>
       <c r="E62">
-        <v>1.923999999999999</v>
+        <v>2.087899999999999</v>
       </c>
       <c r="F62">
-        <v>9.834</v>
+        <v>9.9979</v>
       </c>
       <c r="G62">
         <v>0.553</v>
@@ -6354,37 +6365,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M62">
-        <v>2.3188572</v>
+        <v>2.35750482</v>
       </c>
       <c r="N62">
-        <v>-2.9838572</v>
+        <v>-3.02250482</v>
       </c>
       <c r="O62">
-        <v>-0.7459643</v>
+        <v>-0.755626205</v>
       </c>
       <c r="P62">
-        <v>-2.2378929</v>
+        <v>-2.266878615</v>
       </c>
       <c r="Q62">
-        <v>0.002107099999999917</v>
+        <v>-0.02687861499999977</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1486103585578337</v>
+        <v>0.1512465215977782</v>
       </c>
       <c r="T62">
-        <v>2.003965249111931</v>
+        <v>2.055348973448135</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.07169479862753086</v>
+        <v>-0.07051947405986643</v>
       </c>
       <c r="W62">
-        <v>0.2527056335163718</v>
+        <v>0.2524284919833165</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6392,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.2867791945101235</v>
+        <v>-0.2820778962394657</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6400,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2129675235329566</v>
+        <v>0.2148675235329566</v>
       </c>
       <c r="C63">
-        <v>-4.490173903026649</v>
+        <v>-4.70244173998054</v>
       </c>
       <c r="D63">
-        <v>4.95472609697335</v>
+        <v>4.906358260019459</v>
       </c>
       <c r="E63">
-        <v>2.087899999999999</v>
+        <v>2.251799999999999</v>
       </c>
       <c r="F63">
-        <v>9.9979</v>
+        <v>10.1618</v>
       </c>
       <c r="G63">
         <v>0.553</v>
@@ -6436,37 +6447,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M63">
-        <v>2.35750482</v>
+        <v>2.39615244</v>
       </c>
       <c r="N63">
-        <v>-3.02250482</v>
+        <v>-3.06115244</v>
       </c>
       <c r="O63">
-        <v>-0.755626205</v>
+        <v>-0.76528811</v>
       </c>
       <c r="P63">
-        <v>-2.266878615</v>
+        <v>-2.29586433</v>
       </c>
       <c r="Q63">
-        <v>-0.02687861499999977</v>
+        <v>-0.05586432999999946</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1512465215977782</v>
+        <v>0.1540214300608776</v>
       </c>
       <c r="T63">
-        <v>2.055348973448135</v>
+        <v>2.109437104328349</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.07051947405986643</v>
+        <v>-0.06938206318793309</v>
       </c>
       <c r="W63">
-        <v>0.2524284919833165</v>
+        <v>0.2521602904997147</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6474,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.2820778962394657</v>
+        <v>-0.2775282527517322</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6482,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2148675235329566</v>
+        <v>0.2167675235329566</v>
       </c>
       <c r="C64">
-        <v>-4.70244173998054</v>
+        <v>-4.913774376563423</v>
       </c>
       <c r="D64">
-        <v>4.906358260019459</v>
+        <v>4.858925623436578</v>
       </c>
       <c r="E64">
-        <v>2.251799999999999</v>
+        <v>2.415700000000001</v>
       </c>
       <c r="F64">
-        <v>10.1618</v>
+        <v>10.3257</v>
       </c>
       <c r="G64">
         <v>0.553</v>
@@ -6518,37 +6529,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M64">
-        <v>2.39615244</v>
+        <v>2.434800060000001</v>
       </c>
       <c r="N64">
-        <v>-3.06115244</v>
+        <v>-3.099800060000001</v>
       </c>
       <c r="O64">
-        <v>-0.76528811</v>
+        <v>-0.7749500150000002</v>
       </c>
       <c r="P64">
-        <v>-2.29586433</v>
+        <v>-2.324850045000001</v>
       </c>
       <c r="Q64">
-        <v>-0.05586432999999946</v>
+        <v>-0.08485004500000048</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1540214300608776</v>
+        <v>0.1569463335760364</v>
       </c>
       <c r="T64">
-        <v>2.109437104328349</v>
+        <v>2.166448917958844</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.06938206318793309</v>
+        <v>-0.06828076059764843</v>
       </c>
       <c r="W64">
-        <v>0.2521602904997147</v>
+        <v>0.2519006033489256</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6556,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.2775282527517322</v>
+        <v>-0.2731230423905937</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6564,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2167675235329566</v>
+        <v>0.2186675235329566</v>
       </c>
       <c r="C65">
-        <v>-4.913774376563423</v>
+        <v>-5.124198676456219</v>
       </c>
       <c r="D65">
-        <v>4.858925623436578</v>
+        <v>4.812401323543782</v>
       </c>
       <c r="E65">
-        <v>2.415700000000001</v>
+        <v>2.579600000000001</v>
       </c>
       <c r="F65">
-        <v>10.3257</v>
+        <v>10.4896</v>
       </c>
       <c r="G65">
         <v>0.553</v>
@@ -6600,37 +6611,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M65">
-        <v>2.434800060000001</v>
+        <v>2.47344768</v>
       </c>
       <c r="N65">
-        <v>-3.099800060000001</v>
+        <v>-3.138447680000001</v>
       </c>
       <c r="O65">
-        <v>-0.7749500150000002</v>
+        <v>-0.7846119200000001</v>
       </c>
       <c r="P65">
-        <v>-2.324850045000001</v>
+        <v>-2.35383576</v>
       </c>
       <c r="Q65">
-        <v>-0.08485004500000048</v>
+        <v>-0.1138357600000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1569463335760364</v>
+        <v>0.1600337317309263</v>
       </c>
       <c r="T65">
-        <v>2.166448917958844</v>
+        <v>2.226628054568812</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.06828076059764843</v>
+        <v>-0.06721387371331017</v>
       </c>
       <c r="W65">
-        <v>0.2519006033489256</v>
+        <v>0.2516490314215986</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6638,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.2731230423905937</v>
+        <v>-0.2688554948532407</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6646,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2186675235329566</v>
+        <v>0.2205675235329565</v>
       </c>
       <c r="C66">
-        <v>-5.124198676456219</v>
+        <v>-5.333740484217059</v>
       </c>
       <c r="D66">
-        <v>4.812401323543782</v>
+        <v>4.766759515782942</v>
       </c>
       <c r="E66">
-        <v>2.579600000000001</v>
+        <v>2.743500000000001</v>
       </c>
       <c r="F66">
-        <v>10.4896</v>
+        <v>10.6535</v>
       </c>
       <c r="G66">
         <v>0.553</v>
@@ -6682,37 +6693,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M66">
-        <v>2.47344768</v>
+        <v>2.5120953</v>
       </c>
       <c r="N66">
-        <v>-3.138447680000001</v>
+        <v>-3.1770953</v>
       </c>
       <c r="O66">
-        <v>-0.7846119200000001</v>
+        <v>-0.7942738250000001</v>
       </c>
       <c r="P66">
-        <v>-2.35383576</v>
+        <v>-2.382821475</v>
       </c>
       <c r="Q66">
-        <v>-0.1138357600000002</v>
+        <v>-0.1428214749999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1600337317309263</v>
+        <v>0.1632975526375242</v>
       </c>
       <c r="T66">
-        <v>2.226628054568812</v>
+        <v>2.290245998985064</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.06721387371331017</v>
+        <v>-0.06617981411772079</v>
       </c>
       <c r="W66">
-        <v>0.2516490314215986</v>
+        <v>0.2514052001689586</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6720,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.2688554948532407</v>
+        <v>-0.2647192564708831</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6728,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2205675235329565</v>
+        <v>0.2224675235329566</v>
       </c>
       <c r="C67">
-        <v>-5.333740484217059</v>
+        <v>-5.542424673155105</v>
       </c>
       <c r="D67">
-        <v>4.766759515782942</v>
+        <v>4.721975326844896</v>
       </c>
       <c r="E67">
-        <v>2.743500000000001</v>
+        <v>2.907400000000001</v>
       </c>
       <c r="F67">
-        <v>10.6535</v>
+        <v>10.8174</v>
       </c>
       <c r="G67">
         <v>0.553</v>
@@ -6764,37 +6775,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M67">
-        <v>2.5120953</v>
+        <v>2.55074292</v>
       </c>
       <c r="N67">
-        <v>-3.1770953</v>
+        <v>-3.21574292</v>
       </c>
       <c r="O67">
-        <v>-0.7942738250000001</v>
+        <v>-0.8039357300000001</v>
       </c>
       <c r="P67">
-        <v>-2.382821475</v>
+        <v>-2.41180719</v>
       </c>
       <c r="Q67">
-        <v>-0.1428214749999999</v>
+        <v>-0.17180719</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1632975526375242</v>
+        <v>0.1667533630092161</v>
       </c>
       <c r="T67">
-        <v>2.290245998985064</v>
+        <v>2.357606175425802</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.06617981411772079</v>
+        <v>-0.06517708966139169</v>
       </c>
       <c r="W67">
-        <v>0.2514052001689586</v>
+        <v>0.2511687577421562</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6802,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.2647192564708831</v>
+        <v>-0.2607083586455667</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6810,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2224675235329566</v>
+        <v>0.2243675235329566</v>
       </c>
       <c r="C68">
-        <v>-5.542424673155105</v>
+        <v>-5.750275190530791</v>
       </c>
       <c r="D68">
-        <v>4.721975326844896</v>
+        <v>4.67802480946921</v>
       </c>
       <c r="E68">
-        <v>2.907400000000001</v>
+        <v>3.071300000000001</v>
       </c>
       <c r="F68">
-        <v>10.8174</v>
+        <v>10.9813</v>
       </c>
       <c r="G68">
         <v>0.553</v>
@@ -6846,37 +6857,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M68">
-        <v>2.55074292</v>
+        <v>2.58939054</v>
       </c>
       <c r="N68">
-        <v>-3.21574292</v>
+        <v>-3.25439054</v>
       </c>
       <c r="O68">
-        <v>-0.8039357300000001</v>
+        <v>-0.813597635</v>
       </c>
       <c r="P68">
-        <v>-2.41180719</v>
+        <v>-2.440792905</v>
       </c>
       <c r="Q68">
-        <v>-0.17180719</v>
+        <v>-0.2007929050000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1667533630092161</v>
+        <v>0.1704186164337378</v>
       </c>
       <c r="T68">
-        <v>2.357606175425802</v>
+        <v>2.429048786802341</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.06517708966139169</v>
+        <v>-0.06420429727838585</v>
       </c>
       <c r="W68">
-        <v>0.2511687577421562</v>
+        <v>0.2509393732982434</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6884,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.2607083586455667</v>
+        <v>-0.2568171891135433</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6892,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2243675235329566</v>
+        <v>0.2262675235329566</v>
       </c>
       <c r="C69">
-        <v>-5.750275190530791</v>
+        <v>-5.957315100255109</v>
       </c>
       <c r="D69">
-        <v>4.67802480946921</v>
+        <v>4.634884899744892</v>
       </c>
       <c r="E69">
-        <v>3.071300000000001</v>
+        <v>3.235200000000001</v>
       </c>
       <c r="F69">
-        <v>10.9813</v>
+        <v>11.1452</v>
       </c>
       <c r="G69">
         <v>0.553</v>
@@ -6928,37 +6939,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M69">
-        <v>2.58939054</v>
+        <v>2.62803816</v>
       </c>
       <c r="N69">
-        <v>-3.25439054</v>
+        <v>-3.293038160000001</v>
       </c>
       <c r="O69">
-        <v>-0.813597635</v>
+        <v>-0.8232595400000002</v>
       </c>
       <c r="P69">
-        <v>-2.440792905</v>
+        <v>-2.46977862</v>
       </c>
       <c r="Q69">
-        <v>-0.2007929050000001</v>
+        <v>-0.2297786200000003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1704186164337378</v>
+        <v>0.1743129481972922</v>
       </c>
       <c r="T69">
-        <v>2.429048786802341</v>
+        <v>2.504956561389915</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.06420429727838585</v>
+        <v>-0.06326011643605664</v>
       </c>
       <c r="W69">
-        <v>0.2509393732982434</v>
+        <v>0.2507167354556222</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6966,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.2568171891135433</v>
+        <v>-0.2530404657442267</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6974,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2262675235329566</v>
+        <v>0.2281675235329566</v>
       </c>
       <c r="C70">
-        <v>-5.957315100255109</v>
+        <v>-6.163566623247884</v>
       </c>
       <c r="D70">
-        <v>4.634884899744892</v>
+        <v>4.592533376752117</v>
       </c>
       <c r="E70">
-        <v>3.235200000000001</v>
+        <v>3.399100000000001</v>
       </c>
       <c r="F70">
-        <v>11.1452</v>
+        <v>11.3091</v>
       </c>
       <c r="G70">
         <v>0.553</v>
@@ -7010,37 +7021,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M70">
-        <v>2.62803816</v>
+        <v>2.66668578</v>
       </c>
       <c r="N70">
-        <v>-3.293038160000001</v>
+        <v>-3.331685780000001</v>
       </c>
       <c r="O70">
-        <v>-0.8232595400000002</v>
+        <v>-0.8329214450000002</v>
       </c>
       <c r="P70">
-        <v>-2.46977862</v>
+        <v>-2.498764335000001</v>
       </c>
       <c r="Q70">
-        <v>-0.2297786200000003</v>
+        <v>-0.2587643350000004</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1743129481972922</v>
+        <v>0.1784585271713983</v>
       </c>
       <c r="T70">
-        <v>2.504956561389915</v>
+        <v>2.585761611757331</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.06326011643605664</v>
+        <v>-0.06234330315437465</v>
       </c>
       <c r="W70">
-        <v>0.2507167354556222</v>
+        <v>0.2505005508838016</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7048,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.2530404657442267</v>
+        <v>-0.2493732126174988</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7056,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2281675235329566</v>
+        <v>0.2300675235329566</v>
       </c>
       <c r="C71">
-        <v>-6.163566623247884</v>
+        <v>-6.369051175603428</v>
       </c>
       <c r="D71">
-        <v>4.592533376752117</v>
+        <v>4.550948824396573</v>
       </c>
       <c r="E71">
-        <v>3.399100000000001</v>
+        <v>3.563000000000001</v>
       </c>
       <c r="F71">
-        <v>11.3091</v>
+        <v>11.473</v>
       </c>
       <c r="G71">
         <v>0.553</v>
@@ -7092,37 +7103,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M71">
-        <v>2.66668578</v>
+        <v>2.7053334</v>
       </c>
       <c r="N71">
-        <v>-3.331685780000001</v>
+        <v>-3.370333400000001</v>
       </c>
       <c r="O71">
-        <v>-0.8329214450000002</v>
+        <v>-0.8425833500000002</v>
       </c>
       <c r="P71">
-        <v>-2.498764335000001</v>
+        <v>-2.527750050000001</v>
       </c>
       <c r="Q71">
-        <v>-0.2587643350000004</v>
+        <v>-0.2877500500000005</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1784585271713983</v>
+        <v>0.1828804780771116</v>
       </c>
       <c r="T71">
-        <v>2.585761611757331</v>
+        <v>2.671953665482576</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.06234330315437465</v>
+        <v>-0.06145268453788359</v>
       </c>
       <c r="W71">
-        <v>0.2505005508838016</v>
+        <v>0.250290543014033</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7130,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.2493732126174988</v>
+        <v>-0.2458107381515344</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7138,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2300675235329566</v>
+        <v>0.2319675235329565</v>
       </c>
       <c r="C72">
-        <v>-6.369051175603428</v>
+        <v>-6.573789404701318</v>
       </c>
       <c r="D72">
-        <v>4.550948824396573</v>
+        <v>4.510110595298684</v>
       </c>
       <c r="E72">
-        <v>3.563000000000001</v>
+        <v>3.726900000000002</v>
       </c>
       <c r="F72">
-        <v>11.473</v>
+        <v>11.6369</v>
       </c>
       <c r="G72">
         <v>0.553</v>
@@ -7174,37 +7185,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M72">
-        <v>2.7053334</v>
+        <v>2.743981020000001</v>
       </c>
       <c r="N72">
-        <v>-3.370333400000001</v>
+        <v>-3.408981020000001</v>
       </c>
       <c r="O72">
-        <v>-0.8425833500000002</v>
+        <v>-0.8522452550000001</v>
       </c>
       <c r="P72">
-        <v>-2.527750050000001</v>
+        <v>-2.556735765</v>
       </c>
       <c r="Q72">
-        <v>-0.2877500500000005</v>
+        <v>-0.3167357650000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1828804780771116</v>
+        <v>0.1876073911142534</v>
       </c>
       <c r="T72">
-        <v>2.671953665482576</v>
+        <v>2.764089998775078</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.06145268453788359</v>
+        <v>-0.06058715376974438</v>
       </c>
       <c r="W72">
-        <v>0.250290543014033</v>
+        <v>0.2500864508589057</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7212,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.2458107381515344</v>
+        <v>-0.2423486150789775</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7220,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2319675235329565</v>
+        <v>0.2338675235329566</v>
       </c>
       <c r="C73">
-        <v>-6.573789404701317</v>
+        <v>-6.777801223390174</v>
       </c>
       <c r="D73">
-        <v>4.510110595298684</v>
+        <v>4.469998776609827</v>
       </c>
       <c r="E73">
-        <v>3.726900000000001</v>
+        <v>3.8908</v>
       </c>
       <c r="F73">
-        <v>11.6369</v>
+        <v>11.8008</v>
       </c>
       <c r="G73">
         <v>0.553</v>
@@ -7256,37 +7267,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M73">
-        <v>2.74398102</v>
+        <v>2.78262864</v>
       </c>
       <c r="N73">
-        <v>-3.408981020000001</v>
+        <v>-3.44762864</v>
       </c>
       <c r="O73">
-        <v>-0.8522452550000001</v>
+        <v>-0.8619071600000001</v>
       </c>
       <c r="P73">
-        <v>-2.556735765</v>
+        <v>-2.58572148</v>
       </c>
       <c r="Q73">
-        <v>-0.3167357650000002</v>
+        <v>-0.3457214799999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1876073911142533</v>
+        <v>0.1926719407969052</v>
       </c>
       <c r="T73">
-        <v>2.764089998775077</v>
+        <v>2.86280749873133</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.06058715376974439</v>
+        <v>-0.05974566552294238</v>
       </c>
       <c r="W73">
-        <v>0.2500864508589057</v>
+        <v>0.2498880279303098</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7294,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.2423486150789775</v>
+        <v>-0.2389826620917694</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7302,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2338675235329566</v>
+        <v>0.2357675235329565</v>
       </c>
       <c r="C74">
-        <v>-6.777801223390174</v>
+        <v>-6.981105842363441</v>
       </c>
       <c r="D74">
-        <v>4.469998776609827</v>
+        <v>4.43059415763656</v>
       </c>
       <c r="E74">
-        <v>3.8908</v>
+        <v>4.0547</v>
       </c>
       <c r="F74">
-        <v>11.8008</v>
+        <v>11.9647</v>
       </c>
       <c r="G74">
         <v>0.553</v>
@@ -7338,37 +7349,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M74">
-        <v>2.78262864</v>
+        <v>2.82127626</v>
       </c>
       <c r="N74">
-        <v>-3.44762864</v>
+        <v>-3.48627626</v>
       </c>
       <c r="O74">
-        <v>-0.8619071600000001</v>
+        <v>-0.8715690650000001</v>
       </c>
       <c r="P74">
-        <v>-2.58572148</v>
+        <v>-2.614707195</v>
       </c>
       <c r="Q74">
-        <v>-0.3457214799999999</v>
+        <v>-0.374707195</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1926719407969052</v>
+        <v>0.1981116423079017</v>
       </c>
       <c r="T74">
-        <v>2.86280749873133</v>
+        <v>2.96883740609175</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.05974566552294238</v>
+        <v>-0.0589272317486555</v>
       </c>
       <c r="W74">
-        <v>0.2498880279303098</v>
+        <v>0.249695041246333</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7376,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.2389826620917694</v>
+        <v>-0.235708926994622</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7384,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2357675235329565</v>
+        <v>0.2376675235329565</v>
       </c>
       <c r="C75">
-        <v>-6.981105842363441</v>
+        <v>-7.183721800837648</v>
       </c>
       <c r="D75">
-        <v>4.43059415763656</v>
+        <v>4.391878199162353</v>
       </c>
       <c r="E75">
-        <v>4.0547</v>
+        <v>4.2186</v>
       </c>
       <c r="F75">
-        <v>11.9647</v>
+        <v>12.1286</v>
       </c>
       <c r="G75">
         <v>0.553</v>
@@ -7420,37 +7431,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M75">
-        <v>2.82127626</v>
+        <v>2.85992388</v>
       </c>
       <c r="N75">
-        <v>-3.48627626</v>
+        <v>-3.52492388</v>
       </c>
       <c r="O75">
-        <v>-0.8715690650000001</v>
+        <v>-0.8812309700000001</v>
       </c>
       <c r="P75">
-        <v>-2.614707195</v>
+        <v>-2.64369291</v>
       </c>
       <c r="Q75">
-        <v>-0.374707195</v>
+        <v>-0.4036929100000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1981116423079017</v>
+        <v>0.2039697823966672</v>
       </c>
       <c r="T75">
-        <v>2.96883740609175</v>
+        <v>3.083023460172201</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.0589272317486555</v>
+        <v>-0.0581309178061061</v>
       </c>
       <c r="W75">
-        <v>0.249695041246333</v>
+        <v>0.2495072704186798</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7458,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.235708926994622</v>
+        <v>-0.2325236712244243</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7466,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2376675235329565</v>
+        <v>0.2395675235329566</v>
       </c>
       <c r="C76">
-        <v>-7.183721800837648</v>
+        <v>-7.385666995636195</v>
       </c>
       <c r="D76">
-        <v>4.391878199162353</v>
+        <v>4.353833004363805</v>
       </c>
       <c r="E76">
-        <v>4.2186</v>
+        <v>4.3825</v>
       </c>
       <c r="F76">
-        <v>12.1286</v>
+        <v>12.2925</v>
       </c>
       <c r="G76">
         <v>0.553</v>
@@ -7502,37 +7513,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M76">
-        <v>2.85992388</v>
+        <v>2.8985715</v>
       </c>
       <c r="N76">
-        <v>-3.52492388</v>
+        <v>-3.5635715</v>
       </c>
       <c r="O76">
-        <v>-0.8812309700000001</v>
+        <v>-0.890892875</v>
       </c>
       <c r="P76">
-        <v>-2.64369291</v>
+        <v>-2.672678625</v>
       </c>
       <c r="Q76">
-        <v>-0.4036929100000002</v>
+        <v>-0.4326786249999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2039697823966672</v>
+        <v>0.2102965736925339</v>
       </c>
       <c r="T76">
-        <v>3.083023460172201</v>
+        <v>3.20634439857909</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.0581309178061061</v>
+        <v>-0.05735583890202469</v>
       </c>
       <c r="W76">
-        <v>0.2495072704186798</v>
+        <v>0.2493245068130975</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7540,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.2325236712244243</v>
+        <v>-0.2294233556080987</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7548,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2395675235329566</v>
+        <v>0.2414675235329566</v>
       </c>
       <c r="C77">
-        <v>-7.385666995636195</v>
+        <v>-7.586958708774435</v>
       </c>
       <c r="D77">
-        <v>4.353833004363805</v>
+        <v>4.316441291225566</v>
       </c>
       <c r="E77">
-        <v>4.3825</v>
+        <v>4.5464</v>
       </c>
       <c r="F77">
-        <v>12.2925</v>
+        <v>12.4564</v>
       </c>
       <c r="G77">
         <v>0.553</v>
@@ -7584,37 +7595,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M77">
-        <v>2.8985715</v>
+        <v>2.93721912</v>
       </c>
       <c r="N77">
-        <v>-3.5635715</v>
+        <v>-3.602219120000001</v>
       </c>
       <c r="O77">
-        <v>-0.890892875</v>
+        <v>-0.9005547800000002</v>
       </c>
       <c r="P77">
-        <v>-2.672678625</v>
+        <v>-2.701664340000001</v>
       </c>
       <c r="Q77">
-        <v>-0.4326786249999999</v>
+        <v>-0.4616643400000005</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2102965736925339</v>
+        <v>0.2171505975963895</v>
       </c>
       <c r="T77">
-        <v>3.20634439857909</v>
+        <v>3.33994208185322</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.05735583890202469</v>
+        <v>-0.05660115681120857</v>
       </c>
       <c r="W77">
-        <v>0.2493245068130975</v>
+        <v>0.249146552776083</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7622,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.2294233556080987</v>
+        <v>-0.2264046272448343</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7630,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2414675235329566</v>
+        <v>0.2433675235329565</v>
       </c>
       <c r="C78">
-        <v>-7.586958708774435</v>
+        <v>-7.787613633635435</v>
       </c>
       <c r="D78">
-        <v>4.316441291225566</v>
+        <v>4.279686366364565</v>
       </c>
       <c r="E78">
-        <v>4.5464</v>
+        <v>4.7103</v>
       </c>
       <c r="F78">
-        <v>12.4564</v>
+        <v>12.6203</v>
       </c>
       <c r="G78">
         <v>0.553</v>
@@ -7666,37 +7677,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M78">
-        <v>2.93721912</v>
+        <v>2.97586674</v>
       </c>
       <c r="N78">
-        <v>-3.602219120000001</v>
+        <v>-3.640866740000001</v>
       </c>
       <c r="O78">
-        <v>-0.9005547800000002</v>
+        <v>-0.9102166850000002</v>
       </c>
       <c r="P78">
-        <v>-2.701664340000001</v>
+        <v>-2.730650055000001</v>
       </c>
       <c r="Q78">
-        <v>-0.4616643400000005</v>
+        <v>-0.4906500550000006</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2171505975963895</v>
+        <v>0.2246006235788412</v>
       </c>
       <c r="T78">
-        <v>3.33994208185322</v>
+        <v>3.485156954977271</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.05660115681120857</v>
+        <v>-0.05586607685262145</v>
       </c>
       <c r="W78">
-        <v>0.249146552776083</v>
+        <v>0.2489732209218481</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7704,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.2264046272448343</v>
+        <v>-0.2234643074104858</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7712,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2433675235329565</v>
+        <v>0.2452675235329566</v>
       </c>
       <c r="C79">
-        <v>-7.787613633635435</v>
+        <v>-7.987647899819693</v>
       </c>
       <c r="D79">
-        <v>4.279686366364565</v>
+        <v>4.243552100180307</v>
       </c>
       <c r="E79">
-        <v>4.7103</v>
+        <v>4.8742</v>
       </c>
       <c r="F79">
-        <v>12.6203</v>
+        <v>12.7842</v>
       </c>
       <c r="G79">
         <v>0.553</v>
@@ -7748,37 +7759,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M79">
-        <v>2.97586674</v>
+        <v>3.01451436</v>
       </c>
       <c r="N79">
-        <v>-3.640866740000001</v>
+        <v>-3.679514360000001</v>
       </c>
       <c r="O79">
-        <v>-0.9102166850000002</v>
+        <v>-0.9198785900000002</v>
       </c>
       <c r="P79">
-        <v>-2.730650055000001</v>
+        <v>-2.75963577</v>
       </c>
       <c r="Q79">
-        <v>-0.4906500550000006</v>
+        <v>-0.5196357700000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2246006235788412</v>
+        <v>0.2327279246506067</v>
       </c>
       <c r="T79">
-        <v>3.485156954977271</v>
+        <v>3.643573180203512</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.05586607685262145</v>
+        <v>-0.05514984509810066</v>
       </c>
       <c r="W79">
-        <v>0.2489732209218481</v>
+        <v>0.2488043334741322</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7786,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.2234643074104858</v>
+        <v>-0.2205993803924027</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7794,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2452675235329566</v>
+        <v>0.2471675235329566</v>
       </c>
       <c r="C80">
-        <v>-7.987647899819693</v>
+        <v>-8.187077096746519</v>
       </c>
       <c r="D80">
-        <v>4.243552100180307</v>
+        <v>4.208022903253481</v>
       </c>
       <c r="E80">
-        <v>4.8742</v>
+        <v>5.0381</v>
       </c>
       <c r="F80">
-        <v>12.7842</v>
+        <v>12.9481</v>
       </c>
       <c r="G80">
         <v>0.553</v>
@@ -7830,37 +7841,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M80">
-        <v>3.01451436</v>
+        <v>3.05316198</v>
       </c>
       <c r="N80">
-        <v>-3.679514360000001</v>
+        <v>-3.718161980000001</v>
       </c>
       <c r="O80">
-        <v>-0.9198785900000002</v>
+        <v>-0.9295404950000001</v>
       </c>
       <c r="P80">
-        <v>-2.75963577</v>
+        <v>-2.788621485</v>
       </c>
       <c r="Q80">
-        <v>-0.5196357700000003</v>
+        <v>-0.548621485</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2327279246506067</v>
+        <v>0.2416292543958737</v>
       </c>
       <c r="T80">
-        <v>3.643573180203512</v>
+        <v>3.817076664975108</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.05514984509810066</v>
+        <v>-0.05445174579306142</v>
       </c>
       <c r="W80">
-        <v>0.2488043334741322</v>
+        <v>0.2486397216580039</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7868,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.2205993803924027</v>
+        <v>-0.2178069831722458</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7876,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2471675235329566</v>
+        <v>0.2490675235329566</v>
       </c>
       <c r="C81">
-        <v>-8.187077096746519</v>
+        <v>-8.38591629607965</v>
       </c>
       <c r="D81">
-        <v>4.208022903253481</v>
+        <v>4.173083703920352</v>
       </c>
       <c r="E81">
-        <v>5.0381</v>
+        <v>5.202000000000002</v>
       </c>
       <c r="F81">
-        <v>12.9481</v>
+        <v>13.112</v>
       </c>
       <c r="G81">
         <v>0.553</v>
@@ -7912,37 +7923,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M81">
-        <v>3.05316198</v>
+        <v>3.0918096</v>
       </c>
       <c r="N81">
-        <v>-3.718161980000001</v>
+        <v>-3.7568096</v>
       </c>
       <c r="O81">
-        <v>-0.9295404950000001</v>
+        <v>-0.9392024000000001</v>
       </c>
       <c r="P81">
-        <v>-2.788621485</v>
+        <v>-2.8176072</v>
       </c>
       <c r="Q81">
-        <v>-0.548621485</v>
+        <v>-0.5776072000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2416292543958737</v>
+        <v>0.2514207171156674</v>
       </c>
       <c r="T81">
-        <v>3.817076664975108</v>
+        <v>4.007930498223863</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.05445174579306142</v>
+        <v>-0.05377109897064814</v>
       </c>
       <c r="W81">
-        <v>0.2486397216580039</v>
+        <v>0.2484792251372789</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7950,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.2178069831722458</v>
+        <v>-0.2150843958825925</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7958,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2490675235329566</v>
+        <v>0.2509675235329566</v>
       </c>
       <c r="C82">
-        <v>-8.38591629607965</v>
+        <v>-8.584180073044855</v>
       </c>
       <c r="D82">
-        <v>4.173083703920352</v>
+        <v>4.138719926955147</v>
       </c>
       <c r="E82">
-        <v>5.202000000000002</v>
+        <v>5.365900000000002</v>
       </c>
       <c r="F82">
-        <v>13.112</v>
+        <v>13.2759</v>
       </c>
       <c r="G82">
         <v>0.553</v>
@@ -7994,37 +8005,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M82">
-        <v>3.0918096</v>
+        <v>3.130457220000001</v>
       </c>
       <c r="N82">
-        <v>-3.7568096</v>
+        <v>-3.795457220000001</v>
       </c>
       <c r="O82">
-        <v>-0.9392024000000001</v>
+        <v>-0.9488643050000003</v>
       </c>
       <c r="P82">
-        <v>-2.8176072</v>
+        <v>-2.846592915000001</v>
       </c>
       <c r="Q82">
-        <v>-0.5776072000000001</v>
+        <v>-0.6065929150000007</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2514207171156674</v>
+        <v>0.2622428601217552</v>
       </c>
       <c r="T82">
-        <v>4.007930498223863</v>
+        <v>4.218874208656699</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.05377109897064814</v>
+        <v>-0.05310725824261545</v>
       </c>
       <c r="W82">
-        <v>0.2484792251372789</v>
+        <v>0.2483226914936087</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8032,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.2150843958825925</v>
+        <v>-0.2124290329704619</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8040,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2509675235329566</v>
+        <v>0.2528675235329566</v>
       </c>
       <c r="C83">
-        <v>-8.584180073044855</v>
+        <v>-8.781882526702908</v>
       </c>
       <c r="D83">
-        <v>4.138719926955147</v>
+        <v>4.104917473297093</v>
       </c>
       <c r="E83">
-        <v>5.365900000000002</v>
+        <v>5.529800000000002</v>
       </c>
       <c r="F83">
-        <v>13.2759</v>
+        <v>13.4398</v>
       </c>
       <c r="G83">
         <v>0.553</v>
@@ -8076,37 +8087,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M83">
-        <v>3.130457220000001</v>
+        <v>3.169104840000001</v>
       </c>
       <c r="N83">
-        <v>-3.795457220000001</v>
+        <v>-3.834104840000001</v>
       </c>
       <c r="O83">
-        <v>-0.9488643050000003</v>
+        <v>-0.9585262100000003</v>
       </c>
       <c r="P83">
-        <v>-2.846592915000001</v>
+        <v>-2.875578630000001</v>
       </c>
       <c r="Q83">
-        <v>-0.6065929150000007</v>
+        <v>-0.6355786300000004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2622428601217552</v>
+        <v>0.2742674634618527</v>
       </c>
       <c r="T83">
-        <v>4.218874208656699</v>
+        <v>4.453256109137627</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.05310725824261545</v>
+        <v>-0.05245960875185184</v>
       </c>
       <c r="W83">
-        <v>0.2483226914936087</v>
+        <v>0.2481699757436867</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8114,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.2124290329704619</v>
+        <v>-0.2098384350074074</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8122,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2528675235329566</v>
+        <v>0.2547675235329566</v>
       </c>
       <c r="C84">
-        <v>-8.781882526702908</v>
+        <v>-8.979037299237135</v>
       </c>
       <c r="D84">
-        <v>4.104917473297093</v>
+        <v>4.071662700762866</v>
       </c>
       <c r="E84">
-        <v>5.529800000000002</v>
+        <v>5.693700000000002</v>
       </c>
       <c r="F84">
-        <v>13.4398</v>
+        <v>13.6037</v>
       </c>
       <c r="G84">
         <v>0.553</v>
@@ -8158,37 +8169,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M84">
-        <v>3.169104840000001</v>
+        <v>3.20775246</v>
       </c>
       <c r="N84">
-        <v>-3.834104840000001</v>
+        <v>-3.872752460000001</v>
       </c>
       <c r="O84">
-        <v>-0.9585262100000003</v>
+        <v>-0.9681881150000002</v>
       </c>
       <c r="P84">
-        <v>-2.875578630000001</v>
+        <v>-2.904564345000001</v>
       </c>
       <c r="Q84">
-        <v>-0.6355786300000004</v>
+        <v>-0.6645643450000005</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2742674634618527</v>
+        <v>0.2877067260184323</v>
       </c>
       <c r="T84">
-        <v>4.453256109137627</v>
+        <v>4.715212350851605</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.05245960875185184</v>
+        <v>-0.05182756527291387</v>
       </c>
       <c r="W84">
-        <v>0.2481699757436867</v>
+        <v>0.2480209398913531</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8196,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.2098384350074074</v>
+        <v>-0.2073102610916555</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8204,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2547675235329566</v>
+        <v>0.2566675235329566</v>
       </c>
       <c r="C85">
-        <v>-8.979037299237135</v>
+        <v>-9.175657594310973</v>
       </c>
       <c r="D85">
-        <v>4.071662700762866</v>
+        <v>4.038942405689028</v>
       </c>
       <c r="E85">
-        <v>5.693700000000002</v>
+        <v>5.857600000000001</v>
       </c>
       <c r="F85">
-        <v>13.6037</v>
+        <v>13.7676</v>
       </c>
       <c r="G85">
         <v>0.553</v>
@@ -8240,37 +8251,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M85">
-        <v>3.20775246</v>
+        <v>3.24640008</v>
       </c>
       <c r="N85">
-        <v>-3.872752460000001</v>
+        <v>-3.911400080000001</v>
       </c>
       <c r="O85">
-        <v>-0.9681881150000002</v>
+        <v>-0.9778500200000002</v>
       </c>
       <c r="P85">
-        <v>-2.904564345000001</v>
+        <v>-2.933550060000001</v>
       </c>
       <c r="Q85">
-        <v>-0.6645643450000005</v>
+        <v>-0.6935500600000006</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2877067260184323</v>
+        <v>0.3028258963945843</v>
       </c>
       <c r="T85">
-        <v>4.715212350851605</v>
+        <v>5.009913122779831</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.05182756527291387</v>
+        <v>-0.05121057044823633</v>
       </c>
       <c r="W85">
-        <v>0.2480209398913531</v>
+        <v>0.2478754525116942</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8278,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.2073102610916555</v>
+        <v>-0.2048422817929454</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8286,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2566675235329565</v>
+        <v>0.2585675235329565</v>
       </c>
       <c r="C86">
-        <v>-9.175657594310973</v>
+        <v>-9.371756194547459</v>
       </c>
       <c r="D86">
-        <v>4.038942405689028</v>
+        <v>4.00674380545254</v>
       </c>
       <c r="E86">
-        <v>5.8576</v>
+        <v>6.0215</v>
       </c>
       <c r="F86">
-        <v>13.7676</v>
+        <v>13.9315</v>
       </c>
       <c r="G86">
         <v>0.553</v>
@@ -8322,37 +8333,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M86">
-        <v>3.24640008</v>
+        <v>3.2850477</v>
       </c>
       <c r="N86">
-        <v>-3.91140008</v>
+        <v>-3.950047700000001</v>
       </c>
       <c r="O86">
-        <v>-0.97785002</v>
+        <v>-0.9875119250000002</v>
       </c>
       <c r="P86">
-        <v>-2.93355006</v>
+        <v>-2.962535775000001</v>
       </c>
       <c r="Q86">
-        <v>-0.6935500599999997</v>
+        <v>-0.7225357750000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3028258963945842</v>
+        <v>0.3199609561542232</v>
       </c>
       <c r="T86">
-        <v>5.009913122779827</v>
+        <v>5.343907330965149</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.05121057044823633</v>
+        <v>-0.05060809314884531</v>
       </c>
       <c r="W86">
-        <v>0.2478754525116942</v>
+        <v>0.2477333883644977</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8360,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.2048422817929452</v>
+        <v>-0.2024323725953814</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8368,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2585675235329565</v>
+        <v>0.2604675235329565</v>
       </c>
       <c r="C87">
-        <v>-9.371756194547459</v>
+        <v>-9.56734547817925</v>
       </c>
       <c r="D87">
-        <v>4.00674380545254</v>
+        <v>3.975054521820749</v>
       </c>
       <c r="E87">
-        <v>6.0215</v>
+        <v>6.1854</v>
       </c>
       <c r="F87">
-        <v>13.9315</v>
+        <v>14.0954</v>
       </c>
       <c r="G87">
         <v>0.553</v>
@@ -8404,37 +8415,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M87">
-        <v>3.2850477</v>
+        <v>3.32369532</v>
       </c>
       <c r="N87">
-        <v>-3.950047700000001</v>
+        <v>-3.988695320000001</v>
       </c>
       <c r="O87">
-        <v>-0.9875119250000002</v>
+        <v>-0.9971738300000001</v>
       </c>
       <c r="P87">
-        <v>-2.962535775000001</v>
+        <v>-2.99152149</v>
       </c>
       <c r="Q87">
-        <v>-0.7225357750000003</v>
+        <v>-0.75152149</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3199609561542232</v>
+        <v>0.3395438815938105</v>
       </c>
       <c r="T87">
-        <v>5.343907330965149</v>
+        <v>5.72561499746266</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.05060809314884531</v>
+        <v>-0.05001962694944014</v>
       </c>
       <c r="W87">
-        <v>0.2477333883644977</v>
+        <v>0.247594628034678</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8442,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.2024323725953814</v>
+        <v>-0.2000785077977607</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8450,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2604675235329565</v>
+        <v>0.2623675235329566</v>
       </c>
       <c r="C88">
-        <v>-9.56734547817925</v>
+        <v>-9.76243743491472</v>
       </c>
       <c r="D88">
-        <v>3.975054521820749</v>
+        <v>3.94386256508528</v>
       </c>
       <c r="E88">
-        <v>6.1854</v>
+        <v>6.349299999999999</v>
       </c>
       <c r="F88">
-        <v>14.0954</v>
+        <v>14.2593</v>
       </c>
       <c r="G88">
         <v>0.553</v>
@@ -8486,37 +8497,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M88">
-        <v>3.32369532</v>
+        <v>3.36234294</v>
       </c>
       <c r="N88">
-        <v>-3.988695320000001</v>
+        <v>-4.02734294</v>
       </c>
       <c r="O88">
-        <v>-0.9971738300000001</v>
+        <v>-1.006835735</v>
       </c>
       <c r="P88">
-        <v>-2.99152149</v>
+        <v>-3.020507205</v>
       </c>
       <c r="Q88">
-        <v>-0.75152149</v>
+        <v>-0.7805072050000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3395438815938105</v>
+        <v>0.3621395647933344</v>
       </c>
       <c r="T88">
-        <v>5.72561499746266</v>
+        <v>6.166046920344403</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.05001962694944014</v>
+        <v>-0.04944468870864198</v>
       </c>
       <c r="W88">
-        <v>0.247594628034678</v>
+        <v>0.2474590575974978</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8524,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.2000785077977607</v>
+        <v>-0.197778754834568</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8532,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2623675235329566</v>
+        <v>0.2642675235329566</v>
       </c>
       <c r="C89">
-        <v>-9.76243743491472</v>
+        <v>-9.957043681062892</v>
       </c>
       <c r="D89">
-        <v>3.94386256508528</v>
+        <v>3.91315631893711</v>
       </c>
       <c r="E89">
-        <v>6.349299999999999</v>
+        <v>6.513200000000001</v>
       </c>
       <c r="F89">
-        <v>14.2593</v>
+        <v>14.4232</v>
       </c>
       <c r="G89">
         <v>0.553</v>
@@ -8568,37 +8579,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M89">
-        <v>3.36234294</v>
+        <v>3.40099056</v>
       </c>
       <c r="N89">
-        <v>-4.02734294</v>
+        <v>-4.06599056</v>
       </c>
       <c r="O89">
-        <v>-1.006835735</v>
+        <v>-1.01649764</v>
       </c>
       <c r="P89">
-        <v>-3.020507205</v>
+        <v>-3.04949292</v>
       </c>
       <c r="Q89">
-        <v>-0.7805072050000001</v>
+        <v>-0.8094929200000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3621395647933344</v>
+        <v>0.388501195192779</v>
       </c>
       <c r="T89">
-        <v>6.166046920344403</v>
+        <v>6.679884163706439</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.04944468870864198</v>
+        <v>-0.04888281724604376</v>
       </c>
       <c r="W89">
-        <v>0.2474590575974978</v>
+        <v>0.2473265683066171</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8606,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.197778754834568</v>
+        <v>-0.1955312689841751</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8614,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2642675235329566</v>
+        <v>0.2661675235329565</v>
       </c>
       <c r="C90">
-        <v>-9.957043681062892</v>
+        <v>-10.15117547395724</v>
       </c>
       <c r="D90">
-        <v>3.91315631893711</v>
+        <v>3.882924526042764</v>
       </c>
       <c r="E90">
-        <v>6.513200000000001</v>
+        <v>6.677100000000001</v>
       </c>
       <c r="F90">
-        <v>14.4232</v>
+        <v>14.5871</v>
       </c>
       <c r="G90">
         <v>0.553</v>
@@ -8650,37 +8661,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M90">
-        <v>3.40099056</v>
+        <v>3.439638180000001</v>
       </c>
       <c r="N90">
-        <v>-4.06599056</v>
+        <v>-4.104638180000001</v>
       </c>
       <c r="O90">
-        <v>-1.01649764</v>
+        <v>-1.026159545</v>
       </c>
       <c r="P90">
-        <v>-3.04949292</v>
+        <v>-3.078478635000001</v>
       </c>
       <c r="Q90">
-        <v>-0.8094929200000003</v>
+        <v>-0.8384786350000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.388501195192779</v>
+        <v>0.4196558493012134</v>
       </c>
       <c r="T90">
-        <v>6.679884163706439</v>
+        <v>7.287146360407022</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.04888281724604376</v>
+        <v>-0.04833357210844776</v>
       </c>
       <c r="W90">
-        <v>0.2473265683066171</v>
+        <v>0.247197056303172</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8688,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.1955312689841751</v>
+        <v>-0.1933342884337912</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8696,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2661675235329565</v>
+        <v>0.2680675235329565</v>
       </c>
       <c r="C91">
-        <v>-10.15117547395724</v>
+        <v>-10.34484372571605</v>
       </c>
       <c r="D91">
-        <v>3.882924526042764</v>
+        <v>3.85315627428395</v>
       </c>
       <c r="E91">
-        <v>6.677100000000001</v>
+        <v>6.841000000000001</v>
       </c>
       <c r="F91">
-        <v>14.5871</v>
+        <v>14.751</v>
       </c>
       <c r="G91">
         <v>0.553</v>
@@ -8732,37 +8743,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M91">
-        <v>3.439638180000001</v>
+        <v>3.478285800000001</v>
       </c>
       <c r="N91">
-        <v>-4.104638180000001</v>
+        <v>-4.143285800000001</v>
       </c>
       <c r="O91">
-        <v>-1.026159545</v>
+        <v>-1.03582145</v>
       </c>
       <c r="P91">
-        <v>-3.078478635000001</v>
+        <v>-3.107464350000001</v>
       </c>
       <c r="Q91">
-        <v>-0.8384786350000004</v>
+        <v>-0.8674643500000006</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4196558493012134</v>
+        <v>0.4570414342313348</v>
       </c>
       <c r="T91">
-        <v>7.287146360407022</v>
+        <v>8.015860996447726</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.04833357210844776</v>
+        <v>-0.0477965324183539</v>
       </c>
       <c r="W91">
-        <v>0.247197056303172</v>
+        <v>0.2470704223442478</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8770,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.1933342884337912</v>
+        <v>-0.1911861296734156</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8778,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2680675235329565</v>
+        <v>0.2699675235329566</v>
       </c>
       <c r="C92">
-        <v>-10.34484372571605</v>
+        <v>-10.53805901637462</v>
       </c>
       <c r="D92">
-        <v>3.85315627428395</v>
+        <v>3.823840983625382</v>
       </c>
       <c r="E92">
-        <v>6.841000000000001</v>
+        <v>7.004900000000001</v>
       </c>
       <c r="F92">
-        <v>14.751</v>
+        <v>14.9149</v>
       </c>
       <c r="G92">
         <v>0.553</v>
@@ -8814,37 +8825,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M92">
-        <v>3.478285800000001</v>
+        <v>3.51693342</v>
       </c>
       <c r="N92">
-        <v>-4.143285800000001</v>
+        <v>-4.181933420000001</v>
       </c>
       <c r="O92">
-        <v>-1.03582145</v>
+        <v>-1.045483355</v>
       </c>
       <c r="P92">
-        <v>-3.107464350000001</v>
+        <v>-3.136450065000001</v>
       </c>
       <c r="Q92">
-        <v>-0.8674643500000006</v>
+        <v>-0.8964500650000007</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4570414342313348</v>
+        <v>0.5027349269237054</v>
       </c>
       <c r="T92">
-        <v>8.015860996447726</v>
+        <v>8.906512218275253</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.0477965324183539</v>
+        <v>-0.04727129579837199</v>
       </c>
       <c r="W92">
-        <v>0.2470704223442478</v>
+        <v>0.2469465715492561</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8852,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.1911861296734156</v>
+        <v>-0.1890851831934881</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8860,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2699675235329566</v>
+        <v>0.2718675235329566</v>
       </c>
       <c r="C93">
-        <v>-10.53805901637462</v>
+        <v>-10.7308316064225</v>
       </c>
       <c r="D93">
-        <v>3.823840983625382</v>
+        <v>3.794968393577504</v>
       </c>
       <c r="E93">
-        <v>7.004900000000001</v>
+        <v>7.168800000000001</v>
       </c>
       <c r="F93">
-        <v>14.9149</v>
+        <v>15.0788</v>
       </c>
       <c r="G93">
         <v>0.553</v>
@@ -8896,37 +8907,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M93">
-        <v>3.51693342</v>
+        <v>3.55558104</v>
       </c>
       <c r="N93">
-        <v>-4.181933420000001</v>
+        <v>-4.220581040000001</v>
       </c>
       <c r="O93">
-        <v>-1.045483355</v>
+        <v>-1.05514526</v>
       </c>
       <c r="P93">
-        <v>-3.136450065000001</v>
+        <v>-3.165435780000001</v>
       </c>
       <c r="Q93">
-        <v>-0.8964500650000007</v>
+        <v>-0.9254357800000004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5027349269237054</v>
+        <v>0.5598517927891686</v>
       </c>
       <c r="T93">
-        <v>8.906512218275253</v>
+        <v>10.01982624555966</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.04727129579837199</v>
+        <v>-0.04675747736578099</v>
       </c>
       <c r="W93">
-        <v>0.2469465715492561</v>
+        <v>0.2468254131628512</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8934,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.1890851831934881</v>
+        <v>-0.187029909463124</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8942,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2718675235329566</v>
+        <v>0.2737675235329566</v>
       </c>
       <c r="C94">
-        <v>-10.7308316064225</v>
+        <v>-10.92317144877702</v>
       </c>
       <c r="D94">
-        <v>3.794968393577504</v>
+        <v>3.766528551222978</v>
       </c>
       <c r="E94">
-        <v>7.168800000000001</v>
+        <v>7.332700000000001</v>
       </c>
       <c r="F94">
-        <v>15.0788</v>
+        <v>15.2427</v>
       </c>
       <c r="G94">
         <v>0.553</v>
@@ -8978,37 +8989,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M94">
-        <v>3.55558104</v>
+        <v>3.59422866</v>
       </c>
       <c r="N94">
-        <v>-4.220581040000001</v>
+        <v>-4.259228660000001</v>
       </c>
       <c r="O94">
-        <v>-1.05514526</v>
+        <v>-1.064807165</v>
       </c>
       <c r="P94">
-        <v>-3.165435780000001</v>
+        <v>-3.194421495</v>
       </c>
       <c r="Q94">
-        <v>-0.9254357800000004</v>
+        <v>-0.9544214950000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5598517927891686</v>
+        <v>0.6332877631876214</v>
       </c>
       <c r="T94">
-        <v>10.01982624555966</v>
+        <v>11.45122999492533</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.04675747736578099</v>
+        <v>-0.0462547087919554</v>
       </c>
       <c r="W94">
-        <v>0.2468254131628512</v>
+        <v>0.2467068603331431</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9016,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.187029909463124</v>
+        <v>-0.1850188351678217</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9024,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2737675235329566</v>
+        <v>0.2756675235329565</v>
       </c>
       <c r="C95">
-        <v>-10.92317144877702</v>
+        <v>-11.11508820022248</v>
       </c>
       <c r="D95">
-        <v>3.766528551222978</v>
+        <v>3.738511799777525</v>
       </c>
       <c r="E95">
-        <v>7.332700000000001</v>
+        <v>7.496600000000001</v>
       </c>
       <c r="F95">
-        <v>15.2427</v>
+        <v>15.4066</v>
       </c>
       <c r="G95">
         <v>0.553</v>
@@ -9060,37 +9071,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M95">
-        <v>3.59422866</v>
+        <v>3.632876280000001</v>
       </c>
       <c r="N95">
-        <v>-4.259228660000001</v>
+        <v>-4.297876280000001</v>
       </c>
       <c r="O95">
-        <v>-1.064807165</v>
+        <v>-1.07446907</v>
       </c>
       <c r="P95">
-        <v>-3.194421495</v>
+        <v>-3.22340721</v>
       </c>
       <c r="Q95">
-        <v>-0.9544214950000001</v>
+        <v>-0.9834072100000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6332877631876214</v>
+        <v>0.7312023903855586</v>
       </c>
       <c r="T95">
-        <v>11.45122999492533</v>
+        <v>13.35976832741289</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.0462547087919554</v>
+        <v>-0.04576263742182821</v>
       </c>
       <c r="W95">
-        <v>0.2467068603331431</v>
+        <v>0.2465908299040671</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9098,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.1850188351678217</v>
+        <v>-0.1830505496873127</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9106,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2756675235329565</v>
+        <v>0.2775675235329566</v>
       </c>
       <c r="C96">
-        <v>-11.11508820022248</v>
+        <v>-11.30659123234245</v>
       </c>
       <c r="D96">
-        <v>3.738511799777525</v>
+        <v>3.710908767657548</v>
       </c>
       <c r="E96">
-        <v>7.496600000000001</v>
+        <v>7.660500000000001</v>
       </c>
       <c r="F96">
-        <v>15.4066</v>
+        <v>15.5705</v>
       </c>
       <c r="G96">
         <v>0.553</v>
@@ -9142,37 +9153,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M96">
-        <v>3.632876280000001</v>
+        <v>3.6715239</v>
       </c>
       <c r="N96">
-        <v>-4.297876280000001</v>
+        <v>-4.3365239</v>
       </c>
       <c r="O96">
-        <v>-1.07446907</v>
+        <v>-1.084130975</v>
       </c>
       <c r="P96">
-        <v>-3.22340721</v>
+        <v>-3.252392925000001</v>
       </c>
       <c r="Q96">
-        <v>-0.9834072100000002</v>
+        <v>-1.012392925</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7312023903855586</v>
+        <v>0.8682828684626704</v>
       </c>
       <c r="T96">
-        <v>13.35976832741289</v>
+        <v>16.03172199289547</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.04576263742182821</v>
+        <v>-0.04528092544896686</v>
       </c>
       <c r="W96">
-        <v>0.2465908299040671</v>
+        <v>0.2464772422208664</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9180,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.1830505496873127</v>
+        <v>-0.1811237017958673</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9188,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2775675235329566</v>
+        <v>0.2794675235329566</v>
       </c>
       <c r="C97">
-        <v>-11.30659123234245</v>
+        <v>-11.49768964197149</v>
       </c>
       <c r="D97">
-        <v>3.710908767657548</v>
+        <v>3.683710358028508</v>
       </c>
       <c r="E97">
-        <v>7.660500000000001</v>
+        <v>7.824400000000002</v>
       </c>
       <c r="F97">
-        <v>15.5705</v>
+        <v>15.7344</v>
       </c>
       <c r="G97">
         <v>0.553</v>
@@ -9224,37 +9235,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M97">
-        <v>3.6715239</v>
+        <v>3.710171520000001</v>
       </c>
       <c r="N97">
-        <v>-4.3365239</v>
+        <v>-4.375171520000001</v>
       </c>
       <c r="O97">
-        <v>-1.084130975</v>
+        <v>-1.09379288</v>
       </c>
       <c r="P97">
-        <v>-3.252392925000001</v>
+        <v>-3.281378640000001</v>
       </c>
       <c r="Q97">
-        <v>-1.012392925</v>
+        <v>-1.04137864</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8682828684626704</v>
+        <v>1.073903585578339</v>
       </c>
       <c r="T97">
-        <v>16.03172199289547</v>
+        <v>20.03965249111935</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.04528092544896686</v>
+        <v>-0.04480924914220678</v>
       </c>
       <c r="W97">
-        <v>0.2464772422208664</v>
+        <v>0.2463660209477324</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9262,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.1811237017958673</v>
+        <v>-0.1792369965688272</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9270,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2794675235329566</v>
+        <v>0.2813675235329566</v>
       </c>
       <c r="C98">
-        <v>-11.49768964197149</v>
+        <v>-11.68839226119043</v>
       </c>
       <c r="D98">
-        <v>3.683710358028508</v>
+        <v>3.656907738809569</v>
       </c>
       <c r="E98">
-        <v>7.824400000000001</v>
+        <v>7.988300000000001</v>
       </c>
       <c r="F98">
-        <v>15.7344</v>
+        <v>15.8983</v>
       </c>
       <c r="G98">
         <v>0.553</v>
@@ -9306,37 +9317,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M98">
-        <v>3.71017152</v>
+        <v>3.74881914</v>
       </c>
       <c r="N98">
-        <v>-4.37517152</v>
+        <v>-4.41381914</v>
       </c>
       <c r="O98">
-        <v>-1.09379288</v>
+        <v>-1.103454785</v>
       </c>
       <c r="P98">
-        <v>-3.28137864</v>
+        <v>-3.310364355</v>
       </c>
       <c r="Q98">
-        <v>-1.04137864</v>
+        <v>-1.070364355</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.073903585578336</v>
+        <v>1.416604780771115</v>
       </c>
       <c r="T98">
-        <v>20.03965249111929</v>
+        <v>26.71953665482573</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.04480924914220679</v>
+        <v>-0.04434729812012218</v>
       </c>
       <c r="W98">
-        <v>0.2463660209477324</v>
+        <v>0.2462570928967248</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9344,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.1792369965688272</v>
+        <v>-0.1773891924804887</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9352,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2813675235329566</v>
+        <v>0.2832675235329565</v>
       </c>
       <c r="C99">
-        <v>-11.68839226119043</v>
+        <v>-11.87870766688854</v>
       </c>
       <c r="D99">
-        <v>3.656907738809569</v>
+        <v>3.630492333111456</v>
       </c>
       <c r="E99">
-        <v>7.988300000000001</v>
+        <v>8.152200000000001</v>
       </c>
       <c r="F99">
-        <v>15.8983</v>
+        <v>16.0622</v>
       </c>
       <c r="G99">
         <v>0.553</v>
@@ -9388,37 +9399,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M99">
-        <v>3.74881914</v>
+        <v>3.78746676</v>
       </c>
       <c r="N99">
-        <v>-4.41381914</v>
+        <v>-4.452466760000001</v>
       </c>
       <c r="O99">
-        <v>-1.103454785</v>
+        <v>-1.11311669</v>
       </c>
       <c r="P99">
-        <v>-3.310364355</v>
+        <v>-3.339350070000001</v>
       </c>
       <c r="Q99">
-        <v>-1.070364355</v>
+        <v>-1.099350070000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.416604780771115</v>
+        <v>2.102007171156671</v>
       </c>
       <c r="T99">
-        <v>26.71953665482573</v>
+        <v>40.07930498223858</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.04434729812012218</v>
+        <v>-0.04389477466991685</v>
       </c>
       <c r="W99">
-        <v>0.2462570928967248</v>
+        <v>0.2461503878671664</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9426,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.1773891924804887</v>
+        <v>-0.1755790986796675</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9434,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2832675235329565</v>
+        <v>0.2851675235329565</v>
       </c>
       <c r="C100">
-        <v>-11.87870766688854</v>
+        <v>-12.06864418991423</v>
       </c>
       <c r="D100">
-        <v>3.630492333111456</v>
+        <v>3.604455810085768</v>
       </c>
       <c r="E100">
-        <v>8.152200000000001</v>
+        <v>8.316099999999999</v>
       </c>
       <c r="F100">
-        <v>16.0622</v>
+        <v>16.2261</v>
       </c>
       <c r="G100">
         <v>0.553</v>
@@ -9470,37 +9481,37 @@
         <v>-0.6650000000000003</v>
       </c>
       <c r="M100">
-        <v>3.78746676</v>
+        <v>3.82611438</v>
       </c>
       <c r="N100">
-        <v>-4.452466760000001</v>
+        <v>-4.49111438</v>
       </c>
       <c r="O100">
-        <v>-1.11311669</v>
+        <v>-1.122778595</v>
       </c>
       <c r="P100">
-        <v>-3.339350070000001</v>
+        <v>-3.368335785</v>
       </c>
       <c r="Q100">
-        <v>-1.099350070000001</v>
+        <v>-1.128335785</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.102007171156671</v>
+        <v>4.158214342313344</v>
       </c>
       <c r="T100">
-        <v>40.07930498223858</v>
+        <v>80.15860996447718</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.04389477466991685</v>
+        <v>-0.04345139310759447</v>
       </c>
       <c r="W100">
-        <v>0.2461503878671664</v>
+        <v>0.2460458384947708</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9508,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.1755790986796675</v>
+        <v>-0.1738055724303778</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2851675235329565</v>
-      </c>
-      <c r="C101">
-        <v>-12.06864418991423</v>
-      </c>
-      <c r="D101">
-        <v>3.604455810085768</v>
-      </c>
-      <c r="E101">
-        <v>8.316099999999999</v>
-      </c>
-      <c r="F101">
-        <v>16.2261</v>
-      </c>
-      <c r="G101">
-        <v>0.553</v>
-      </c>
-      <c r="H101">
-        <v>8.48</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.575</v>
-      </c>
-      <c r="K101">
-        <v>2.24</v>
-      </c>
-      <c r="L101">
-        <v>-0.6650000000000003</v>
-      </c>
-      <c r="M101">
-        <v>3.82611438</v>
-      </c>
-      <c r="N101">
-        <v>-4.49111438</v>
-      </c>
-      <c r="O101">
-        <v>-1.122778595</v>
-      </c>
-      <c r="P101">
-        <v>-3.368335785</v>
-      </c>
-      <c r="Q101">
-        <v>-1.128335785</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.158214342313344</v>
-      </c>
-      <c r="T101">
-        <v>80.15860996447718</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.04345139310759447</v>
-      </c>
-      <c r="W101">
-        <v>0.2460458384947708</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.1738055724303778</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
